--- a/data/kennedy_mira_consolidado.xlsx
+++ b/data/kennedy_mira_consolidado.xlsx
@@ -18792,7 +18792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J222"/>
+  <dimension ref="A1:K222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18843,6 +18843,11 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>LIDER</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>OBSERVACIONES</t>
         </is>
       </c>
@@ -18875,7 +18880,8 @@
           <t>TERRITORIO</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
         <is>
           <t>Lanzamiento de campaña en Kennedy</t>
         </is>
@@ -18909,7 +18915,8 @@
           <t>TERRITORIO</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
         <is>
           <t>Lanzamiento de campaña en Kennedy</t>
         </is>
@@ -18943,7 +18950,8 @@
           <t>TERRITORIO</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
         <is>
           <t>Lanzamiento de campaña en Kennedy</t>
         </is>
@@ -18983,6 +18991,11 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>Hamilton Liz (Delegado Político)</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>Reunión con líderes Patio Bonito para seguimiento de preparativos de reuniones campaña 13 de diciembre</t>
         </is>
       </c>
@@ -19021,6 +19034,11 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>Jenny García (Delegado Político)</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>Reunión con líderes Kennedy Central para seguimiento de preparativos de reuniones campaña 14 de diciembre</t>
         </is>
       </c>
@@ -19059,6 +19077,11 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t>Sergio Osorio (Delagado Político)</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>Reunión con líderes Carvajal para seguimiento de preparativos de reuniones campaña 16 de diciembre</t>
         </is>
       </c>
@@ -19101,6 +19124,11 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
+          <t>Paula Alarcón (3504846700)</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t>MT - VILLA HERMOSA MALLA VIAL (3822) Reunión con vecinos del sector + MT - VILLA HERMOSA TAPAS TELECOMUNICACIONES</t>
         </is>
       </c>
@@ -19143,6 +19171,11 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t>Hamilton Liz (Delegado Político)</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Almuerzo </t>
         </is>
       </c>
@@ -19185,6 +19218,11 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t>Ana Temilda Guerrero (3124899155)</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t>MT - CIUDADELA PRIMAVERA MALLA VIAL Y CANCHA (248)</t>
         </is>
       </c>
@@ -19228,6 +19266,11 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t>Luz Elena Garzón ( 3144359628)</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t>MT - TINTAL BASURAS PUNTO CRITICO (2738)</t>
         </is>
       </c>
@@ -19264,7 +19307,8 @@
           <t>ENSENANZA</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
         <is>
           <t>Reunion de Afinidad Objetivo
 Que los hnos puedan compartir con  nuestros representantes, y ellos puedan motivarlos a activar sus referidos y a participar activamente del bingo
@@ -19309,7 +19353,8 @@
           <t>ENSENANZA</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
         <is>
           <t>Reunion de Afinidad Objetivo
 Que los hnos puedan compartir con  nuestros representantes, y ellos puedan motivarlos a activar sus referidos y a participar activamente del bingo
@@ -19352,6 +19397,11 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
+          <t>Jenny García - Delegada Política 3108524285</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
           <t>En la sede</t>
         </is>
       </c>
@@ -19390,7 +19440,8 @@
           <t>TERRITORIO</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
         <is>
           <t>MT - ROMA IV 1ER SECTOR MALLA VIAL (1969) Reunión con sector comercial
 y habitantes de Roma + MT - CASABLANCA JORNADA OPAM (5646)</t>
@@ -19435,6 +19486,11 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
+          <t>Rafael Gutierrez (3114901573)</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t>MT - LAS MARGARITAS ZONAS DE CESION (4329)</t>
         </is>
       </c>
@@ -19477,6 +19533,11 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
+          <t>Sergio Osorio (Delagado Político) 3505621182</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
           <t>REUNION EN EL SEGUNDO PISO CON LIDERES QUE NO TIENEN REFERIDOS Y CON LOS QUE SOLO TIENEN 5 REFERIDOS</t>
         </is>
       </c>
@@ -19518,6 +19579,11 @@
         </is>
       </c>
       <c r="J18" t="inlineStr">
+        <is>
+          <t>Carmen Garzón</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>MT - CARVAJAL PARE ACOSTADO MAL PARQUEO PARQUE MARACANA</t>
         </is>
@@ -19547,7 +19613,8 @@
           <t>ALMUERZO</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
         <is>
           <t>Almuerzo</t>
         </is>
@@ -19591,6 +19658,11 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
+          <t>Gloria Rincón</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
           <t>MT - AMERICAS CLÍNICA OCCIDENTE MALLA VIAL (2052)</t>
         </is>
       </c>
@@ -19633,6 +19705,11 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
+          <t>Jimmy Gutierrez</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t>MT - MANDALAY OBRAS DE RENOVACIÓN EAAB (3269)</t>
         </is>
       </c>
@@ -19675,6 +19752,11 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
+          <t>Sergio Osorio (Delagado Político) 3505621182</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t>REUNION EN EL SEGUNDO PISO CON LIDERES QUE NO TIENEN REFERIDOS Y CON LOS QUE SOLO TIENEN 5 REFERIDOS</t>
         </is>
       </c>
@@ -19713,6 +19795,11 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
+          <t>Fernando Zamora - Lorena Garzón</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t>Reunión con DP para seguimiento de preparativos de reuniones campaña enero</t>
         </is>
       </c>
@@ -19755,6 +19842,11 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
+          <t>Sergio Osorio (Delagado Político) 3505621182</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
           <t>Bingo</t>
         </is>
       </c>
@@ -19797,6 +19889,11 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
+          <t>Jenny García (3108524285)</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
           <t>Bingo</t>
         </is>
       </c>
@@ -19839,6 +19936,11 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
+          <t>Bryan Rodríguez (3202378579)</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
           <t xml:space="preserve">Reunion Identidad y Conviccion y motivacion a personas recientes en la iglesia </t>
         </is>
       </c>
@@ -19881,6 +19983,11 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
+          <t>Albeiro Rodriguez (3124215077)</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
           <t xml:space="preserve">Micro reunion con líderes que tienen de 0 a 5 referidos; objetivo motivarlos a hablar del partido </t>
         </is>
       </c>
@@ -19923,6 +20030,11 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
+          <t>Jenny García (3108524285)</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
           <t>Actividad de afinidad - activación de líderes y referidos [PENDIENTE DELEGADO DESCRIBIR LA ACTIVIDAD]</t>
         </is>
       </c>
@@ -19965,6 +20077,11 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
+          <t>Jenny García (3108524285)</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t>Actividad de afinidad - activación de líderes y referidos [PENDIENTE DELEGADO DESCRIBIR LA ACTIVIDAD]</t>
         </is>
       </c>
@@ -20007,6 +20124,11 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
+          <t>Hamilton Liz (3125621911)</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t>Actividad de afinidad - activación de líderes y referidos [PENDIENTE DELEGADO DESCRIBIR LA ACTIVIDAD]</t>
         </is>
       </c>
@@ -20049,6 +20171,11 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
+          <t>Hamilton Liz (3125621911)</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t>Actividad de afinidad - activación de líderes y referidos [PENDIENTE DELEGADO DESCRIBIR LA ACTIVIDAD]</t>
         </is>
       </c>
@@ -20089,7 +20216,8 @@
           <t>ALABANZA</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
         <is>
           <t>Actividad de afinidad - activación de líderes y referidos Colaboradores de la iglesia</t>
         </is>
@@ -20132,6 +20260,11 @@
         </is>
       </c>
       <c r="J33" t="inlineStr">
+        <is>
+          <t>Blanca</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
         <is>
           <t>MT – PORTAL DE CALI REDES DE ACUEDUCTO (2015)</t>
         </is>
@@ -20161,7 +20294,8 @@
           <t>ALMUERZO</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
         <is>
           <t>ALMUERZO</t>
         </is>
@@ -20205,6 +20339,11 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
+          <t>Aldemar Rodriguez</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
           <t>MT - VEGAS DE SANTA ANA MALLA VIAL E INUNDACIONES RÍO TUNJUELO (5509)</t>
         </is>
       </c>
@@ -20247,6 +20386,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
+          <t xml:space="preserve">Liliana Malagon 
+</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
           <t>Reunión con vecinos y familiares</t>
         </is>
       </c>
@@ -20287,7 +20432,8 @@
           <t>ALABANZA</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
         <is>
           <t>Actividad de afinidad - activación de líderes y referidos - Colaboradores de la iglesia</t>
         </is>
@@ -20325,7 +20471,12 @@
           <t>ENSENANZA</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Hamilton Liz (3125621911)</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -20365,6 +20516,11 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
+          <t>ALVARO GARZÓN</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
           <t>VISITA MICROEMPRESA</t>
         </is>
       </c>
@@ -20408,6 +20564,11 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
+          <t>VERONICA AVILA</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
           <t>Riveras de Occidente</t>
         </is>
       </c>
@@ -20444,7 +20605,12 @@
           <t>ENSENANZA</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Hamilton Liz (3125621911)</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -20482,7 +20648,8 @@
           <t>ENSENANZA</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
         <is>
           <t>Actividad de afinidad - activación de líderes y referidos 
 Microreunión Focalizada MRF
@@ -20527,6 +20694,12 @@
         </is>
       </c>
       <c r="J43" t="inlineStr">
+        <is>
+          <t>ORLANDO MARULANDA LEON
+3045831717</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
         <is>
           <t>MT - CIUDAD DE CALI AFECTACIÓN POR SEMÁFORO (5109)</t>
         </is>
@@ -20556,7 +20729,8 @@
           <t>ALMUERZO</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
         <is>
           <t>ALMUERZO	ALMUERZO</t>
         </is>
@@ -20601,6 +20775,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
+          <t>MIGUEL ADRIEL GUERRERO SANCHEZ
+3214929228</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t>MT - CIUDAD KENNEDY OCCIDENTAL INSEGURIDAD POR RETIRO DE REJAS DE INGRESO (6236</t>
         </is>
       </c>
@@ -20643,6 +20823,13 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
+          <t xml:space="preserve">NUBIA LILIANA PARRA GUERRERO
+3202930363
+</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t>MT - JORNADA OPAM PARQUE HOLANDA (6172)</t>
         </is>
       </c>
@@ -20683,7 +20870,8 @@
           <t>ENSENANZA</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
         <is>
           <t>Actividad de afinidad - activación de líderes y referidos 
 Microreunión Focalizada MRF
@@ -20727,7 +20915,8 @@
           <t>ENSENANZA</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
         <is>
           <t>Actividad de afinidad - activación de líderes y referidos 
 Microreunión Focalizada MRF
@@ -20771,7 +20960,8 @@
           <t>ALABANZA</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
         <is>
           <t xml:space="preserve">Actividad de afinidad - activación de líderes y referidos:
 REUNION CON LIDERES EN EL SEGUNDO PISO DE CARVAJAL, SE VA A INVITAR APROXIMADAMENTE 30 PERSONAS QUE AUN NO SE HAN ACTIVADO COMO LIDERES, QUE NO TIENE REFERIDOS, PARA REALIZAR ACTIVIDAD DENTRO DE LA REUNION, ASI M ISMO SE DARA A CONOCER A LOS CANDIDATOS Y SE REALIZARA PEDAGOGIA ELECTORAL </t>
@@ -20815,6 +21005,12 @@
         </is>
       </c>
       <c r="J50" t="inlineStr">
+        <is>
+          <t>FRANZ JAIR RODRIGUEZ MENDOZA
+3005588503</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
         <is>
           <t>MT – AMERICAS OCCIDENTAL REDUCTORES DE VELOCIDAD</t>
         </is>
@@ -20844,7 +21040,8 @@
           <t>ALMUERZO</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
         <is>
           <t>ALMUERZO</t>
         </is>
@@ -20888,6 +21085,12 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
+          <t>ANA EULALIA BECERRA RODRIGUEZ
+3132151731</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t>MT - VILLA ALSACIA MALA DISPOSICIÓN DE RESIDUOS EN CANECAS METALICAS (6239)</t>
         </is>
       </c>
@@ -20930,6 +21133,11 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
+          <t xml:space="preserve">MARIA LUISA ARIAS Y SERGIO OSORIO </t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t>FERIA DE SERVICIOS</t>
         </is>
       </c>
@@ -20970,7 +21178,8 @@
           <t>ALABANZA</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
         <is>
           <t xml:space="preserve">Actividad de afinidad - activación de líderes y referidos:
 REUNION CON LIDERES EN EL SEGUNDO PISO DE CARVAJAL, SE VA A INVITAR APROXIMADAMENTE 30 PERSONAS QUE AUN NO SE HAN ACTIVADO COMO LIDERES, QUE NO TIENE REFERIDOS, PARA REALIZAR ACTIVIDAD DENTRO DE LA REUNION, ASI M ISMO SE DARA A CONOCER A LOS CANDIDATOS Y SE REALIZARA PEDAGOGIA ELECTORAL </t>
@@ -21013,7 +21222,8 @@
           <t>ALABANZA</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
         <is>
           <t xml:space="preserve">Actividad de afinidad - Microreunión activación de líderes y referidos </t>
         </is>
@@ -21057,6 +21267,12 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
+          <t>LILIANA ANDREA TOCA SANCHEZ
+3115822253</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
           <t>Reunión con familiares y referidos</t>
         </is>
       </c>
@@ -21099,6 +21315,11 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
+          <t xml:space="preserve"> Fabio Andrés Cortes 3178081946</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
           <t>Reunión empresario de corabastos</t>
         </is>
       </c>
@@ -21135,7 +21356,8 @@
           <t>ALMUERZO</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
         <is>
           <t>ALMUERZO</t>
         </is>
@@ -21179,6 +21401,11 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
+          <t>Cristian Gomez</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
           <t>Actividad de Juventudes</t>
         </is>
       </c>
@@ -21221,6 +21448,11 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
+          <t>Mary Mendez</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
           <t>Reunión con familiares y referidos</t>
         </is>
       </c>
@@ -21263,6 +21495,12 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
+          <t>MIGUEL MOJICA
+(líder externo)</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
           <t>Reunión con familiares y referidos</t>
         </is>
       </c>
@@ -21303,7 +21541,8 @@
           <t>ALABANZA</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
         <is>
           <t xml:space="preserve">Actividad de afinidad - Microreunión activación de líderes y referidos </t>
         </is>
@@ -21346,6 +21585,11 @@
         </is>
       </c>
       <c r="J63" t="inlineStr">
+        <is>
+          <t>Ricardo Gutiérrez</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
         <is>
           <t>Reunión con empresario de jeans</t>
         </is>
@@ -21375,7 +21619,8 @@
           <t>ALMUERZO</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
         <is>
           <t>ALMUERZO</t>
         </is>
@@ -21419,6 +21664,11 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
+          <t>John Jairo Díaz  3227864558</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
           <t>Visita empresa JJD world logistic sas</t>
         </is>
       </c>
@@ -21461,6 +21711,11 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
+          <t>Rocio Aranzalez</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
           <t>Visita empresa Pastelería Cikoloto</t>
         </is>
       </c>
@@ -21502,6 +21757,11 @@
         </is>
       </c>
       <c r="J67" t="inlineStr">
+        <is>
+          <t>Rocio Aranzalez</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
         <is>
           <t>Recorrido comerciantes:
 Carrera 70 b # 2 a 30 pet shop
@@ -21548,6 +21808,11 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
+          <t>Rocio Aranzalez</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
           <t>Reunión de campaña</t>
         </is>
       </c>
@@ -21588,7 +21853,8 @@
           <t>ALABANZA</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
         <is>
           <t xml:space="preserve">Actividad de afinidad - Microreunión activación de líderes y referidos </t>
         </is>
@@ -21628,6 +21894,11 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
+          <t>Hamilton Liz (3125621911)</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
           <t xml:space="preserve">Actividad de afinidad - Microreunión activación de líderes y referidos </t>
         </is>
       </c>
@@ -21670,6 +21941,11 @@
         </is>
       </c>
       <c r="J71" t="inlineStr">
+        <is>
+          <t>Mary Preciado</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
         <is>
           <t>Recorrido con vecinos y comerciantes</t>
         </is>
@@ -21699,7 +21975,8 @@
           <t>ALMUERZO</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
         <is>
           <t>ALMUERZO</t>
         </is>
@@ -21743,6 +22020,11 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
+          <t>Isaura Porras</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
           <t>MT - CIUDAD GRANADA FERIA DE EMPLEO (3672) + MT - CIUDAD GRANADA JORNADA DE OPAM (3300)</t>
         </is>
       </c>
@@ -21785,6 +22067,12 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
+          <t>MARIA HERMENCIA SANCHEZ CASTRO
+3212923898</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
           <t>MT - UNIR 1 PARQUE (2763)</t>
         </is>
       </c>
@@ -21823,6 +22111,11 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
+          <t>Hamilton Liz (3125621911)</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
           <t xml:space="preserve">Actividad de afinidad - Microreunión activación de líderes y referidos </t>
         </is>
       </c>
@@ -21865,6 +22158,12 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
+          <t>DAIRO GARCIA CALDERON
+3196422287</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
           <t>MT - SINAI MALLA VIAL DETERIORADA FABRICA RECICLAJE Y SALÓN (2011) +  MT - SINAÍ PARQUE TRANSMILENIO Y EXCRETAS (1788)</t>
         </is>
       </c>
@@ -21907,6 +22206,12 @@
         </is>
       </c>
       <c r="J77" t="inlineStr">
+        <is>
+          <t>Claudia Nieto
+3102215612</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
         <is>
           <t>Reunión de campaña</t>
         </is>
@@ -21936,7 +22241,8 @@
           <t>ALMUERZO</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
         <is>
           <t>ALMUERZO	ALMUERZO</t>
         </is>
@@ -21978,7 +22284,8 @@
           <t>TERRITORIO</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
         <is>
           <t>Reunion de identidad y convicción</t>
         </is>
@@ -22024,6 +22331,14 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
+          <t>- TERESA DE JESUS PORTELA GRISALES
+3153137308
+- LILIANA SICACHÁ
+- LUIS MOYA</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
           <t>MT - CASABLANCA ANDENES Y PARADERO SITP (4620)</t>
         </is>
       </c>
@@ -22064,7 +22379,8 @@
           <t>ESTUDIO BIBLICO</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr">
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
         <is>
           <t xml:space="preserve">Actividad de afinidad - Microreunión activación de líderes y referidos </t>
         </is>
@@ -22108,6 +22424,11 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
+          <t>Ana Elcy</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
           <t>Reunión referidos líder Ana Elsy  Ibarra</t>
         </is>
       </c>
@@ -22150,6 +22471,11 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
+          <t>Lorena Garzón</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
           <t>Reunión líderes Sector Religioso</t>
         </is>
       </c>
@@ -22190,7 +22516,8 @@
           <t>ESTUDIO BIBLICO</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr">
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
         <is>
           <t xml:space="preserve">Actividad de afinidad - Microreunión activación de líderes y referidos </t>
         </is>
@@ -22232,7 +22559,8 @@
           <t>ENSENANZA</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr">
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
         <is>
           <t xml:space="preserve">REUNION CON LIDERES EN EL SEGUNDO PISO DE CARVAJAL, SE VA A INVITAR APROXIMADAMENTE 30 PERSONAS QUE AUN NO SE HAN ACTIVADO COMO LIDERES, QUE NO TIENE REFERIDOS, PARA REALIZAR ACTIVIDAD DENTRO DE LA REUNION, ASI M ISMO SE DARA A CONOCER A LOS CANDIDATOS Y SE REALIZARA PEDAGOGIA ELECTORAL </t>
         </is>
@@ -22276,6 +22604,11 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
+          <t>Sebastian Angel</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
           <t>Turismauro - visita empleados</t>
         </is>
       </c>
@@ -22318,6 +22651,12 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
+          <t xml:space="preserve">Silvia Cabuya
+</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
           <t>MT - LUCERNA PROVIVIENDA OCCIDENTAL HUECO EN LA VIA CIV 8008866 (3271)</t>
         </is>
       </c>
@@ -22358,7 +22697,8 @@
           <t>ENSENANZA</t>
         </is>
       </c>
-      <c r="J88" t="inlineStr">
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
         <is>
           <t xml:space="preserve">REUNION CON LIDERES EN EL SEGUNDO PISO DE CARVAJAL, SE VA A INVITAR APROXIMADAMENTE 30 PERSONAS QUE AUN NO SE HAN ACTIVADO COMO LIDERES, QUE NO TIENE REFERIDOS, PARA REALIZAR ACTIVIDAD DENTRO DE LA REUNION, ASI M ISMO SE DARA A CONOCER A LOS CANDIDATOS Y SE REALIZARA PEDAGOGIA ELECTORAL </t>
         </is>
@@ -22388,7 +22728,8 @@
           <t>TERRITORIO</t>
         </is>
       </c>
-      <c r="J89" t="inlineStr">
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
         <is>
           <t>REPROGRAMAR LA ACTIVIDAD DE CORABASTOS</t>
         </is>
@@ -22432,6 +22773,12 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
+          <t>MERCEDES LAVERDE
+3208267021</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
           <t>MT - TINTALITO PUNTO DE ARROJO (3691)</t>
         </is>
       </c>
@@ -22468,7 +22815,8 @@
           <t>TERRITORIO</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr">
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
         <is>
           <t>Reunión Corabastos</t>
         </is>
@@ -22498,7 +22846,8 @@
           <t>ENSENANZA</t>
         </is>
       </c>
-      <c r="J92" t="inlineStr">
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
         <is>
           <t xml:space="preserve">Actividad de afinidad - Microreunión activación de líderes y referidos </t>
         </is>
@@ -22540,7 +22889,8 @@
           <t>ALABANZA</t>
         </is>
       </c>
-      <c r="J93" t="inlineStr">
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
         <is>
           <t xml:space="preserve">Actividad de afinidad - activación de líderes y referidos:
 REUNION CON LIDERES EN EL SEGUNDO PISO DE CARVAJAL, SE VA A INVITAR APROXIMADAMENTE 30 PERSONAS QUE AUN NO SE HAN ACTIVADO COMO LIDERES, QUE NO TIENE REFERIDOS, PARA REALIZAR ACTIVIDAD DENTRO DE LA REUNION, ASI M ISMO SE DARA A CONOCER A LOS CANDIDATOS Y SE REALIZARA PEDAGOGIA ELECTORAL </t>
@@ -22584,6 +22934,12 @@
         </is>
       </c>
       <c r="J94" t="inlineStr">
+        <is>
+          <t>Wilson Gonzalez
+(3142772157</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
         <is>
           <t xml:space="preserve">Reunion empresa Industrias Fagor </t>
         </is>
@@ -22613,7 +22969,8 @@
           <t>ALMUERZO</t>
         </is>
       </c>
-      <c r="J95" t="inlineStr">
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
         <is>
           <t>ALMUERZO</t>
         </is>
@@ -22657,6 +23014,11 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
+          <t>Carolina montañez y sandra montañez( 3134235526)</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
           <t xml:space="preserve">Recorrido negocios Carolina </t>
         </is>
       </c>
@@ -22699,6 +23061,12 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
+          <t>Betzabe Soto
+‪3134295319‬</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
           <t>Reunión con familia y vecinos</t>
         </is>
       </c>
@@ -22739,7 +23107,8 @@
           <t>ALABANZA</t>
         </is>
       </c>
-      <c r="J98" t="inlineStr">
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
         <is>
           <t xml:space="preserve">Actividad de afinidad - activación de líderes y referidos:
 REUNION CON LIDERES EN EL SEGUNDO PISO DE CARVAJAL, SE VA A INVITAR APROXIMADAMENTE 30 PERSONAS QUE AUN NO SE HAN ACTIVADO COMO LIDERES, QUE NO TIENE REFERIDOS, PARA REALIZAR ACTIVIDAD DENTRO DE LA REUNION, ASI M ISMO SE DARA A CONOCER A LOS CANDIDATOS Y SE REALIZARA PEDAGOGIA ELECTORAL </t>
@@ -22770,7 +23139,8 @@
           <t>ENSENANZA</t>
         </is>
       </c>
-      <c r="J99" t="inlineStr">
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
         <is>
           <t xml:space="preserve">Actividad de afinidad - Microreunión activación de líderes y referidos </t>
         </is>
@@ -22813,6 +23183,14 @@
         </is>
       </c>
       <c r="J100" t="inlineStr">
+        <is>
+          <t>NILCE SALGADO CALVO
+3202012650
+CLARA MERCEDES LUMPAQUE ESTRADA
+3058167240</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
         <is>
           <t>Recorrido comerciantes Britalia</t>
         </is>
@@ -22842,7 +23220,8 @@
           <t>ALMUERZO</t>
         </is>
       </c>
-      <c r="J101" t="inlineStr">
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
         <is>
           <t>ALMUERZO</t>
         </is>
@@ -22886,6 +23265,11 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
+          <t>Nidia Peréz y Maximino Leal</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
           <t>Reunión amigos y familiares líderes Maximino y Nidia Perez</t>
         </is>
       </c>
@@ -22928,6 +23312,11 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
+          <t>Zamudio</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
           <t>Reunión con familia y vecinos Parqueadero líderes Zamudio</t>
         </is>
       </c>
@@ -22969,6 +23358,11 @@
         </is>
       </c>
       <c r="J104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Luis Gonzales </t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
         <is>
           <t xml:space="preserve">Reunión amigos y familiares líder Luis Gonzales </t>
         </is>
@@ -22998,7 +23392,8 @@
           <t>ENSENANZA</t>
         </is>
       </c>
-      <c r="J105" t="inlineStr">
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
         <is>
           <t xml:space="preserve">Actividad de afinidad - Microreunión activación de líderes y referidos </t>
         </is>
@@ -23042,6 +23437,11 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
+          <t>Erik Mejía</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
           <t>Reunion con referidos líder Erik Mejía</t>
         </is>
       </c>
@@ -23085,6 +23485,11 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sara Nobsa </t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
           <t>Reunion con referidos líder Sara Nobsa - Carvajal</t>
         </is>
       </c>
@@ -23126,6 +23531,11 @@
         </is>
       </c>
       <c r="J108" t="inlineStr">
+        <is>
+          <t>Aleyda Triana</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
         <is>
           <t>Recorrido Castilla Líder Aleyda</t>
         </is>
@@ -23155,7 +23565,8 @@
           <t>ALMUERZO</t>
         </is>
       </c>
-      <c r="J109" t="inlineStr">
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
         <is>
           <t>ALMUERZO</t>
         </is>
@@ -23194,6 +23605,11 @@
         </is>
       </c>
       <c r="J110" t="inlineStr">
+        <is>
+          <t>Gilma Perez</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
         <is>
           <t>Reunion con referidos hermana Gilma - Carvajal</t>
         </is>
@@ -23228,6 +23644,7 @@
         </is>
       </c>
       <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -23258,6 +23675,7 @@
         </is>
       </c>
       <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -23288,6 +23706,7 @@
         </is>
       </c>
       <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -23318,6 +23737,7 @@
         </is>
       </c>
       <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -23357,6 +23777,11 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
+          <t>Jenny García (DP)</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
           <t>Microreunión con hermanos menos 10 referi</t>
         </is>
       </c>
@@ -23399,6 +23824,11 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
+          <t>Sergio Osorio (DP)</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
           <t xml:space="preserve">Microreunión </t>
         </is>
       </c>
@@ -23439,7 +23869,8 @@
           <t>MICROREUNION</t>
         </is>
       </c>
-      <c r="J117" t="inlineStr">
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
         <is>
           <t xml:space="preserve">Microreunión </t>
         </is>
@@ -23483,6 +23914,11 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
+          <t>Sergio Osorio (DP)</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
           <t xml:space="preserve">Microreunión </t>
         </is>
       </c>
@@ -23525,6 +23961,11 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
+          <t>Hamilton Liz (DP)</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
           <t xml:space="preserve">Microreunión </t>
         </is>
       </c>
@@ -23567,6 +24008,11 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
+          <t>Jenny García (DP)</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
           <t xml:space="preserve">Microreunión </t>
         </is>
       </c>
@@ -23603,7 +24049,8 @@
           <t>MICROREUNION</t>
         </is>
       </c>
-      <c r="J121" t="inlineStr">
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
         <is>
           <t xml:space="preserve">Microreunión </t>
         </is>
@@ -23633,7 +24080,8 @@
           <t>MICROREUNION</t>
         </is>
       </c>
-      <c r="J122" t="inlineStr">
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
         <is>
           <t xml:space="preserve">Microreunión </t>
         </is>
@@ -23663,7 +24111,8 @@
           <t>MICROREUNION</t>
         </is>
       </c>
-      <c r="J123" t="inlineStr">
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
         <is>
           <t xml:space="preserve">Microreunión </t>
         </is>
@@ -23693,7 +24142,8 @@
           <t>MICROREUNION</t>
         </is>
       </c>
-      <c r="J124" t="inlineStr">
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
         <is>
           <t xml:space="preserve">Microreunión </t>
         </is>
@@ -23723,7 +24173,8 @@
           <t>MICROREUNION</t>
         </is>
       </c>
-      <c r="J125" t="inlineStr">
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
         <is>
           <t xml:space="preserve">Microreunión </t>
         </is>
@@ -23765,7 +24216,8 @@
           <t>MICROREUNION</t>
         </is>
       </c>
-      <c r="J126" t="inlineStr">
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
         <is>
           <t xml:space="preserve">Microreunión </t>
         </is>
@@ -23795,7 +24247,8 @@
           <t>MICROREUNION</t>
         </is>
       </c>
-      <c r="J127" t="inlineStr">
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
         <is>
           <t xml:space="preserve">Microreunión </t>
         </is>
@@ -23839,6 +24292,11 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
+          <t>Ana Temilda Guerrero</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
           <t>Volanteo Ciudadela Primavera</t>
         </is>
       </c>
@@ -23881,6 +24339,11 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
+          <t>Bryan Rodriguez</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
           <t>Volanteo zona Roma</t>
         </is>
       </c>
@@ -23923,6 +24386,12 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
+          <t>Andrés Caicedo
+Carmen Garzón</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
           <t>Volanteo Parque Maracaná</t>
         </is>
       </c>
@@ -23965,6 +24434,11 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
+          <t>Olga Saenz</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
           <t>Volanteo arreglo vía Corabastos</t>
         </is>
       </c>
@@ -24007,6 +24481,13 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
+          <t>Liliana Sicacha
+Teresa Portela 
+Luis Moya</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
           <t>Volanteo de la gestión en la zona de Casablanca</t>
         </is>
       </c>
@@ -24049,6 +24530,11 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
+          <t>Paula Coronado</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
           <t>Volanteo de la gestión en la zona de Ciudad Granada y Los Almendros</t>
         </is>
       </c>
@@ -24091,6 +24577,11 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
+          <t>Sandra</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
           <t>Volanteo de la gestión en la zona de Pastranita 2 sector</t>
         </is>
       </c>
@@ -24133,6 +24624,11 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
+          <t>Jimmy</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
           <t>Volanteo de la gestión en la zona de Villa Andriana y Villa Claudia</t>
         </is>
       </c>
@@ -24175,6 +24671,11 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
+          <t>Jenny García</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
           <t>Volanteo Kennedy Central</t>
         </is>
       </c>
@@ -24216,6 +24717,11 @@
         </is>
       </c>
       <c r="J137" t="inlineStr">
+        <is>
+          <t>Samyr</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
         <is>
           <t>Volanteo Villa Hermosa</t>
         </is>
@@ -24246,6 +24752,7 @@
         </is>
       </c>
       <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -24284,6 +24791,11 @@
         </is>
       </c>
       <c r="J139" t="inlineStr">
+        <is>
+          <t>Gloria</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
         <is>
           <t>Volanteo Americas Occidental</t>
         </is>
@@ -24313,7 +24825,8 @@
           <t>VOLANTEO</t>
         </is>
       </c>
-      <c r="J140" t="inlineStr">
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
         <is>
           <t>Volanteo Margaritas - Parque las Margaritas etapa 1</t>
         </is>
@@ -24357,6 +24870,11 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
+          <t>Silvia Cabuya</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
           <t>Volanteo Lucerna</t>
         </is>
       </c>
@@ -24398,6 +24916,11 @@
         </is>
       </c>
       <c r="J142" t="inlineStr">
+        <is>
+          <t>Franz</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
         <is>
           <t>Volanteo Américas Occidental</t>
         </is>
@@ -24427,7 +24950,8 @@
           <t>VOLANTEO</t>
         </is>
       </c>
-      <c r="J143" t="inlineStr">
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
         <is>
           <t>Volanteo logros generales</t>
         </is>
@@ -24457,7 +24981,8 @@
           <t>VOLANTEO</t>
         </is>
       </c>
-      <c r="J144" t="inlineStr">
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
         <is>
           <t>Volanteo logros generales</t>
         </is>
@@ -24501,6 +25026,11 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
+          <t>Mercedes Laverde</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
           <t>Volanteo Dintalito</t>
         </is>
       </c>
@@ -24542,6 +25072,11 @@
         </is>
       </c>
       <c r="J146" t="inlineStr">
+        <is>
+          <t>Luz Elena Garzón</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
         <is>
           <t>Volanteo Tintal</t>
         </is>
@@ -24571,7 +25106,8 @@
           <t>VOLANTEO</t>
         </is>
       </c>
-      <c r="J147" t="inlineStr">
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
         <is>
           <t>Volanteo Portal de Cali - Milenio Plaza</t>
         </is>
@@ -24601,7 +25137,8 @@
           <t>VOLANTEO</t>
         </is>
       </c>
-      <c r="J148" t="inlineStr">
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
         <is>
           <t>Volanteo Castilla</t>
         </is>
@@ -24631,7 +25168,8 @@
           <t>VOLANTEO</t>
         </is>
       </c>
-      <c r="J149" t="inlineStr">
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
         <is>
           <t>Volanteo logros generales</t>
         </is>
@@ -24661,7 +25199,8 @@
           <t>VOLANTEO</t>
         </is>
       </c>
-      <c r="J150" t="inlineStr">
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
         <is>
           <t>Volanteo logros generales</t>
         </is>
@@ -24691,7 +25230,8 @@
           <t>VOLANTEO</t>
         </is>
       </c>
-      <c r="J151" t="inlineStr">
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
         <is>
           <t>Volanteo logros generales</t>
         </is>
@@ -24721,7 +25261,8 @@
           <t>VOLANTEO</t>
         </is>
       </c>
-      <c r="J152" t="inlineStr">
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
         <is>
           <t>Volanteo Castilla</t>
         </is>
@@ -24764,6 +25305,11 @@
         </is>
       </c>
       <c r="J153" t="inlineStr">
+        <is>
+          <t>Sergio Osorio</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
         <is>
           <t>Volanteo Carvajal</t>
         </is>
@@ -24794,6 +25340,7 @@
         </is>
       </c>
       <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -24820,6 +25367,7 @@
         </is>
       </c>
       <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -24846,6 +25394,7 @@
         </is>
       </c>
       <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -24872,6 +25421,7 @@
         </is>
       </c>
       <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -24898,6 +25448,7 @@
         </is>
       </c>
       <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -24924,6 +25475,7 @@
         </is>
       </c>
       <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -24950,6 +25502,7 @@
         </is>
       </c>
       <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -24976,6 +25529,7 @@
         </is>
       </c>
       <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -25002,6 +25556,7 @@
         </is>
       </c>
       <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -25028,6 +25583,7 @@
         </is>
       </c>
       <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -25054,6 +25610,7 @@
         </is>
       </c>
       <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -25080,6 +25637,7 @@
         </is>
       </c>
       <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -25106,6 +25664,7 @@
         </is>
       </c>
       <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -25132,6 +25691,7 @@
         </is>
       </c>
       <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -25158,6 +25718,7 @@
         </is>
       </c>
       <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -25184,6 +25745,7 @@
         </is>
       </c>
       <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -25210,6 +25772,7 @@
         </is>
       </c>
       <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -25236,6 +25799,7 @@
         </is>
       </c>
       <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -25273,7 +25837,8 @@
           <t>ENSENANZA</t>
         </is>
       </c>
-      <c r="J172" t="inlineStr">
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
         <is>
           <t xml:space="preserve">Punto de InfoMIRA PI -  activación de líderes y referidos </t>
         </is>
@@ -25315,7 +25880,8 @@
           <t>ENSENANZA</t>
         </is>
       </c>
-      <c r="J173" t="inlineStr">
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
         <is>
           <t xml:space="preserve">Punto de InfoMIRA PI -  activación de líderes y referidos </t>
         </is>
@@ -25357,7 +25923,8 @@
           <t>ALABANZA</t>
         </is>
       </c>
-      <c r="J174" t="inlineStr">
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
         <is>
           <t xml:space="preserve">Punto de InfoMIRA PI -  activación de líderes y referidos </t>
         </is>
@@ -25399,7 +25966,8 @@
           <t>ALABANZA</t>
         </is>
       </c>
-      <c r="J175" t="inlineStr">
+      <c r="J175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
         <is>
           <t xml:space="preserve">Punto de InfoMIRA PI -  activación de líderes y referidos </t>
         </is>
@@ -25441,7 +26009,8 @@
           <t>ALABANZA</t>
         </is>
       </c>
-      <c r="J176" t="inlineStr">
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
         <is>
           <t xml:space="preserve">Punto de InfoMIRA PI -  activación de líderes y referidos </t>
         </is>
@@ -25483,7 +26052,8 @@
           <t>ENSENANZA</t>
         </is>
       </c>
-      <c r="J177" t="inlineStr">
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
         <is>
           <t>Punto de InfoMIRA PI y Microreunión Focalizada MRF
 MRF: Líderes activos, con 0 referidos activos, pero con referidos inactivos.</t>
@@ -25527,6 +26097,12 @@
         </is>
       </c>
       <c r="J178" t="inlineStr">
+        <is>
+          <t>ORLANDO MARULANDA LEON
+3045831717</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
         <is>
           <t>MT - CIUDAD DE CALI AFECTACIÓN POR SEMÁFORO (5109)</t>
         </is>
@@ -25556,7 +26132,8 @@
           <t>ALMUERZO</t>
         </is>
       </c>
-      <c r="J179" t="inlineStr">
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
         <is>
           <t>ALMUERZO	ALMUERZO</t>
         </is>
@@ -25601,6 +26178,12 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
+          <t>MIGUEL ADRIEL GUERRERO SANCHEZ
+3214929228</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
           <t>MT - CIUDAD KENNEDY OCCIDENTAL INSEGURIDAD POR RETIRO DE REJAS DE INGRESO (6236</t>
         </is>
       </c>
@@ -25643,6 +26226,13 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
+          <t xml:space="preserve">NUBIA LILIANA PARRA GUERRERO
+3202930363
+</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
           <t>MT - JORNADA OPAM PARQUE HOLANDA (6172)</t>
         </is>
       </c>
@@ -25683,7 +26273,8 @@
           <t>ENSENANZA</t>
         </is>
       </c>
-      <c r="J182" t="inlineStr">
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
         <is>
           <t>Punto de InfoMIRA PI y Microreunión Focalizada MRF
 MRF: Líderes activos, con 0 referidos activos, pero con referidos inactivos.</t>
@@ -25726,7 +26317,8 @@
           <t>ENSENANZA</t>
         </is>
       </c>
-      <c r="J183" t="inlineStr">
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
         <is>
           <t>Punto de InfoMIRA PI y Microreunión Focalizada MRF
 MRF: Líderes activos, con 0 referidos activos, pero con referidos inactivos.</t>
@@ -25769,7 +26361,8 @@
           <t>ENSENANZA</t>
         </is>
       </c>
-      <c r="J184" t="inlineStr">
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
         <is>
           <t>Punto de InfoMIRA PI y Microreunión Focalizada MRF
 MRF: Líderes activos, con 0 referidos activos, pero con referidos inactivos.</t>
@@ -25812,7 +26405,8 @@
           <t>ENSENANZA</t>
         </is>
       </c>
-      <c r="J185" t="inlineStr">
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
         <is>
           <t>Punto de InfoMIRA PI y Microreunión Focalizada MRF
 MRF: Líderes activos, con 0 referidos activos, pero con referidos inactivos.</t>
@@ -25855,7 +26449,8 @@
           <t>ENSENANZA</t>
         </is>
       </c>
-      <c r="J186" t="inlineStr">
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
         <is>
           <t xml:space="preserve">Punto de InfoMIRA PI -  activación de líderes y referidos </t>
         </is>
@@ -25897,7 +26492,8 @@
           <t>ENSENANZA</t>
         </is>
       </c>
-      <c r="J187" t="inlineStr">
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
         <is>
           <t>Punto de InfoMIRA PI y Microreunión Focalizada MRF
 MRF: Líderes inactivos, inscritos como testigos</t>
@@ -25940,7 +26536,8 @@
           <t>ENSENANZA</t>
         </is>
       </c>
-      <c r="J188" t="inlineStr">
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
         <is>
           <t>Punto de InfoMIRA PI y Microreunión Focalizada MRF
 MRF: Líderes inactivos, inscritos como testigos</t>
@@ -25983,7 +26580,8 @@
           <t>ENSENANZA</t>
         </is>
       </c>
-      <c r="J189" t="inlineStr">
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
         <is>
           <t xml:space="preserve">Punto de InfoMIRA PI -  activación de líderes y referidos </t>
         </is>
@@ -26025,7 +26623,8 @@
           <t>ENSENANZA</t>
         </is>
       </c>
-      <c r="J190" t="inlineStr">
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
         <is>
           <t xml:space="preserve">Punto de InfoMIRA PI -  activación de líderes y referidos </t>
         </is>
@@ -26067,7 +26666,8 @@
           <t>ENSENANZA</t>
         </is>
       </c>
-      <c r="J191" t="inlineStr">
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
         <is>
           <t xml:space="preserve">Punto de InfoMIRA PI -  activación de líderes y referidos </t>
         </is>
@@ -26109,7 +26709,8 @@
           <t>ENSENANZA</t>
         </is>
       </c>
-      <c r="J192" t="inlineStr">
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
         <is>
           <t>Punto de InfoMIRA PI y Microreunión Focalizada MRF
 MRF: Hermanos que apoyan labores en la iglesia</t>
@@ -26152,7 +26753,8 @@
           <t>ENSENANZA</t>
         </is>
       </c>
-      <c r="J193" t="inlineStr">
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
         <is>
           <t>Punto de InfoMIRA PI y Microreunión Focalizada MRF
 MRF: Hermanos que apoyan labores en la iglesia</t>
@@ -26195,7 +26797,8 @@
           <t>ENSENANZA</t>
         </is>
       </c>
-      <c r="J194" t="inlineStr">
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
         <is>
           <t>Punto de InfoMIRA PI y Microreunión Focalizada MRF
 MRF: Hermanos que apoyan labores en la iglesia</t>
@@ -26238,7 +26841,8 @@
           <t>ENSENANZA</t>
         </is>
       </c>
-      <c r="J195" t="inlineStr">
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
         <is>
           <t>Punto de InfoMIRA PI y Microreunión Focalizada MRF
 MRF: Entre 1 y 4 referidos activos, con referidos inactivos.</t>
@@ -26281,7 +26885,8 @@
           <t>ENSENANZA</t>
         </is>
       </c>
-      <c r="J196" t="inlineStr">
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
         <is>
           <t>Punto de InfoMIRA PI y Microreunión Focalizada MRF
 MRF: Entre 1 y 4 referidos activos, con referidos inactivos.</t>
@@ -26324,7 +26929,8 @@
           <t>ENSENANZA</t>
         </is>
       </c>
-      <c r="J197" t="inlineStr">
+      <c r="J197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
         <is>
           <t>Punto de InfoMIRA PI y Microreunión Focalizada MRF
 MRF: Entre 1 y 4 referidos activos, con referidos inactivos.</t>
@@ -26367,7 +26973,8 @@
           <t>ENSENANZA</t>
         </is>
       </c>
-      <c r="J198" t="inlineStr">
+      <c r="J198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
         <is>
           <t>Punto de InfoMIRA PI y Microreunión Focalizada MRF
 MRF: Entre 1 y 4 referidos activos, con referidos inactivos.</t>
@@ -26410,7 +27017,8 @@
           <t>ENSENANZA</t>
         </is>
       </c>
-      <c r="J199" t="inlineStr">
+      <c r="J199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
         <is>
           <t>Punto de InfoMIRA PI y Microreunión Focalizada MRF
 MRF: Entre 1 y 4 referidos activos, con referidos inactivos.</t>
@@ -26453,7 +27061,8 @@
           <t>ENSENANZA</t>
         </is>
       </c>
-      <c r="J200" t="inlineStr">
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
         <is>
           <t xml:space="preserve">Punto de InfoMIRA PI -  activación de líderes y referidos </t>
         </is>
@@ -26495,7 +27104,8 @@
           <t>VOLANTEO</t>
         </is>
       </c>
-      <c r="J201" t="inlineStr">
+      <c r="J201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
         <is>
           <t>Volanteo arreglo vía Corabastos</t>
         </is>
@@ -26539,6 +27149,13 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
+          <t>Liliana Sicacha
+Teresa Portela 
+Luis Moya</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
           <t>Volanteo de la gestión en la zona de Casablanca</t>
         </is>
       </c>
@@ -26579,7 +27196,8 @@
           <t>ENSENANZA</t>
         </is>
       </c>
-      <c r="J203" t="inlineStr">
+      <c r="J203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
         <is>
           <t>Punto de InfoMIRA PI y Microreunión Focalizada MRF
 MRF: Entre 5 y 9 referidos activos, con referidos inactivos.</t>
@@ -26622,7 +27240,8 @@
           <t>ENSENANZA</t>
         </is>
       </c>
-      <c r="J204" t="inlineStr">
+      <c r="J204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
         <is>
           <t>Punto de InfoMIRA PI y Microreunión Focalizada MRF
 MRF: Entre 5 y 9 referidos activos, con referidos inactivos.</t>
@@ -26665,7 +27284,8 @@
           <t>ALABANZA</t>
         </is>
       </c>
-      <c r="J205" t="inlineStr">
+      <c r="J205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
         <is>
           <t>Punto de InfoMIRA PI y Microreunión Focalizada MRF
 MRF: Líderes Activos, con 0 referidos activos e inactivos</t>
@@ -26708,7 +27328,8 @@
           <t>ALABANZA</t>
         </is>
       </c>
-      <c r="J206" t="inlineStr">
+      <c r="J206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
         <is>
           <t>Punto de InfoMIRA PI y Microreunión Focalizada MRF
 MRF: Líderes Activos, con 0 referidos activos e inactivos</t>
@@ -26751,7 +27372,8 @@
           <t>ALABANZA</t>
         </is>
       </c>
-      <c r="J207" t="inlineStr">
+      <c r="J207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
         <is>
           <t>Punto de InfoMIRA PI y Microreunión Focalizada MRF
 MRF: Líderes Activos, con 0 referidos activos e inactivos</t>
@@ -26794,7 +27416,8 @@
           <t>ALABANZA</t>
         </is>
       </c>
-      <c r="J208" t="inlineStr">
+      <c r="J208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
         <is>
           <t>Punto de InfoMIRA PI y Microreunión Focalizada MRF
 MRF: Líderes Activos, con 0 referidos activos e inactivos</t>
@@ -26837,7 +27460,8 @@
           <t>ALABANZA</t>
         </is>
       </c>
-      <c r="J209" t="inlineStr">
+      <c r="J209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
         <is>
           <t>Punto de InfoMIRA PI y Microreunión Focalizada MRF
 MRF: Líderes Activos, con 0 referidos activos e inactivos</t>
@@ -26880,7 +27504,8 @@
           <t>ALABANZA</t>
         </is>
       </c>
-      <c r="J210" t="inlineStr">
+      <c r="J210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
         <is>
           <t>Punto de InfoMIRA PI y Microreunión Focalizada MRF
 MRF: Líderes Activos, con 0 referidos activos e inactivos</t>
@@ -26925,6 +27550,11 @@
       </c>
       <c r="J211" t="inlineStr">
         <is>
+          <t>Jenny García</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
           <t>Volanteo Kennedy Central</t>
         </is>
       </c>
@@ -26965,7 +27595,8 @@
           <t>ENSENANZA</t>
         </is>
       </c>
-      <c r="J212" t="inlineStr">
+      <c r="J212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
         <is>
           <t>Punto de InfoMIRA PI y Microreunión Focalizada MRF
 MRF: Líderes Activos, con 0 referidos activos e inactivos</t>
@@ -27008,7 +27639,8 @@
           <t>ENSENANZA</t>
         </is>
       </c>
-      <c r="J213" t="inlineStr">
+      <c r="J213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
         <is>
           <t>Punto de InfoMIRA PI y Microreunión Focalizada MRF
 MRF: Líderes Activos, con 0 referidos activos e inactivos</t>
@@ -27051,7 +27683,8 @@
           <t>ENSENANZA</t>
         </is>
       </c>
-      <c r="J214" t="inlineStr">
+      <c r="J214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
         <is>
           <t>Punto de InfoMIRA PI y Microreunión Focalizada MRF
 MRF: Líderes Activos, con 0 referidos activos e inactivos</t>
@@ -27094,7 +27727,8 @@
           <t>ENSENANZA</t>
         </is>
       </c>
-      <c r="J215" t="inlineStr">
+      <c r="J215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
         <is>
           <t>Punto de InfoMIRA PI y Microreunión Focalizada MRF
 MRF: Líderes Activos, con 0 referidos activos e inactivos</t>
@@ -27137,7 +27771,8 @@
           <t>ENSENANZA</t>
         </is>
       </c>
-      <c r="J216" t="inlineStr">
+      <c r="J216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
         <is>
           <t>Punto de InfoMIRA PI y Microreunión Focalizada MRF
 MRF: Líderes Activos, con 0 referidos activos e inactivos</t>
@@ -27180,7 +27815,8 @@
           <t>ENSENANZA</t>
         </is>
       </c>
-      <c r="J217" t="inlineStr">
+      <c r="J217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
         <is>
           <t>Punto de InfoMIRA PI y Microreunión Focalizada MRF
 MRF: Líderes Activos, con 0 referidos activos e inactivos</t>
@@ -27225,6 +27861,12 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
+          <t>DAIRO GARCIA CALDERON
+3196422287</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
           <t>MT - SINAI MALLA VIAL DETERIORADA FABRICA RECICLAJE Y SALÓN (2011) +  MT - SINAÍ PARQUE TRANSMILENIO Y EXCRETAS (1788)</t>
         </is>
       </c>
@@ -27266,6 +27908,14 @@
         </is>
       </c>
       <c r="J219" t="inlineStr">
+        <is>
+          <t>NILCE SALGADO CALVO
+3202012650
+CLARA MERCEDES LUMPAQUE ESTRADA
+3058167240</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
         <is>
           <t>MT - GRAN BRITALIA CAMBIO SENTIDO VIAL (2013) + MT - PARQUE URBANIZACION GRAN BRITALIA MALLA Y GRADAS (6909)</t>
         </is>
@@ -27295,7 +27945,8 @@
           <t>ALMUERZO</t>
         </is>
       </c>
-      <c r="J220" t="inlineStr">
+      <c r="J220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
         <is>
           <t>ALMUERZO	ALMUERZO</t>
         </is>
@@ -27339,6 +27990,14 @@
       </c>
       <c r="J221" t="inlineStr">
         <is>
+          <t>- TERESA DE JESUS PORTELA GRISALES
+3153137308
+- LILIANA SICACHÁ
+- LUIS MOYA</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
           <t>MT - CASABLANCA ANDENES Y PARADERO SITP (4620)</t>
         </is>
       </c>
@@ -27381,6 +28040,12 @@
         </is>
       </c>
       <c r="J222" t="inlineStr">
+        <is>
+          <t>Claudia Nieto
+3102215612</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
         <is>
           <t>Reunión de campaña</t>
         </is>
@@ -27397,7 +28062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L255"/>
+  <dimension ref="A1:M255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27453,10 +28118,15 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
+          <t>LIDER</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>ESTADO</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>OBSERVACIONES</t>
         </is>
@@ -27499,10 +28169,15 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
+          <t>SIRLEY ANDREA FANDIÑO LOPEZ</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -27543,10 +28218,15 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
+          <t>EUTALIA LATORRE ROCHA</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -27587,10 +28267,15 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
+          <t>ANGIE LORENA GARZON DEAZA</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -27631,10 +28316,15 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
+          <t>JUAN SEBASTIAN MARQUEZ SANCHEZ</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -27675,10 +28365,15 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
+          <t>FERNANDO JOSE ZAMORA CAMACHO</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -27719,10 +28414,15 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
+          <t>RUBY MARITHZA CALLEJAS APONTE</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -27759,10 +28459,15 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
+          <t>ERICK EDUARDO MERCADO LOBO</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -27803,10 +28508,15 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
+          <t>CLARA MERCEDES LUMPAQUE ESTRADA</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -27847,10 +28557,15 @@
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
+          <t>CHEPE PINILLA GUTIERRES</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -27891,10 +28606,15 @@
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
+          <t>DIANA LUCIA REAL MARROQUIN</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -27935,10 +28655,15 @@
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
+          <t>ANGELICA MARIA MUNERA GONZALEZ</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>1</v>
       </c>
     </row>
@@ -27979,10 +28704,15 @@
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
+          <t>MARTHA JOSEFINA GARCIA AVILA</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -28023,10 +28753,15 @@
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
+          <t>ANA EULALIA BECERRA RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -28063,10 +28798,15 @@
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
+          <t>MIGUEL ADRIEL GUERRERO SANCHEZ</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>2</v>
       </c>
     </row>
@@ -28107,10 +28847,15 @@
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
+          <t>LEIDY MARCELA NEIRA ARIAS</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>3</v>
       </c>
     </row>
@@ -28151,10 +28896,15 @@
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
+          <t>NUBIA LILIANA PARRA GUERRERO</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -28191,10 +28941,15 @@
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
+          <t>MAGALY GONZALEZ TIQUE</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>2</v>
       </c>
     </row>
@@ -28231,10 +28986,15 @@
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
+          <t>CARMEN ROSA PITO</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>1</v>
       </c>
     </row>
@@ -28271,10 +29031,15 @@
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
+          <t>YOSSEF ANDREY ACERO</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -28315,10 +29080,15 @@
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
+          <t>MARIA FANNY CONTRERAS RIAÑO</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>2</v>
       </c>
     </row>
@@ -28359,10 +29129,15 @@
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
+          <t>FERNANDO JOSE ZAMORA CAMACHO</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>1</v>
       </c>
     </row>
@@ -28403,10 +29178,15 @@
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
+          <t>GESSICA NATALIA BARRERO MOSCOSO</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>1</v>
       </c>
     </row>
@@ -28443,10 +29223,15 @@
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
+          <t>SERGIO YOUSEFF OSORIO INFANTE</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>1</v>
       </c>
     </row>
@@ -28487,10 +29272,15 @@
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
+          <t>HERNAN FRANCISCO MONTES</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" t="n">
         <v>2</v>
       </c>
     </row>
@@ -28531,10 +29321,15 @@
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
+          <t>TERESA DE JESUS PORTELA GRISALES</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -28575,10 +29370,15 @@
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
+          <t>JIMMY ALEXANDER GUTIERREZ SARMIENTO</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" t="n">
         <v>1</v>
       </c>
     </row>
@@ -28619,10 +29419,15 @@
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
+          <t>OLGA LUCIA SAENZ GOMEZ</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
         <v>1</v>
       </c>
     </row>
@@ -28663,10 +29468,15 @@
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
+          <t>FERNANDO JOSE ZAMORA CAMACHO</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
         <v>2</v>
       </c>
     </row>
@@ -28707,10 +29517,15 @@
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
+          <t>LETICIA ROA ZAMBRANO</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L30" t="n">
+      <c r="M30" t="n">
         <v>1</v>
       </c>
     </row>
@@ -28747,10 +29562,15 @@
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
+          <t>DIEGO ANDRÉS ROJAS PINTO</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L31" t="n">
+      <c r="M31" t="n">
         <v>1</v>
       </c>
     </row>
@@ -28791,10 +29611,15 @@
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
+          <t>JULIANA LIZETH REINA JARA</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L32" t="n">
+      <c r="M32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -28835,10 +29660,15 @@
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
+          <t>JHOANA MILENA CARDENAS PAEZ</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L33" t="n">
+      <c r="M33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -28875,10 +29705,15 @@
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
+          <t>ERICK EDUARDO MERCADO LOBO</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L34" t="n">
+      <c r="M34" t="n">
         <v>1</v>
       </c>
     </row>
@@ -28919,10 +29754,15 @@
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
+          <t>MARIA ELIZABETH NARVAEZ GARZON</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L35" t="n">
+      <c r="M35" t="n">
         <v>2</v>
       </c>
     </row>
@@ -28963,10 +29803,15 @@
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
+          <t>LUCIA EISINENA CABEZAS</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L36" t="n">
+      <c r="M36" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29007,10 +29852,15 @@
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
+          <t>ORLANDO MARULANDA LEON</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L37" t="n">
+      <c r="M37" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29051,10 +29901,15 @@
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
+          <t>FERNANDO JOSE ZAMORA CAMACHO</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L38" t="n">
+      <c r="M38" t="n">
         <v>2</v>
       </c>
     </row>
@@ -29095,10 +29950,15 @@
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
+          <t>OLGA LUCIA SAENZ GOMEZ</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L39" t="n">
+      <c r="M39" t="n">
         <v>3</v>
       </c>
     </row>
@@ -29139,10 +29999,15 @@
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
+          <t>SANDRA MILENA MONROY</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L40" t="n">
+      <c r="M40" t="n">
         <v>8</v>
       </c>
     </row>
@@ -29183,10 +30048,15 @@
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
+          <t>TERESA DE JESUS PORTELA GRISALES</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L41" t="n">
+      <c r="M41" t="n">
         <v>4</v>
       </c>
     </row>
@@ -29227,10 +30097,15 @@
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
+          <t>ANGIE LORENA GARZON DEAZA</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L42" t="n">
+      <c r="M42" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29271,10 +30146,15 @@
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
+          <t>LAURA MELISSA FORERO ESTRADA</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L43" t="n">
+      <c r="M43" t="n">
         <v>4</v>
       </c>
     </row>
@@ -29315,10 +30195,15 @@
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
+          <t>MARLEY YESENIA CORTES AVILA</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L44" t="n">
+      <c r="M44" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29359,10 +30244,15 @@
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
+          <t>STEVE LOPEZ OJEDA</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L45" t="n">
+      <c r="M45" t="n">
         <v>5</v>
       </c>
     </row>
@@ -29403,10 +30293,15 @@
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
+          <t>MARIA DEL TRANSITO MORA ROMERO</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L46" t="n">
+      <c r="M46" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29443,10 +30338,15 @@
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
+          <t>RAFAEL GUTIERREZ</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L47" t="n">
+      <c r="M47" t="n">
         <v>6</v>
       </c>
     </row>
@@ -29487,10 +30387,15 @@
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
+          <t>JHONNY ANDRES BOSSA BERMUDEZ</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L48" t="n">
+      <c r="M48" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29531,10 +30436,15 @@
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
+          <t>ANGIE LORENA GARZON DEAZA</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L49" t="n">
+      <c r="M49" t="n">
         <v>4</v>
       </c>
     </row>
@@ -29575,10 +30485,15 @@
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
+          <t>ANGIE LORENA GARZON DEAZA</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L50" t="n">
+      <c r="M50" t="n">
         <v>4</v>
       </c>
     </row>
@@ -29619,10 +30534,15 @@
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
+          <t>ANDREA URRUTIA CASTAÑEDA</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L51" t="n">
+      <c r="M51" t="n">
         <v>4</v>
       </c>
     </row>
@@ -29663,10 +30583,15 @@
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
+          <t>FERNANDO JOSE ZAMORA CAMACHO</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L52" t="n">
+      <c r="M52" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29707,10 +30632,15 @@
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
+          <t>FERNANDO JOSE ZAMORA CAMACHO</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L53" t="n">
+      <c r="M53" t="n">
         <v>2</v>
       </c>
     </row>
@@ -29751,10 +30681,15 @@
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
+          <t>FERNANDO JOSE ZAMORA CAMACHO</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
           <t>CERRADA SATISFACTORIAMENTE</t>
         </is>
       </c>
-      <c r="L54" t="n">
+      <c r="M54" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29795,10 +30730,15 @@
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
+          <t>FERNANDO JOSE ZAMORA CAMACHO</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L55" t="n">
+      <c r="M55" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29839,10 +30779,15 @@
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
+          <t>FERNANDO JOSE ZAMORA CAMACHO</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L56" t="n">
+      <c r="M56" t="n">
         <v>2</v>
       </c>
     </row>
@@ -29883,10 +30828,15 @@
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
+          <t>FERNANDO JOSE ZAMORA CAMACHO</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L57" t="n">
+      <c r="M57" t="n">
         <v>4</v>
       </c>
     </row>
@@ -29927,10 +30877,15 @@
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
+          <t>FERNANDO JOSE ZAMORA CAMACHO</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
         <v>5</v>
       </c>
     </row>
@@ -29971,10 +30926,15 @@
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
+          <t>FERNANDO JOSE ZAMORA CAMACHO</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L59" t="n">
+      <c r="M59" t="n">
         <v>2</v>
       </c>
     </row>
@@ -30015,10 +30975,15 @@
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
+          <t>OLGA PATRICIA TORRES BUITRAGO</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L60" t="n">
+      <c r="M60" t="n">
         <v>3</v>
       </c>
     </row>
@@ -30059,10 +31024,15 @@
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
+          <t>FERNANDO JOSE ZAMORA CAMACHO</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L61" t="n">
+      <c r="M61" t="n">
         <v>2</v>
       </c>
     </row>
@@ -30103,10 +31073,15 @@
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
+          <t>FERNANDO JOSE ZAMORA CAMACHO</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L62" t="n">
+      <c r="M62" t="n">
         <v>2</v>
       </c>
     </row>
@@ -30147,10 +31122,15 @@
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
+          <t>FERNANDO JOSE ZAMORA CAMACHO</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L63" t="n">
+      <c r="M63" t="n">
         <v>5</v>
       </c>
     </row>
@@ -30191,10 +31171,15 @@
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
+          <t>FERNANDO JOSE ZAMORA CAMACHO</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L64" t="n">
+      <c r="M64" t="n">
         <v>8</v>
       </c>
     </row>
@@ -30235,10 +31220,15 @@
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
+          <t>FERNANDO JOSE ZAMORA CAMACHO</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L65" t="n">
+      <c r="M65" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30279,10 +31269,15 @@
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
+          <t>FERNANDO JOSE ZAMORA CAMACHO</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L66" t="n">
+      <c r="M66" t="n">
         <v>5</v>
       </c>
     </row>
@@ -30323,10 +31318,15 @@
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
+          <t>FERNANDO JOSE ZAMORA CAMACHO</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L67" t="n">
+      <c r="M67" t="n">
         <v>3</v>
       </c>
     </row>
@@ -30363,10 +31363,15 @@
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
+          <t>MERCEDES LAVERDE</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L68" t="n">
+      <c r="M68" t="n">
         <v>3</v>
       </c>
     </row>
@@ -30407,10 +31412,15 @@
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
+          <t>FERNANDO JOSE ZAMORA CAMACHO</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L69" t="n">
+      <c r="M69" t="n">
         <v>2</v>
       </c>
     </row>
@@ -30451,10 +31461,15 @@
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
+          <t>FERNANDO JOSE ZAMORA CAMACHO</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L70" t="n">
+      <c r="M70" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30495,10 +31510,15 @@
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
+          <t>FERNANDO JOSE ZAMORA CAMACHO</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L71" t="n">
+      <c r="M71" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30539,10 +31559,15 @@
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
+          <t>SCHEYMAN JULIAN SCARPETTA ZAMBRANO</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L72" t="n">
+      <c r="M72" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30583,10 +31608,15 @@
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
+          <t>SEGUNDO ANTONIO SALAMANCA GALAN</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L73" t="n">
+      <c r="M73" t="n">
         <v>6</v>
       </c>
     </row>
@@ -30627,10 +31657,15 @@
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
+          <t>FERNANDO JOSE ZAMORA CAMACHO</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L74" t="n">
+      <c r="M74" t="n">
         <v>2</v>
       </c>
     </row>
@@ -30671,10 +31706,15 @@
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
         <is>
+          <t>JIMMY ALEXANDER GUTIERREZ SARMIENTO</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L75" t="n">
+      <c r="M75" t="n">
         <v>2</v>
       </c>
     </row>
@@ -30715,10 +31755,15 @@
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
+          <t>FERNANDO JOSE ZAMORA CAMACHO</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L76" t="n">
+      <c r="M76" t="n">
         <v>3</v>
       </c>
     </row>
@@ -30759,10 +31804,15 @@
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
         <is>
+          <t>FERNANDO JOSE ZAMORA CAMACHO</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L77" t="n">
+      <c r="M77" t="n">
         <v>6</v>
       </c>
     </row>
@@ -30803,10 +31853,15 @@
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
         <is>
+          <t>MARTHA ELENA DUQUE LONDOÑO</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L78" t="n">
+      <c r="M78" t="n">
         <v>4</v>
       </c>
     </row>
@@ -30847,10 +31902,15 @@
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr">
         <is>
+          <t>FERNANDO JOSE ZAMORA CAMACHO</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L79" t="n">
+      <c r="M79" t="n">
         <v>4</v>
       </c>
     </row>
@@ -30891,10 +31951,15 @@
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
         <is>
+          <t>FERNANDO JOSE ZAMORA CAMACHO</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L80" t="n">
+      <c r="M80" t="n">
         <v>6</v>
       </c>
     </row>
@@ -30935,10 +32000,15 @@
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
         <is>
+          <t>FERNANDO JOSÉ ZAMORA CAMACHO</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L81" t="n">
+      <c r="M81" t="n">
         <v>2</v>
       </c>
     </row>
@@ -30979,10 +32049,15 @@
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
         <is>
+          <t>MARIA GLORIA RINCON GARZON</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L82" t="n">
+      <c r="M82" t="n">
         <v>4</v>
       </c>
     </row>
@@ -31023,10 +32098,15 @@
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr">
         <is>
+          <t>ANGIE FERNANDA BENITEZ PULIDO</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L83" t="n">
+      <c r="M83" t="n">
         <v>1</v>
       </c>
     </row>
@@ -31067,10 +32147,15 @@
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
         <is>
+          <t>ANGIE FERNANDA BENITEZ PULIDO</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L84" t="n">
+      <c r="M84" t="n">
         <v>7</v>
       </c>
     </row>
@@ -31111,10 +32196,15 @@
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr">
         <is>
+          <t>ANGIE FERNANDA BENITEZ PULIDO</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L85" t="n">
+      <c r="M85" t="n">
         <v>3</v>
       </c>
     </row>
@@ -31155,10 +32245,15 @@
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
+          <t>ANGIE FERNANDA BENITEZ PULIDO</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L86" t="n">
+      <c r="M86" t="n">
         <v>5</v>
       </c>
     </row>
@@ -31199,10 +32294,15 @@
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
         <is>
+          <t>ANGIE FERNANDA BENITEZ PULIDO</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L87" t="n">
+      <c r="M87" t="n">
         <v>4</v>
       </c>
     </row>
@@ -31243,10 +32343,15 @@
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr">
         <is>
+          <t>ANGIE FERNANDA BENITEZ PULIDO</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L88" t="n">
+      <c r="M88" t="n">
         <v>6</v>
       </c>
     </row>
@@ -31287,10 +32392,15 @@
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
+          <t>ANGIE FERNANDA BENITEZ PULIDO</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
           <t>CERRADA SATISFACTORIAMENTE</t>
         </is>
       </c>
-      <c r="L89" t="n">
+      <c r="M89" t="n">
         <v>4</v>
       </c>
     </row>
@@ -31331,10 +32441,15 @@
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr">
         <is>
+          <t>ANGIE FERNANDA BENITEZ PULIDO</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L90" t="n">
+      <c r="M90" t="n">
         <v>1</v>
       </c>
     </row>
@@ -31375,10 +32490,15 @@
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
         <is>
+          <t>ANGIE FERNANDA BENITEZ PULIDO</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L91" t="n">
+      <c r="M91" t="n">
         <v>2</v>
       </c>
     </row>
@@ -31415,10 +32535,15 @@
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
+          <t>ANGIE FERNANDA BENITEZ PULIDO</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L92" t="n">
+      <c r="M92" t="n">
         <v>4</v>
       </c>
     </row>
@@ -31455,10 +32580,15 @@
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr">
         <is>
+          <t>ANGIE FERNANDA BENITEZ PULIDO</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L93" t="n">
+      <c r="M93" t="n">
         <v>2</v>
       </c>
     </row>
@@ -31499,10 +32629,15 @@
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr">
         <is>
+          <t>FERNANDO JOSE ZAMORA CAMACHO</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L94" t="n">
+      <c r="M94" t="n">
         <v>2</v>
       </c>
     </row>
@@ -31543,10 +32678,15 @@
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr">
         <is>
+          <t>FERNANDO JOSE ZAMORA CAMACHO</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L95" t="n">
+      <c r="M95" t="n">
         <v>0</v>
       </c>
     </row>
@@ -31587,10 +32727,15 @@
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
         <is>
+          <t>RAFAEL ENRIQUE GUTIERREZ USAQUEN</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L96" t="n">
+      <c r="M96" t="n">
         <v>0</v>
       </c>
     </row>
@@ -31631,10 +32776,15 @@
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr">
         <is>
+          <t>FERNANDO JOSE ZAMORA CAMACHO</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
           <t>EN TRAMITE</t>
         </is>
       </c>
-      <c r="L97" t="n">
+      <c r="M97" t="n">
         <v>1</v>
       </c>
     </row>
@@ -31673,10 +32823,15 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
+          <t>Edil</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
           <t>Finalizado</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -31713,10 +32868,15 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
+          <t>Edil</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
           <t>Finalizado</t>
         </is>
       </c>
-      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -31753,10 +32913,15 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
+          <t>Edil</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
           <t>Finalizado</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -31793,10 +32958,15 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
+          <t>Edil</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
           <t>En Proceso</t>
         </is>
       </c>
-      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -31833,10 +33003,15 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
+          <t>Edil</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
           <t>En Proceso</t>
         </is>
       </c>
-      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -31873,10 +33048,15 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
+          <t>Edil</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
           <t>Finalizado</t>
         </is>
       </c>
-      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -31909,10 +33089,15 @@
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr">
         <is>
+          <t>Edil</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -31949,10 +33134,15 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
+          <t>Edil</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
           <t>Finalizado</t>
         </is>
       </c>
-      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -31989,10 +33179,15 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
+          <t>Edil</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
           <t>En Proceso</t>
         </is>
       </c>
-      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -32029,10 +33224,15 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
+          <t>Edil</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
           <t>Finalizado</t>
         </is>
       </c>
-      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -32069,10 +33269,15 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
+          <t>Edil</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
           <t>Finalizado</t>
         </is>
       </c>
-      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -32109,10 +33314,15 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
+          <t>Edil</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
           <t>Finalizado</t>
         </is>
       </c>
-      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -32149,10 +33359,15 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
+          <t>Edil</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
           <t>Finalizado</t>
         </is>
       </c>
-      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -32189,10 +33404,15 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
+          <t>Edil</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
           <t>Finalizado</t>
         </is>
       </c>
-      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -32229,10 +33449,15 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
+          <t>Edil</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
           <t>En Proceso</t>
         </is>
       </c>
-      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -32269,10 +33494,15 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
+          <t>Edil</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
           <t>Finalizado</t>
         </is>
       </c>
-      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -32307,8 +33537,13 @@
           <t>Alcaldias Locales</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Edil</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -32345,10 +33580,15 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
+          <t>Edil</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
           <t>En Proceso</t>
         </is>
       </c>
-      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -32385,10 +33625,15 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
+          <t>Edil</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
           <t>Finalizado</t>
         </is>
       </c>
-      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -32425,10 +33670,15 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
+          <t>Edil</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
           <t>Finalizado</t>
         </is>
       </c>
-      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -32465,10 +33715,15 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
+          <t>Edil</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
           <t>Finalizado</t>
         </is>
       </c>
-      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -32505,10 +33760,15 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
+          <t>Edil</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
           <t>Finalizado</t>
         </is>
       </c>
-      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -32545,10 +33805,15 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
+          <t>Edil</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
           <t>Finalizado</t>
         </is>
       </c>
-      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -32585,10 +33850,15 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
+          <t>Edil</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
           <t>Finalizado</t>
         </is>
       </c>
-      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -32625,10 +33895,15 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
+          <t>Edil</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
           <t>Finalizado</t>
         </is>
       </c>
-      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -32665,10 +33940,15 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
+          <t>Edil</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
           <t>Finalizado</t>
         </is>
       </c>
-      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -32705,10 +33985,15 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
+          <t>Edil</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
           <t>En Proceso</t>
         </is>
       </c>
-      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -32733,6 +34018,7 @@
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -32769,10 +34055,15 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
+          <t>Edil</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
           <t>En Proceso</t>
         </is>
       </c>
-      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -32809,10 +34100,15 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
+          <t>Edil</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
           <t>En Proceso</t>
         </is>
       </c>
-      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -32849,10 +34145,15 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
+          <t>Edil</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
           <t>Finalizado</t>
         </is>
       </c>
-      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -32889,10 +34190,15 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
+          <t>Edil</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
           <t>Finalizado</t>
         </is>
       </c>
-      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -32929,10 +34235,15 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
+          <t>Edil</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
           <t>Finalizado</t>
         </is>
       </c>
-      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -32969,10 +34280,15 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
+          <t>Edil</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
           <t>Finalizado</t>
         </is>
       </c>
-      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -33009,10 +34325,15 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
+          <t>Edil</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
           <t>En Proceso</t>
         </is>
       </c>
-      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -33049,10 +34370,15 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
+          <t>Edil</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -33089,10 +34415,15 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
+          <t>Edil</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
           <t>Finalizado</t>
         </is>
       </c>
-      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -33129,10 +34460,15 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
+          <t>Edil</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
           <t>Finalizado</t>
         </is>
       </c>
-      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -33169,10 +34505,15 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
+          <t>Edil</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
           <t>En Proceso</t>
         </is>
       </c>
-      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -33209,10 +34550,15 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
+          <t>Edil</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
           <t>En Proceso</t>
         </is>
       </c>
-      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -33244,7 +34590,8 @@
       </c>
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr"/>
-      <c r="L138" t="inlineStr">
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
         <is>
           <t>JORNADA OPAM, RESPONSABILIDAD CON ANIMALES</t>
         </is>
@@ -33280,7 +34627,8 @@
       </c>
       <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr">
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
         <is>
           <t>SOLICITUD DE REVISIÓN DE ANDENES</t>
         </is>
@@ -33316,7 +34664,8 @@
       </c>
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr">
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
         <is>
           <t>ESTUDIO DE EFECTIVIDAD DEL USO DE LA CICLOVÍA, solicitar a movilidad</t>
         </is>
@@ -33352,7 +34701,8 @@
       </c>
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr">
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
         <is>
           <t>MOVILIDAD HIZO VISITA Y CORROBORO EL ESTADO , ESTA PENDIENTE QUE LO PRIORICEN LOS REDUCTORES DE VELOCIDAD YA TIENEN CONCEPTO POSITIVO</t>
         </is>
@@ -33388,7 +34738,8 @@
       </c>
       <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr">
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
         <is>
           <t>REVISION CASO SALON COMUNAL</t>
         </is>
@@ -33424,7 +34775,8 @@
       </c>
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr">
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
         <is>
           <t>3. CONVOCAR JORNADA DE EMBELLECIMIENTO DEL PARQUE Y JORNADA DE SENSIBILIZACIÓN SOBRE TENENCIA DE MASCOTAS CON: CIUDAD LIMPIA, CANCHA</t>
         </is>
@@ -33456,7 +34808,8 @@
       <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr"/>
-      <c r="L144" t="inlineStr">
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
         <is>
           <t>REVISAR CON RECTOR TEMAS O DEFINITIVAMENTE CERRAR</t>
         </is>
@@ -33492,7 +34845,8 @@
       </c>
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr">
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
         <is>
           <t>CONTINUAR GESTIONANDO DE 2 SEGMENTOS VIALES</t>
         </is>
@@ -33528,7 +34882,8 @@
       </c>
       <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr"/>
-      <c r="L146" t="inlineStr">
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
         <is>
           <t>REVISAR SOBRE SOLICITUDES VIA PEATONAL VS CALZADA</t>
         </is>
@@ -33564,7 +34919,8 @@
       </c>
       <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr"/>
-      <c r="L147" t="inlineStr">
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
         <is>
           <t>MESA TECNICA CON METRO, ALCALDIA Y DESARROLLO ECONOMICO, SECRETARIA DE SEGURIDAD, PARA EVALUAR FERIAS, PENDONES, ZONA COMERCIAL, HACERLO EN EL SALON COMUNAL.</t>
         </is>
@@ -33600,7 +34956,8 @@
       </c>
       <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr">
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
         <is>
           <t xml:space="preserve">ESCALAR LA SOLICITUD DE SEÑALIZACIÓN PARA LA ZONA DE GRAN BRITALIA, ESPECÍFICAMENTE EN LA CALLE 46, ANTE METRO. </t>
         </is>
@@ -33636,7 +34993,8 @@
       </c>
       <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr">
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
         <is>
           <t>SOLICITUD DE INTERVENTORIA A CONTRATISTA SOBRE LAS OBSERVACIONES DE MOVILIDAD A SEÑALIZACION, AUN MOVILIDAD NO HA RECIBIDO SEÑALIZACION, REUNION EN DOS MESAS CONVOCAR MESA DE TRABAJO PARA SABER EN QUE ESTADO VA ESPECIALMENTE EN LA SEÑALIZACION DE LA CUADRA</t>
         </is>
@@ -33672,7 +35030,8 @@
       </c>
       <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr">
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
         <is>
           <t>REVISION DE ESTADO VIA, PARA ARREGLO VIAL</t>
         </is>
@@ -33708,7 +35067,8 @@
       </c>
       <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr">
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
         <is>
           <t>2. CULMINAR PROCESO DE LEGALIZACIÓN DEL BARRIO PARA PROCEDER A HACER LA SOLICITUD DE CAMBIO DE REDES DE ALCANTARILLADO Y PAVIMENTACIÓN DE VÍAS.</t>
         </is>
@@ -33744,7 +35104,8 @@
       </c>
       <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr"/>
-      <c r="L152" t="inlineStr">
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr">
         <is>
           <t xml:space="preserve">3. MESA DE TRABAJO CON ALCALDÍA DE BOSA Y ACUEDUCTO PARA QUE ALCALDÍA HAGA DISEÑO DE LOS DOS CIV PARA AVANZAR EN SOLICITUD DE CAMBIO DE REDES Y PAVIMENTACIÓN DE VÍA DE ACCESO AL BARRIO. </t>
         </is>
@@ -33780,7 +35141,8 @@
       </c>
       <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr"/>
-      <c r="L153" t="inlineStr">
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
         <is>
           <t>SOLICITAR INFORMACIÓN A ENTIDADES SOBRE ESTADO DE ENTREGA DEL BARRIO EN SU LEGALIZACIÓN.</t>
         </is>
@@ -33816,7 +35178,8 @@
       </c>
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr"/>
-      <c r="L154" t="inlineStr">
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" t="inlineStr">
         <is>
           <t>PENDIENTES ACUEDUCTO</t>
         </is>
@@ -33852,7 +35215,8 @@
       </c>
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr"/>
-      <c r="L155" t="inlineStr">
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
         <is>
           <t>MESA DE TRABAJO SEGUN PROBLEMATICA AV GUAYACANES, SILLAS DAÑADAS, HABITABILIDAD EN LA CALLE</t>
         </is>
@@ -33884,7 +35248,8 @@
       <c r="I156" t="inlineStr"/>
       <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr">
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr">
         <is>
           <t>EVALUAR PUNTO DE ARROJO PERSISTE JAIRO ANIBAL NIÑO</t>
         </is>
@@ -33920,7 +35285,8 @@
       </c>
       <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr">
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
         <is>
           <t>CONCEPTO TECNICO DETERMINAR CARACTERISTICAS DEL SEGMENTO VIAL PARA RESTRICCION DE CARGA PESADA.</t>
         </is>
@@ -33956,7 +35322,8 @@
       </c>
       <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr"/>
-      <c r="L158" t="inlineStr">
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
         <is>
           <t>SOLICITUD DE CCTV PARA EVALUAR LAS REDES EN TRAMO VIAL CON CIV 8008354</t>
         </is>
@@ -33992,7 +35359,8 @@
       </c>
       <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
-      <c r="L159" t="inlineStr">
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr">
         <is>
           <t>INGRESO DE 4 CAMARAS CON LAS ESPECIFICACIONES PARA INGRESAR AL C4 APLICATIVO</t>
         </is>
@@ -34028,7 +35396,8 @@
       </c>
       <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr"/>
-      <c r="L160" t="inlineStr">
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr">
         <is>
           <t>SOLICITAR RESUMEN DEL PROCESO DEL ESTADO JURIDICO, LA SANCION DE LOS CIV. SABER FECHAS DE AVANNCE PARA INTERVENCION</t>
         </is>
@@ -34064,7 +35433,8 @@
       </c>
       <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr"/>
-      <c r="L161" t="inlineStr">
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr">
         <is>
           <t>DIAGNÓSTICO DE VECTORES, INSPECCIÓN DE SALUD, ESPECIALMENTE POR ROEDORES EN LOS CONTENEDORES.</t>
         </is>
@@ -34100,7 +35470,8 @@
       </c>
       <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr"/>
-      <c r="L162" t="inlineStr">
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" t="inlineStr">
         <is>
           <t>SI BIEN YA TIENE LOGROS FINALIZADOS, EVALUAR NUEVAS ACCIONES</t>
         </is>
@@ -34136,7 +35507,8 @@
       </c>
       <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr"/>
-      <c r="L163" t="inlineStr">
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" t="inlineStr">
         <is>
           <t>A SE REALIZÒ SIEMBRA, REVISAR COMO FORTALECER MESA</t>
         </is>
@@ -34172,7 +35544,8 @@
       </c>
       <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr"/>
-      <c r="L164" t="inlineStr">
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr">
         <is>
           <t>ARREGLO DE VIA</t>
         </is>
@@ -34208,7 +35581,8 @@
       </c>
       <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr"/>
-      <c r="L165" t="inlineStr">
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr">
         <is>
           <t>NUEVO ESTUDIO DE CONTEO DE LA ZONA, CUANDO SALGA EL CONTRATO - AFORO</t>
         </is>
@@ -34244,7 +35618,8 @@
       </c>
       <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr"/>
-      <c r="L166" t="inlineStr">
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="inlineStr">
         <is>
           <t>GESTION DE VIA EN MAL ESTADO</t>
         </is>
@@ -34280,7 +35655,8 @@
       </c>
       <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr"/>
-      <c r="L167" t="inlineStr">
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr">
         <is>
           <t>GESTION DE VIA EN MAL ESTADO</t>
         </is>
@@ -34316,7 +35692,8 @@
       </c>
       <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr"/>
-      <c r="L168" t="inlineStr">
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr">
         <is>
           <t>GESTION DE SOCAVON</t>
         </is>
@@ -34352,7 +35729,8 @@
       </c>
       <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr"/>
-      <c r="L169" t="inlineStr">
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="inlineStr">
         <is>
           <t>INCLUIR EL CIV EN EL BANCO DE INICIATIVAS (ALCALDÍA). IGUAL TENER PRESENTE QUE YA ACUDUCTO HIZO INTERVENCION</t>
         </is>
@@ -34388,7 +35766,8 @@
       </c>
       <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr"/>
-      <c r="L170" t="inlineStr">
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="inlineStr">
         <is>
           <t>EVALUAR YA SE RESOLVIO, SIN EMBARGO, LA LIDER HA SOLICTADO OFERTA MUJERES Y A DULTO MAYOR</t>
         </is>
@@ -34424,7 +35803,8 @@
       </c>
       <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr"/>
-      <c r="L171" t="inlineStr">
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" t="inlineStr">
         <is>
           <t>GESTION SEGMENTO VIAL</t>
         </is>
@@ -34460,7 +35840,8 @@
       </c>
       <c r="J172" t="inlineStr"/>
       <c r="K172" t="inlineStr"/>
-      <c r="L172" t="inlineStr">
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" t="inlineStr">
         <is>
           <t>FERIA DE SERVICIOS</t>
         </is>
@@ -34496,7 +35877,8 @@
       </c>
       <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr"/>
-      <c r="L173" t="inlineStr">
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" t="inlineStr">
         <is>
           <t>RESIDUOS JORNADA DE EMBELLECIMIENTO</t>
         </is>
@@ -34532,7 +35914,8 @@
       </c>
       <c r="J174" t="inlineStr"/>
       <c r="K174" t="inlineStr"/>
-      <c r="L174" t="inlineStr">
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" t="inlineStr">
         <is>
           <t>CONFORMACION FRENTE DE SEGURIDAD</t>
         </is>
@@ -34568,7 +35951,8 @@
       </c>
       <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr"/>
-      <c r="L175" t="inlineStr">
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" t="inlineStr">
         <is>
           <t>REUBICACION CONTENEDORES DE BASURA</t>
         </is>
@@ -34604,7 +35988,8 @@
       </c>
       <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr"/>
-      <c r="L176" t="inlineStr">
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" t="inlineStr">
         <is>
           <t>POR IDRD ESTA INCLUIDO EN CONTRATO 1148 DE 2024, MANTENIMIENTO DE PARQUE, ARREGLARON EL PARQUE DE LOS NIÑOS</t>
         </is>
@@ -34640,7 +36025,8 @@
       </c>
       <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr"/>
-      <c r="L177" t="inlineStr">
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" t="inlineStr">
         <is>
           <t>REUNION PARA CREAR FRENTE DE SEGURIDAD Y POLICIA Y SECRETARIA DE SEGURIDAD</t>
         </is>
@@ -34676,7 +36062,8 @@
       </c>
       <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr"/>
-      <c r="L178" t="inlineStr">
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" t="inlineStr">
         <is>
           <t>INCLUSION EN EL BANCO DE INICIATIVAS, FALTA DOCUMENTO FORMAL</t>
         </is>
@@ -34712,7 +36099,8 @@
       </c>
       <c r="J179" t="inlineStr"/>
       <c r="K179" t="inlineStr"/>
-      <c r="L179" t="inlineStr">
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" t="inlineStr">
         <is>
           <t>MESA DE TRABAJO PARA CONOCER COMANDANTE DEL CUADRANTE CREACION DE FRENTES DE SEGURIDAD CON LA COMUNIDAD</t>
         </is>
@@ -34748,7 +36136,8 @@
       </c>
       <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr"/>
-      <c r="L180" t="inlineStr">
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" t="inlineStr">
         <is>
           <t>OPERATIVO COMERCIANTES MAL PARQUEO AL LADO DEL POLIDEPORTIVO Y TAMBIEN CON HABITANTES DE CALLE</t>
         </is>
@@ -34784,7 +36173,8 @@
       </c>
       <c r="J181" t="inlineStr"/>
       <c r="K181" t="inlineStr"/>
-      <c r="L181" t="inlineStr">
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" t="inlineStr">
         <is>
           <t>EVALUAR CON COMUNIDAD EXTERNA SI SE PUEDE SERGUIR TRABAJANDO EN ALGO ADICIONAL, YA QUE YA SE ARREGLO LA TAPA</t>
         </is>
@@ -34820,7 +36210,8 @@
       </c>
       <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr"/>
-      <c r="L182" t="inlineStr">
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" t="inlineStr">
         <is>
           <t>YA SE ARREGLARON UNOS SEGMENTOS, EVALUAR LOS OTROS</t>
         </is>
@@ -34856,7 +36247,8 @@
       </c>
       <c r="J183" t="inlineStr"/>
       <c r="K183" t="inlineStr"/>
-      <c r="L183" t="inlineStr">
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" t="inlineStr">
         <is>
           <t>DOMINGO 13 DE JULIO ACTIVIDAD DE TOMA DEL PARQUE.</t>
         </is>
@@ -34892,7 +36284,8 @@
       </c>
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr"/>
-      <c r="L184" t="inlineStr">
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" t="inlineStr">
         <is>
           <t>IVC ESCALAR CON SECRETARIA DE SEGURIDAD LA POSIBILIDAD DE PATRULLAJE MIXTO</t>
         </is>
@@ -34928,7 +36321,8 @@
       </c>
       <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr"/>
-      <c r="L185" t="inlineStr">
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" t="inlineStr">
         <is>
           <t>ARREGLO DE ANDEN POR PROBLEMATICA RAICES ARBOLES</t>
         </is>
@@ -34964,7 +36358,8 @@
       </c>
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr"/>
-      <c r="L186" t="inlineStr">
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" t="inlineStr">
         <is>
           <t>EVALUAR PORQUE YA ARREGLARON BOCACALLES, NO TENEMOS LIDERES EXTERNOS, no hay drive pendiente fernando</t>
         </is>
@@ -35000,7 +36395,8 @@
       </c>
       <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr"/>
-      <c r="L187" t="inlineStr">
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" t="inlineStr">
         <is>
           <t>EVALUAR CON LA LIDER MAS ACCIONES A REALIZAR, SE REVISARON YA LAS LUMINARIAS</t>
         </is>
@@ -35036,7 +36432,8 @@
       </c>
       <c r="J188" t="inlineStr"/>
       <c r="K188" t="inlineStr"/>
-      <c r="L188" t="inlineStr">
+      <c r="L188" t="inlineStr"/>
+      <c r="M188" t="inlineStr">
         <is>
           <t>IMPLEMENTACION INTEGRAL DEL DISEÑO DE SEÑALIZACION UNA VEZ SE SURTA EL ARREGLO DE LA VIA FRENTE AL COLEGIO</t>
         </is>
@@ -35072,7 +36469,8 @@
       </c>
       <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr"/>
-      <c r="L189" t="inlineStr">
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" t="inlineStr">
         <is>
           <t>GESTION ARREGLO DE VIA Y ANDENES</t>
         </is>
@@ -35108,7 +36506,8 @@
       </c>
       <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr"/>
-      <c r="L190" t="inlineStr">
+      <c r="L190" t="inlineStr"/>
+      <c r="M190" t="inlineStr">
         <is>
           <t>GESTION DE ARREGLO DE VIAS (IDU - ALCALDIA)</t>
         </is>
@@ -35144,7 +36543,8 @@
       </c>
       <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr"/>
-      <c r="L191" t="inlineStr">
+      <c r="L191" t="inlineStr"/>
+      <c r="M191" t="inlineStr">
         <is>
           <t>TRASLADO EVALUAR PERTINENCIA INSTALACION, RESULTADO. FRANJAS DE ESTOPEROLES TENGAN EN CUENTA EL CONVENIO 10 ESTUDIO</t>
         </is>
@@ -35180,7 +36580,8 @@
       </c>
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr"/>
-      <c r="L192" t="inlineStr">
+      <c r="L192" t="inlineStr"/>
+      <c r="M192" t="inlineStr">
         <is>
           <t>ENVIAR UN ACTA CON LA SITUACION QUE SUCEDE, CAMBIO DE CARPETA ATENCION DE EMERGENCIAS</t>
         </is>
@@ -35216,7 +36617,8 @@
       </c>
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr"/>
-      <c r="L193" t="inlineStr">
+      <c r="L193" t="inlineStr"/>
+      <c r="M193" t="inlineStr">
         <is>
           <t>ENVIAR DERECHO DE PETICION DE ECOPUNTO</t>
         </is>
@@ -35252,7 +36654,8 @@
       </c>
       <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr"/>
-      <c r="L194" t="inlineStr">
+      <c r="L194" t="inlineStr"/>
+      <c r="M194" t="inlineStr">
         <is>
           <t>EVALUAR CON EL LIDER NUEVAS ACCIONES YA QUE LAS PROBLEMASTICAS DE LA MESA SE SOLUCIONARON</t>
         </is>
@@ -35288,7 +36691,8 @@
       </c>
       <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr"/>
-      <c r="L195" t="inlineStr">
+      <c r="L195" t="inlineStr"/>
+      <c r="M195" t="inlineStr">
         <is>
           <t>REVSION DE POSTE</t>
         </is>
@@ -35324,7 +36728,8 @@
       </c>
       <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr"/>
-      <c r="L196" t="inlineStr">
+      <c r="L196" t="inlineStr"/>
+      <c r="M196" t="inlineStr">
         <is>
           <t>SOLICITUD A MOVILIDAD SOBRE INSTALACION DE SEMAFORO EN CRUZ DEL PARQUE MARACANA</t>
         </is>
@@ -35360,7 +36765,8 @@
       </c>
       <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr"/>
-      <c r="L197" t="inlineStr">
+      <c r="L197" t="inlineStr"/>
+      <c r="M197" t="inlineStr">
         <is>
           <t>CAMBIO DE POSTE DE REDES ELÉCTRICAS EN MAL ESTADO.</t>
         </is>
@@ -35396,7 +36802,8 @@
       </c>
       <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr"/>
-      <c r="L198" t="inlineStr">
+      <c r="L198" t="inlineStr"/>
+      <c r="M198" t="inlineStr">
         <is>
           <t>GESTION DE ARREGLO DE VIAS (IDU - ALCALDIA)</t>
         </is>
@@ -35432,7 +36839,8 @@
       </c>
       <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr"/>
-      <c r="L199" t="inlineStr">
+      <c r="L199" t="inlineStr"/>
+      <c r="M199" t="inlineStr">
         <is>
           <t>GESTION ARREGLO POMPEYANO</t>
         </is>
@@ -35468,7 +36876,8 @@
       </c>
       <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr"/>
-      <c r="L200" t="inlineStr">
+      <c r="L200" t="inlineStr"/>
+      <c r="M200" t="inlineStr">
         <is>
           <t>REVISAR GESTIONES CON LIDER</t>
         </is>
@@ -35504,7 +36913,8 @@
       </c>
       <c r="J201" t="inlineStr"/>
       <c r="K201" t="inlineStr"/>
-      <c r="L201" t="inlineStr">
+      <c r="L201" t="inlineStr"/>
+      <c r="M201" t="inlineStr">
         <is>
           <t>REVISAR BASE PORQUE NO SE CUENTA Y GESTION (FERNANDO)</t>
         </is>
@@ -35540,7 +36950,8 @@
       </c>
       <c r="J202" t="inlineStr"/>
       <c r="K202" t="inlineStr"/>
-      <c r="L202" t="inlineStr">
+      <c r="L202" t="inlineStr"/>
+      <c r="M202" t="inlineStr">
         <is>
           <t>GESTION ARREGLO PARQUE</t>
         </is>
@@ -35576,7 +36987,8 @@
       </c>
       <c r="J203" t="inlineStr"/>
       <c r="K203" t="inlineStr"/>
-      <c r="L203" t="inlineStr">
+      <c r="L203" t="inlineStr"/>
+      <c r="M203" t="inlineStr">
         <is>
           <t>GESTION VIA EN MAL ESTADO</t>
         </is>
@@ -35612,7 +37024,8 @@
       </c>
       <c r="J204" t="inlineStr"/>
       <c r="K204" t="inlineStr"/>
-      <c r="L204" t="inlineStr">
+      <c r="L204" t="inlineStr"/>
+      <c r="M204" t="inlineStr">
         <is>
           <t>MAL PARQUEO CAMIONES Y MULAS MAS CONSTANTES CUADRA ESTRECHA (PENDIENTE COMPROBANTES COMUNIDAD)</t>
         </is>
@@ -35644,7 +37057,8 @@
       <c r="I205" t="inlineStr"/>
       <c r="J205" t="inlineStr"/>
       <c r="K205" t="inlineStr"/>
-      <c r="L205" t="inlineStr">
+      <c r="L205" t="inlineStr"/>
+      <c r="M205" t="inlineStr">
         <is>
           <t>MESA DE TRABAJO DE SEGUIMIENTO PARA REALIZAR FINALIZANDO AGOSTO ( OJO AVISAR CON 8 DIAS) SABADO, ENTRE SEMANA A LAS (6:00 PM)</t>
         </is>
@@ -35680,7 +37094,8 @@
       </c>
       <c r="J206" t="inlineStr"/>
       <c r="K206" t="inlineStr"/>
-      <c r="L206" t="inlineStr">
+      <c r="L206" t="inlineStr"/>
+      <c r="M206" t="inlineStr">
         <is>
           <t>REVISAR LA ALCANTARILLA SI HABIA EN LA CRA 81 D BIS SE INUNDA EN LA MITAD</t>
         </is>
@@ -35716,7 +37131,8 @@
       </c>
       <c r="J207" t="inlineStr"/>
       <c r="K207" t="inlineStr"/>
-      <c r="L207" t="inlineStr">
+      <c r="L207" t="inlineStr"/>
+      <c r="M207" t="inlineStr">
         <is>
           <t>GESTION DE ARREGLO DE ANDENES</t>
         </is>
@@ -35752,7 +37168,8 @@
       </c>
       <c r="J208" t="inlineStr"/>
       <c r="K208" t="inlineStr"/>
-      <c r="L208" t="inlineStr">
+      <c r="L208" t="inlineStr"/>
+      <c r="M208" t="inlineStr">
         <is>
           <t>LIMPIEZA DE 2 SUMIDEROS MANTENIMIENTO Y RESULTADO DE LA INSPECCION ( DIAGNOSTICO)</t>
         </is>
@@ -35788,7 +37205,8 @@
       </c>
       <c r="J209" t="inlineStr"/>
       <c r="K209" t="inlineStr"/>
-      <c r="L209" t="inlineStr">
+      <c r="L209" t="inlineStr"/>
+      <c r="M209" t="inlineStr">
         <is>
           <t>REALIZAR VISITA TÉCNICA E INCLUSIÓN EN EL BANCO DE INICIATIVAS.</t>
         </is>
@@ -35824,7 +37242,8 @@
       </c>
       <c r="J210" t="inlineStr"/>
       <c r="K210" t="inlineStr"/>
-      <c r="L210" t="inlineStr">
+      <c r="L210" t="inlineStr"/>
+      <c r="M210" t="inlineStr">
         <is>
           <t>SE HIZO GESTION PROBLEMATICA HABITANTES PERO NO HAY RESPUESTA EN DRIVE</t>
         </is>
@@ -35860,7 +37279,8 @@
       </c>
       <c r="J211" t="inlineStr"/>
       <c r="K211" t="inlineStr"/>
-      <c r="L211" t="inlineStr">
+      <c r="L211" t="inlineStr"/>
+      <c r="M211" t="inlineStr">
         <is>
           <t xml:space="preserve">REVISAR CON LIDER GESTIONES </t>
         </is>
@@ -35896,7 +37316,8 @@
       </c>
       <c r="J212" t="inlineStr"/>
       <c r="K212" t="inlineStr"/>
-      <c r="L212" t="inlineStr">
+      <c r="L212" t="inlineStr"/>
+      <c r="M212" t="inlineStr">
         <is>
           <t>ENVIAR REPORTE A MOVILIDAD SOBRE INTERVENCIÓN DE SEÑALES EN MAL ESTADO.</t>
         </is>
@@ -35932,7 +37353,8 @@
       </c>
       <c r="J213" t="inlineStr"/>
       <c r="K213" t="inlineStr"/>
-      <c r="L213" t="inlineStr">
+      <c r="L213" t="inlineStr"/>
+      <c r="M213" t="inlineStr">
         <is>
           <t>PROGRAMA GUARDA CAMINOS REUNION CON EL RECTOR</t>
         </is>
@@ -35968,7 +37390,8 @@
       </c>
       <c r="J214" t="inlineStr"/>
       <c r="K214" t="inlineStr"/>
-      <c r="L214" t="inlineStr">
+      <c r="L214" t="inlineStr"/>
+      <c r="M214" t="inlineStr">
         <is>
           <t xml:space="preserve">REVISAR CON LIDER GESTIONES </t>
         </is>
@@ -36004,7 +37427,8 @@
       </c>
       <c r="J215" t="inlineStr"/>
       <c r="K215" t="inlineStr"/>
-      <c r="L215" t="inlineStr">
+      <c r="L215" t="inlineStr"/>
+      <c r="M215" t="inlineStr">
         <is>
           <t>TRASLADO DERECHO DE PETICIÓN SOBRE ÁRBOL Y POSIBLE NUEVA PLANTACIÓN</t>
         </is>
@@ -36040,7 +37464,8 @@
       </c>
       <c r="J216" t="inlineStr"/>
       <c r="K216" t="inlineStr"/>
-      <c r="L216" t="inlineStr">
+      <c r="L216" t="inlineStr"/>
+      <c r="M216" t="inlineStr">
         <is>
           <t>TRASLADO DE SOLICITUD DE VISITA UAESP A CUADRA POR POCA ILUMINACIÓN Y REVISAR ESTADO DE POSTE 11855185</t>
         </is>
@@ -36076,7 +37501,8 @@
       </c>
       <c r="J217" t="inlineStr"/>
       <c r="K217" t="inlineStr"/>
-      <c r="L217" t="inlineStr">
+      <c r="L217" t="inlineStr"/>
+      <c r="M217" t="inlineStr">
         <is>
           <t>REALIZAR DIAGNÓSTICO E INCLUSIÓN A BANCO DE INICIATIVAS</t>
         </is>
@@ -36112,7 +37538,8 @@
       </c>
       <c r="J218" t="inlineStr"/>
       <c r="K218" t="inlineStr"/>
-      <c r="L218" t="inlineStr">
+      <c r="L218" t="inlineStr"/>
+      <c r="M218" t="inlineStr">
         <is>
           <t>TRASLADO DE DERCHO DE PETICIÓN DE DIAGNOSTICO DE SECRETARIA DE SALUD SOBRE VECTORES.</t>
         </is>
@@ -36148,7 +37575,8 @@
       </c>
       <c r="J219" t="inlineStr"/>
       <c r="K219" t="inlineStr"/>
-      <c r="L219" t="inlineStr">
+      <c r="L219" t="inlineStr"/>
+      <c r="M219" t="inlineStr">
         <is>
           <t>REPORTAR A AGUAS DE BOGOTÁ SOBRE LLANTAS</t>
         </is>
@@ -36184,7 +37612,8 @@
       </c>
       <c r="J220" t="inlineStr"/>
       <c r="K220" t="inlineStr"/>
-      <c r="L220" t="inlineStr">
+      <c r="L220" t="inlineStr"/>
+      <c r="M220" t="inlineStr">
         <is>
           <t>ENVIAR DE MANERA FORMAL EL ESTADO ACTUAL DE VÍAS.</t>
         </is>
@@ -36220,7 +37649,8 @@
       </c>
       <c r="J221" t="inlineStr"/>
       <c r="K221" t="inlineStr"/>
-      <c r="L221" t="inlineStr">
+      <c r="L221" t="inlineStr"/>
+      <c r="M221" t="inlineStr">
         <is>
           <t>OPERATIVOS EN ZONA DE MAL PARQUEO (YA SE REALIZO UNO PERO NO TUVO IMPACTOO)</t>
         </is>
@@ -36256,7 +37686,8 @@
       </c>
       <c r="J222" t="inlineStr"/>
       <c r="K222" t="inlineStr"/>
-      <c r="L222" t="inlineStr">
+      <c r="L222" t="inlineStr"/>
+      <c r="M222" t="inlineStr">
         <is>
           <t>PROBLEMATICA CONTENEDORES</t>
         </is>
@@ -36292,7 +37723,8 @@
       </c>
       <c r="J223" t="inlineStr"/>
       <c r="K223" t="inlineStr"/>
-      <c r="L223" t="inlineStr">
+      <c r="L223" t="inlineStr"/>
+      <c r="M223" t="inlineStr">
         <is>
           <t>GESTION ARREGLO VIAS (CONSULTAR CON PASTORES)</t>
         </is>
@@ -36328,7 +37760,8 @@
       </c>
       <c r="J224" t="inlineStr"/>
       <c r="K224" t="inlineStr"/>
-      <c r="L224" t="inlineStr">
+      <c r="L224" t="inlineStr"/>
+      <c r="M224" t="inlineStr">
         <is>
           <t>PROBLEMATICA REDES DEL ACUEDUCTO</t>
         </is>
@@ -36364,7 +37797,8 @@
       </c>
       <c r="J225" t="inlineStr"/>
       <c r="K225" t="inlineStr"/>
-      <c r="L225" t="inlineStr">
+      <c r="L225" t="inlineStr"/>
+      <c r="M225" t="inlineStr">
         <is>
           <t>ENVIAR ACTA DE ACUEDUCTO AL CONCEJAL SOBRE RESPUESTA DE LOS 2 PUNTOS. SOBRE EL SEGUNDO PUNTO ENVIAR INFORME QUE MENCIONÓ DELEGADO DE LA ENTIDAD, DONDE SE CONFIRMA QUE NO FUE INCLUIDO EN PLANES DE RENOVACIÓN PORQUE YA ESTÁ EN PVC.</t>
         </is>
@@ -36400,7 +37834,8 @@
       </c>
       <c r="J226" t="inlineStr"/>
       <c r="K226" t="inlineStr"/>
-      <c r="L226" t="inlineStr">
+      <c r="L226" t="inlineStr"/>
+      <c r="M226" t="inlineStr">
         <is>
           <t>ENVIAR RESPUESTA FORMAL SOBRE LA REVISIÓN A LAS REDES DEL ACUEDUCTO.</t>
         </is>
@@ -36436,7 +37871,8 @@
       </c>
       <c r="J227" t="inlineStr"/>
       <c r="K227" t="inlineStr"/>
-      <c r="L227" t="inlineStr">
+      <c r="L227" t="inlineStr"/>
+      <c r="M227" t="inlineStr">
         <is>
           <t>INFORME ESTADO DE VIA ALCALDIA (SE ENVIO POR CONCEJO NO HAY RESPUESTA)FERNANDO</t>
         </is>
@@ -36472,7 +37908,8 @@
       </c>
       <c r="J228" t="inlineStr"/>
       <c r="K228" t="inlineStr"/>
-      <c r="L228" t="inlineStr">
+      <c r="L228" t="inlineStr"/>
+      <c r="M228" t="inlineStr">
         <is>
           <t>INFORME ACUEDUCTO ESTADO DE REDES (SE ENVIO POR CONCEJO AUN NO HAY REPSUESTA) FERNANDO</t>
         </is>
@@ -36508,7 +37945,8 @@
       </c>
       <c r="J229" t="inlineStr"/>
       <c r="K229" t="inlineStr"/>
-      <c r="L229" t="inlineStr">
+      <c r="L229" t="inlineStr"/>
+      <c r="M229" t="inlineStr">
         <is>
           <t>TRASLADO DE FICHA TÉCNICA POR PARTE DEL DADEP A LA ALCALDÍA LOCAL, DE ACUERDO A ESTO, SE REALICE UN DIAGNÓSTICO DEL ANDÉN PARA QUE LA ALCALDÍA LOCAL PUEDA COMPLEMENTAR LA ZONA DEL ANDÉN, QUE FALTARÍA POR INTERVENIR.</t>
         </is>
@@ -36544,7 +37982,8 @@
       </c>
       <c r="J230" t="inlineStr"/>
       <c r="K230" t="inlineStr"/>
-      <c r="L230" t="inlineStr">
+      <c r="L230" t="inlineStr"/>
+      <c r="M230" t="inlineStr">
         <is>
           <t>VALIDAR LA VIABILIDAD PARA LA INSTALACIÓN DE MATERAS, ASÍ COMO DETERMINAR LA CANTIDAD REQUERIDA Y LAS ÁREAS QUE NECESITAN PINTURA, CONFORME AL DIAGNÓSTICO TÉCNICO.</t>
         </is>
@@ -36580,7 +38019,8 @@
       </c>
       <c r="J231" t="inlineStr"/>
       <c r="K231" t="inlineStr"/>
-      <c r="L231" t="inlineStr">
+      <c r="L231" t="inlineStr"/>
+      <c r="M231" t="inlineStr">
         <is>
           <t>REALIZAR LAS GESTIONES PARA SOLICITAR A LA ENTIDAD COMPETENTE UNA JORNADA DE CONTROL DE VECTORES EN EL SECTOR.</t>
         </is>
@@ -36616,7 +38056,8 @@
       </c>
       <c r="J232" t="inlineStr"/>
       <c r="K232" t="inlineStr"/>
-      <c r="L232" t="inlineStr">
+      <c r="L232" t="inlineStr"/>
+      <c r="M232" t="inlineStr">
         <is>
           <t>REVISAR LIDER GESTIONES (POR EJEMPLO VISITAR LA EMPRESA Y ESCUCHAR QUE NECESITAN SUS EMPLEADOS)</t>
         </is>
@@ -36652,7 +38093,8 @@
       </c>
       <c r="J233" t="inlineStr"/>
       <c r="K233" t="inlineStr"/>
-      <c r="L233" t="inlineStr">
+      <c r="L233" t="inlineStr"/>
+      <c r="M233" t="inlineStr">
         <is>
           <t>SE CONSULTARÁ CON LA UAESP SI YA SE HA REALIZADO INTERVENCIÓN EN LOS POSTES DE LUZ</t>
         </is>
@@ -36688,7 +38130,8 @@
       </c>
       <c r="J234" t="inlineStr"/>
       <c r="K234" t="inlineStr"/>
-      <c r="L234" t="inlineStr">
+      <c r="L234" t="inlineStr"/>
+      <c r="M234" t="inlineStr">
         <is>
           <t>EVALUAR ACCIONES CON POLICIA PORQUE CON EL FRENTE A SIDO COMPLICADO</t>
         </is>
@@ -36724,7 +38167,8 @@
       </c>
       <c r="J235" t="inlineStr"/>
       <c r="K235" t="inlineStr"/>
-      <c r="L235" t="inlineStr">
+      <c r="L235" t="inlineStr"/>
+      <c r="M235" t="inlineStr">
         <is>
           <t>REVISIÓN DEL ESTADO DE LAS VÍAS DEL SECTOR, EN ATENCIÓN A LA SOLICITUD DE LA COMUNIDAD PARA EL ARREGLO DE LAS BAHÍAS.</t>
         </is>
@@ -36760,7 +38204,8 @@
       </c>
       <c r="J236" t="inlineStr"/>
       <c r="K236" t="inlineStr"/>
-      <c r="L236" t="inlineStr">
+      <c r="L236" t="inlineStr"/>
+      <c r="M236" t="inlineStr">
         <is>
           <t>SOBRE LA AV. VILLAVICENCIO SE IDENTIFICÓ EXTENSIÓN DE COMERCIO; LA ALCALDÍA REALIZARÁ JORNADA DE SENSIBILIZACIÓN CON LOS ESTABLECIMIENTOS DEL SECTOR.</t>
         </is>
@@ -36796,7 +38241,8 @@
       </c>
       <c r="J237" t="inlineStr"/>
       <c r="K237" t="inlineStr"/>
-      <c r="L237" t="inlineStr">
+      <c r="L237" t="inlineStr"/>
+      <c r="M237" t="inlineStr">
         <is>
           <t>GESTIONES DE ARBOLES Y CABLES</t>
         </is>
@@ -36832,7 +38278,8 @@
       </c>
       <c r="J238" t="inlineStr"/>
       <c r="K238" t="inlineStr"/>
-      <c r="L238" t="inlineStr">
+      <c r="L238" t="inlineStr"/>
+      <c r="M238" t="inlineStr">
         <is>
           <t>PROBLEMATICA DE BASURAS (CAZAINFRACTORES)</t>
         </is>
@@ -36868,7 +38315,8 @@
       </c>
       <c r="J239" t="inlineStr"/>
       <c r="K239" t="inlineStr"/>
-      <c r="L239" t="inlineStr">
+      <c r="L239" t="inlineStr"/>
+      <c r="M239" t="inlineStr">
         <is>
           <t xml:space="preserve">EVALUAR CON LIDER FERIAS </t>
         </is>
@@ -36904,7 +38352,8 @@
       </c>
       <c r="J240" t="inlineStr"/>
       <c r="K240" t="inlineStr"/>
-      <c r="L240" t="inlineStr">
+      <c r="L240" t="inlineStr"/>
+      <c r="M240" t="inlineStr">
         <is>
           <t>DERECHO DE PETICIÓN PARA JORNADA DE SALUD ANIMAL (SE ENVIO DERECHO PERO AUN LIDER NO ENVIA)</t>
         </is>
@@ -36940,7 +38389,8 @@
       </c>
       <c r="J241" t="inlineStr"/>
       <c r="K241" t="inlineStr"/>
-      <c r="L241" t="inlineStr">
+      <c r="L241" t="inlineStr"/>
+      <c r="M241" t="inlineStr">
         <is>
           <t>LA ALCALDÍA ENVIARÁ INFORME DEL CONTRATISTA SOBRE LA PÓLIZA DE ESTABILIDAD QUE TIENE EL PARQUE CON CONTRATO 324 DEL 2019. (LA MESA SOLO ASISTIO LIDER, SERIA ARTICULAR CON SANDRA Y LUCY)</t>
         </is>
@@ -36976,7 +38426,8 @@
       </c>
       <c r="J242" t="inlineStr"/>
       <c r="K242" t="inlineStr"/>
-      <c r="L242" t="inlineStr">
+      <c r="L242" t="inlineStr"/>
+      <c r="M242" t="inlineStr">
         <is>
           <t>OPERATIVO SOBRE CAMBUCHES DE HABITANTES DE CALLE EN EL PARQUE CIUDAD TECHO II ENTRE LA NOCHE-MADRUGADA.</t>
         </is>
@@ -37012,7 +38463,8 @@
       </c>
       <c r="J243" t="inlineStr"/>
       <c r="K243" t="inlineStr"/>
-      <c r="L243" t="inlineStr">
+      <c r="L243" t="inlineStr"/>
+      <c r="M243" t="inlineStr">
         <is>
           <t>GESTION ARREGLO DE VIA</t>
         </is>
@@ -37048,7 +38500,8 @@
       </c>
       <c r="J244" t="inlineStr"/>
       <c r="K244" t="inlineStr"/>
-      <c r="L244" t="inlineStr">
+      <c r="L244" t="inlineStr"/>
+      <c r="M244" t="inlineStr">
         <is>
           <t>GESTION POR VENDEDORES INFORMALES DESORGANIZADOS EN ESPACIO PUBLICO</t>
         </is>
@@ -37084,7 +38537,8 @@
       </c>
       <c r="J245" t="inlineStr"/>
       <c r="K245" t="inlineStr"/>
-      <c r="L245" t="inlineStr">
+      <c r="L245" t="inlineStr"/>
+      <c r="M245" t="inlineStr">
         <is>
           <t>ROEDORES POR MALA DISPOSICION DE RESIDUOS</t>
         </is>
@@ -37120,7 +38574,8 @@
       </c>
       <c r="J246" t="inlineStr"/>
       <c r="K246" t="inlineStr"/>
-      <c r="L246" t="inlineStr">
+      <c r="L246" t="inlineStr"/>
+      <c r="M246" t="inlineStr">
         <is>
           <t>FERIA DE EMPLEO Y EMPRENDIMIENTO, ASÍ COMO JORNADA DE PERSONALIZACIÓN DE TARJETAS SITP PARA LA COMUNIDAD. revisar porque en la mesa solo fue 1 persona pero no apoya al Partido</t>
         </is>
@@ -37156,7 +38611,8 @@
       </c>
       <c r="J247" t="inlineStr"/>
       <c r="K247" t="inlineStr"/>
-      <c r="L247" t="inlineStr">
+      <c r="L247" t="inlineStr"/>
+      <c r="M247" t="inlineStr">
         <is>
           <t>LA ALCALDÍA LOCAL TOMA LA SOLICITUD PARA SU INCLUSIÓN EN EL BANCO DE INICIATIVAS, RELACIONADA CON LA INSTALACIÓN DE MALLA PARA LA CANCHA.</t>
         </is>
@@ -37192,7 +38648,8 @@
       </c>
       <c r="J248" t="inlineStr"/>
       <c r="K248" t="inlineStr"/>
-      <c r="L248" t="inlineStr">
+      <c r="L248" t="inlineStr"/>
+      <c r="M248" t="inlineStr">
         <is>
           <t>SENSIBILIZACIÓN SOBRE VACUNACIÓN GRATUITA Y MANEJO DE EXCRETAS, DESARROLLADA ENTRE ENERO Y DICIEMBRE, EN ARTICULACIÓN CON LA POLICÍA COMUNITARIA.</t>
         </is>
@@ -37228,7 +38685,8 @@
       </c>
       <c r="J249" t="inlineStr"/>
       <c r="K249" t="inlineStr"/>
-      <c r="L249" t="inlineStr">
+      <c r="L249" t="inlineStr"/>
+      <c r="M249" t="inlineStr">
         <is>
           <t>EVALUAR LA POSIBILIDAD, CON EL APOYO DE LA SUPERVISIÓN, DE REALIZAR ESTA ACTIVIDAD A TRAVÉS DEL CONTRATO DE FERRETERÍA O DE CONSTRUCCIÓN.</t>
         </is>
@@ -37264,7 +38722,8 @@
       </c>
       <c r="J250" t="inlineStr"/>
       <c r="K250" t="inlineStr"/>
-      <c r="L250" t="inlineStr">
+      <c r="L250" t="inlineStr"/>
+      <c r="M250" t="inlineStr">
         <is>
           <t xml:space="preserve">REVISAR CON LIDER GESTIONES </t>
         </is>
@@ -37300,7 +38759,8 @@
       </c>
       <c r="J251" t="inlineStr"/>
       <c r="K251" t="inlineStr"/>
-      <c r="L251" t="inlineStr">
+      <c r="L251" t="inlineStr"/>
+      <c r="M251" t="inlineStr">
         <is>
           <t>SOLICITUD DE EVALUAR INSTALACION DE RESALTOS PARABOLICOS</t>
         </is>
@@ -37336,7 +38796,8 @@
       </c>
       <c r="J252" t="inlineStr"/>
       <c r="K252" t="inlineStr"/>
-      <c r="L252" t="inlineStr">
+      <c r="L252" t="inlineStr"/>
+      <c r="M252" t="inlineStr">
         <is>
           <t>SOLICITAR ESTADO DE POLIZA SOBRE ARREGLO DE VÍA, PARA SABER SOBRE LA SEÑALIZACION EN LA VÍA</t>
         </is>
@@ -37372,7 +38833,8 @@
       </c>
       <c r="J253" t="inlineStr"/>
       <c r="K253" t="inlineStr"/>
-      <c r="L253" t="inlineStr">
+      <c r="L253" t="inlineStr"/>
+      <c r="M253" t="inlineStr">
         <is>
           <t>INCLUSIÓN DEL SEGMENTO VÍAL EN BANCO DE INICIATIVAS.</t>
         </is>
@@ -37408,7 +38870,8 @@
       </c>
       <c r="J254" t="inlineStr"/>
       <c r="K254" t="inlineStr"/>
-      <c r="L254" t="inlineStr">
+      <c r="L254" t="inlineStr"/>
+      <c r="M254" t="inlineStr">
         <is>
           <t>no hay base. COORDINAR CON LA UMV LA VIABILIDAD DE LOS RESALTOS PARABÓLICOS Y GESTIONAR CON LA ENTIDAD DE MOVILIDAD EL RESPECTIVO CONCEPTO DE VIABILIDAD.</t>
         </is>
@@ -37445,6 +38908,7 @@
       <c r="J255" t="inlineStr"/>
       <c r="K255" t="inlineStr"/>
       <c r="L255" t="inlineStr"/>
+      <c r="M255" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/kennedy_mira_consolidado.xlsx
+++ b/data/kennedy_mira_consolidado.xlsx
@@ -18,7 +18,9 @@
     <sheet name="matriz_priorizacion" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="informe_ejecutivo" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="control_calidad" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="reporte_tecnologia_kennedy" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="asignacion_puestos" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="resumen_asignacion_templos" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="reporte_tecnologia_kennedy" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -959,6 +961,9882 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:V124"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>PUESTO_ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>PUESTO</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>DIRECCION</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>BARRIO</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>UPZ</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>LATITUD</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>LONGITUD</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>IGLESIA_ACTUAL</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>TEMPLO_MAS_CERCANO</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>TEMPLO_ASIGNADO_PROPUESTO</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>DISTANCIA_MINIMA_KM</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>DIST_CLASS_ROMA_KM</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>DIST_KENNEDY_CENTRAL_KM</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>DIST_PATIO_BONITO_KM</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>DIST_CARVAJAL_KM</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>DIST_VALLADOLID_KM</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>VOTOS_2026</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>VOTOS_2023</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>VARIACION_ABSOLUTA</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>VARIACION_PORCENTUAL</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>PRIORIDAD</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>OBSERVACION_ASIGNACION</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>COL. GABRIEL BETANCOURT MEJIA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CRA. 87A # 6A-23</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>4.644292235589808</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-74.15644335036971</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>PATIO BONITO</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>VALLADOLID</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>VALLADOLID</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>1.00753934475239</v>
+      </c>
+      <c r="L2" t="n">
+        <v>3.983540464505233</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2.681748215086874</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1.846101594114285</v>
+      </c>
+      <c r="O2" t="n">
+        <v>3.578675407982128</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.00753934475239</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>188</v>
+      </c>
+      <c r="R2" t="n">
+        <v>192</v>
+      </c>
+      <c r="S2" t="n">
+        <v>-4</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-0.02083333333333333</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>COL. CLASS IED SEDE C</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CLL. 57A SUR # 78 N-21</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>4.610509909254805</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-74.17420989606875</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>CLASS ROMA</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>CLASS ROMA</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>CLASS ROMA</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>0.4811623334331136</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.4811623334331136</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.611690974232974</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3.952467374790942</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3.799441338571588</v>
+      </c>
+      <c r="P3" t="n">
+        <v>5.060024340266122</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>169.5</v>
+      </c>
+      <c r="R3" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="S3" t="n">
+        <v>-11</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-0.06094182825484765</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>COL. CAFAM BELLAVISTA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CLL. 40 SUR # 94C-50</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>4.645482340192321</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-74.17262467707668</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>PATIO BONITO</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>PATIO BONITO</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>PATIO BONITO</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>0.0747456453861397</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3.483182843840495</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2.771610028554275</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.0747456453861397</v>
+      </c>
+      <c r="O4" t="n">
+        <v>4.819537740519142</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.73387108071128</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>208</v>
+      </c>
+      <c r="R4" t="n">
+        <v>181</v>
+      </c>
+      <c r="S4" t="n">
+        <v>27</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.1491712707182321</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CENTRO COMERCIAL EL EDEN</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CRA. 72 # 12B-48</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>4.646026734930531</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-74.12916858346193</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>VALLADOLID</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>VALLADOLID</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>2.104152965784638</v>
+      </c>
+      <c r="L5" t="n">
+        <v>6.289727003515091</v>
+      </c>
+      <c r="M5" t="n">
+        <v>4.803939050458323</v>
+      </c>
+      <c r="N5" t="n">
+        <v>4.858749107358372</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3.528848056257717</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.104152965784638</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>135</v>
+      </c>
+      <c r="R5" t="n">
+        <v>155.5</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-20.5</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-0.1318327974276527</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CASABLANCA 32</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CRA. 79F # 46-16 SUR</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>4.618373742252989</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-74.16795706090684</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>0.4963146798678437</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.015996661516345</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.4963146798678437</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3.126341315802905</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3.058954386716513</v>
+      </c>
+      <c r="P6" t="n">
+        <v>3.946896956739045</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>128.5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>140</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-0.08214285714285714</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>JAIRO ANIBAL NINO</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CRA 87 H BIS # 39A-23SUR CRA 87 H BIS # 39-23SUR</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>PATIO BONITO</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>SIN COORDENADAS</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>PATIO BONITO</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="n">
+        <v>129</v>
+      </c>
+      <c r="R7" t="n">
+        <v>153</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-24</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-0.1568627450980392</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Sin coordenadas válidas; revisar manualmente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>POLIDEPORTIVO CAYETANO CANIZARES</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CRA. 80 # 39A-55 SUR</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>4.626116811687468</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-74.16023846739097</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>0.7192070571144851</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2.198991362176392</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.7192070571144851</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.628402898274735</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.449399450296685</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.764412108260535</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>126</v>
+      </c>
+      <c r="R8" t="n">
+        <v>148</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-22</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-0.1486486486486487</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>COL. HERNANDO DURAN DUSSAN</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CLL. 42F SUR # 88A-25</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>4.634929614102265</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-74.17263213502845</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>PATIO BONITO</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>PATIO BONITO</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>PATIO BONITO</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>1.235580232617679</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.321041210193308</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.692368202458507</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.235580232617679</v>
+      </c>
+      <c r="O9" t="n">
+        <v>4.123955264702889</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3.076526624051304</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>125.5</v>
+      </c>
+      <c r="R9" t="n">
+        <v>143.5</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-18</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-0.1254355400696864</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>COLEGIO NUEVA CASTILLA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CRA. 78C #8A-43</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="n">
+        <v>4.64067528612429</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-74.14189503751876</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>VALLADOLID</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>VALLADOLID</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>1.048318215675195</v>
+      </c>
+      <c r="L10" t="n">
+        <v>4.797038009293953</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3.316596386693194</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3.4994196135513</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.710423176155712</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.048318215675195</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="R10" t="n">
+        <v>147.5</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-15</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-0.1016949152542373</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>COL. DIST. MANUEL ZAPATA OLIVELLA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CLL. 1 BIS SUR # 87-84</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>4.640612761635222</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-74.16038524671931</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>PATIO BONITO</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>PATIO BONITO</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>PATIO BONITO</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>1.52341981408907</v>
+      </c>
+      <c r="L11" t="n">
+        <v>3.404535825763666</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2.160518041428967</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.52341981408907</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3.488937827215171</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.582770938848449</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>150.5</v>
+      </c>
+      <c r="R11" t="n">
+        <v>145.5</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.03436426116838488</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CENTRO DE DESARROLLO COMUNITARIO KENNEDY</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CRA. 80 # 43-43 SUR</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="n">
+        <v>4.621023401386413</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-74.16647420619317</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>0.1802292532016126</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.307316363281492</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.1802292532016126</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.873917759557415</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.93279308586488</v>
+      </c>
+      <c r="P12" t="n">
+        <v>3.610820479881535</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>134.5</v>
+      </c>
+      <c r="R12" t="n">
+        <v>133</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.0112781954887218</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>COLEGIO NELSON MANDELA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CRA. 91 # 43-98 SUR</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="n">
+        <v>4.636341511312218</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-74.1779070336277</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>PATIO BONITO</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>PATIO BONITO</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>1.206889962859002</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2.451637773468011</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2.162917996188757</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.206889962859002</v>
+      </c>
+      <c r="O13" t="n">
+        <v>4.711169495984386</v>
+      </c>
+      <c r="P13" t="n">
+        <v>3.544646044789819</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>142</v>
+      </c>
+      <c r="R13" t="n">
+        <v>127</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.1181102362204724</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Reasignación sugerida por cercanía: PATIO BONITO.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>COLEGIO CLASS I D E SEDE B ROMA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CLL.56A SUR# 78A-20</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="n">
+        <v>4.608653675647391</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-74.1711836339373</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>CLASS ROMA</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>CLASS ROMA</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>CLASS ROMA</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>0.843036061339793</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.843036061339793</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.607616981406148</v>
+      </c>
+      <c r="N14" t="n">
+        <v>4.161544609906549</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3.513873288336299</v>
+      </c>
+      <c r="P14" t="n">
+        <v>5.052518894029468</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>109</v>
+      </c>
+      <c r="R14" t="n">
+        <v>125</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-16</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-0.128</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>COLEGIO ALFONSO LOPEZ PUMAREJO</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CRA. 72G # 39-99 SUR</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="n">
+        <v>4.607911118698036</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-74.14369350793383</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>1.004867935809037</v>
+      </c>
+      <c r="L15" t="n">
+        <v>3.672646621054015</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2.819323065549961</v>
+      </c>
+      <c r="N15" t="n">
+        <v>5.341074751350236</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.004867935809037</v>
+      </c>
+      <c r="P15" t="n">
+        <v>4.463845660902213</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>136.5</v>
+      </c>
+      <c r="R15" t="n">
+        <v>130.5</v>
+      </c>
+      <c r="S15" t="n">
+        <v>6</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.04597701149425287</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SUPERIOR AMERICANO</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CRA. 71C # 3A-41</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="n">
+        <v>4.626251664751758</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-74.13582560619315</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>1.214327152876638</v>
+      </c>
+      <c r="L16" t="n">
+        <v>4.665268550766148</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.273836215190995</v>
+      </c>
+      <c r="N16" t="n">
+        <v>4.671396758878715</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.214327152876638</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.755342715473075</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="R16" t="n">
+        <v>128.5</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-16</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-0.1245136186770428</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CENTRO COMERCIAL TINTAL PLAZA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AV. CRA. 86 # 6-37</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="n">
+        <v>4.642371700793638</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-74.15621391783964</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>PATIO BONITO</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>VALLADOLID</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>VALLADOLID</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>1.087027032840975</v>
+      </c>
+      <c r="L17" t="n">
+        <v>3.821598720116154</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2.493035404316083</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1.905385047003306</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3.381654310228411</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.087027032840975</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>112</v>
+      </c>
+      <c r="R17" t="n">
+        <v>123</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-11</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-0.08943089430894309</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>COL. DIST. SAN JOSE IED SEDE A</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CLL. 42A SUR # 79D-37</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="n">
+        <v>4.621579248090049</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-74.16301692433507</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>0.2221615084966937</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.666355745125991</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.2221615084966937</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.936194973884385</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.569886012639742</v>
+      </c>
+      <c r="P18" t="n">
+        <v>3.355159620727086</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>128.5</v>
+      </c>
+      <c r="R18" t="n">
+        <v>122</v>
+      </c>
+      <c r="S18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.05327868852459016</v>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>COLEGIO OEA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CRA. 72L #34-19 SUR</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="n">
+        <v>4.618405160388168</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-74.14258030996405</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>0.330456410987276</v>
+      </c>
+      <c r="L19" t="n">
+        <v>3.752379697970258</v>
+      </c>
+      <c r="M19" t="n">
+        <v>2.513994208918924</v>
+      </c>
+      <c r="N19" t="n">
+        <v>4.56203637313176</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.330456410987276</v>
+      </c>
+      <c r="P19" t="n">
+        <v>3.326632817348134</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>118.5</v>
+      </c>
+      <c r="R19" t="n">
+        <v>121</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-0.02066115702479339</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>COLEGIO LA AMISTAD</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CRA. 78 # 35-30 SUR</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="n">
+        <v>4.623344078629173</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-74.1481965051552</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>1.160327613920861</v>
+      </c>
+      <c r="L20" t="n">
+        <v>3.259701239558222</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.872575641665486</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3.732068341271538</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.160327613920861</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.721397193890543</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="R20" t="n">
+        <v>114</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-13.5</v>
+      </c>
+      <c r="T20" t="n">
+        <v>-0.1184210526315789</v>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Reasignación sugerida por cercanía: CARVAJAL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>COL. EDUARDO UMANA LUNA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CRA. 93A # 42A-37 SUR</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="n">
+        <v>4.64188255738029</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-74.17488453148712</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>PATIO BONITO</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>PATIO BONITO</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>PATIO BONITO</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>0.506401524957607</v>
+      </c>
+      <c r="L21" t="n">
+        <v>3.063822334383916</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2.492720538415028</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.506401524957607</v>
+      </c>
+      <c r="O21" t="n">
+        <v>4.758607650453425</v>
+      </c>
+      <c r="P21" t="n">
+        <v>3.044371831077259</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>118</v>
+      </c>
+      <c r="R21" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="T21" t="n">
+        <v>-0.02074688796680498</v>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>COL. DIST. CLASS SEDE A</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CRA. 80I # 57B-50 SUR</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="n">
+        <v>4.614244894271299</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-74.17897390381921</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>CLASS ROMA</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>CLASS ROMA</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>CLASS ROMA</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>0.3086001798407338</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.3086001798407338</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.757249895430369</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3.596212745374857</v>
+      </c>
+      <c r="O22" t="n">
+        <v>4.278035099503642</v>
+      </c>
+      <c r="P22" t="n">
+        <v>5.066439020661386</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="R22" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="S22" t="n">
+        <v>-24</v>
+      </c>
+      <c r="T22" t="n">
+        <v>-0.1991701244813278</v>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>BRITALIA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CLL. 47A SUR # 82-99</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="n">
+        <v>4.625302318772165</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-74.17293288727228</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>0.9628803782134904</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.269239757937547</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.9628803782134904</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.30539784230573</v>
+      </c>
+      <c r="O23" t="n">
+        <v>3.73729766154521</v>
+      </c>
+      <c r="P23" t="n">
+        <v>3.723170952931024</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>118.5</v>
+      </c>
+      <c r="R23" t="n">
+        <v>114.5</v>
+      </c>
+      <c r="S23" t="n">
+        <v>4</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.03493449781659388</v>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>FRANCISCO MIRANDA</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>DIAG. 41 SUR # 73A-80</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="n">
+        <v>4.612660586868968</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-74.15436210977813</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>1.553392277044595</v>
+      </c>
+      <c r="L24" t="n">
+        <v>2.426869591991916</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.553392277044595</v>
+      </c>
+      <c r="N24" t="n">
+        <v>4.247703741925769</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.5972263423294</v>
+      </c>
+      <c r="P24" t="n">
+        <v>3.971046052223503</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="R24" t="n">
+        <v>107</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-18.5</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.1728971962616822</v>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>COLEGIO GUSTAVO ROJAS PINILLA</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CLL. 11B # 80B-61</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="n">
+        <v>4.648881528200116</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-74.14107806491462</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>VALLADOLID</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>VALLADOLID</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>0.783759199572664</v>
+      </c>
+      <c r="L25" t="n">
+        <v>5.466333190258233</v>
+      </c>
+      <c r="M25" t="n">
+        <v>4.018381975075621</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.552945004760073</v>
+      </c>
+      <c r="O25" t="n">
+        <v>3.618773484150638</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.783759199572664</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>115.5</v>
+      </c>
+      <c r="R25" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="S25" t="n">
+        <v>8</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.07441860465116279</v>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>COLEGIO JAIME GARZON</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>TRV. 85A# 49-45 SUR</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="n">
+        <v>4.626030831642272</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-74.17546202049152</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>CLASS ROMA</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>1.252380169397706</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.300281479749882</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.252380169397706</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2.240936497598265</v>
+      </c>
+      <c r="O26" t="n">
+        <v>4.029060832783713</v>
+      </c>
+      <c r="P26" t="n">
+        <v>3.884120340570138</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>143.5</v>
+      </c>
+      <c r="R26" t="n">
+        <v>115</v>
+      </c>
+      <c r="S26" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.2478260869565218</v>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Reasignación sugerida por cercanía: KENNEDY CENTRAL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>MANDALAY - COLEGIO KENNEDY</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CLL. 5 SUR # 72A-69</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="n">
+        <v>4.620510353378262</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-74.14118429746844</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>0.4707609253983733</v>
+      </c>
+      <c r="L27" t="n">
+        <v>3.939853987701996</v>
+      </c>
+      <c r="M27" t="n">
+        <v>2.644767860271953</v>
+      </c>
+      <c r="N27" t="n">
+        <v>4.527258697117214</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.4707609253983733</v>
+      </c>
+      <c r="P27" t="n">
+        <v>3.130858408533069</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="R27" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>LA FLORESTA SUR</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CRA. 68B BIS# 1-09 SUR</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="n">
+        <v>4.622583250049652</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-74.12711239211473</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>1.631272769642787</v>
+      </c>
+      <c r="L28" t="n">
+        <v>5.515998897485674</v>
+      </c>
+      <c r="M28" t="n">
+        <v>4.201919949317947</v>
+      </c>
+      <c r="N28" t="n">
+        <v>5.716202813254837</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.631272769642787</v>
+      </c>
+      <c r="P28" t="n">
+        <v>3.642530784308035</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>90</v>
+      </c>
+      <c r="R28" t="n">
+        <v>98</v>
+      </c>
+      <c r="S28" t="n">
+        <v>-8</v>
+      </c>
+      <c r="T28" t="n">
+        <v>-0.08163265306122448</v>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>COL DE TIMIZA</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CRA.74 # 42G-52 SUR</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="n">
+        <v>4.610028365990958</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-74.15842867735786</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>1.492791419901812</v>
+      </c>
+      <c r="L29" t="n">
+        <v>2.026845950294253</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.492791419901812</v>
+      </c>
+      <c r="N29" t="n">
+        <v>4.317559412968742</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2.114555365949149</v>
+      </c>
+      <c r="P29" t="n">
+        <v>4.356050202403189</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>95</v>
+      </c>
+      <c r="R29" t="n">
+        <v>98</v>
+      </c>
+      <c r="S29" t="n">
+        <v>-3</v>
+      </c>
+      <c r="T29" t="n">
+        <v>-0.03061224489795918</v>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>VISION DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CRA. 79 C # 13A-40</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="n">
+        <v>4.650763509151811</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-74.13536108917161</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>VALLADOLID</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>VALLADOLID</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>1.445975186873295</v>
+      </c>
+      <c r="L30" t="n">
+        <v>6.071606137981414</v>
+      </c>
+      <c r="M30" t="n">
+        <v>4.6062739342785</v>
+      </c>
+      <c r="N30" t="n">
+        <v>4.205418534167157</v>
+      </c>
+      <c r="O30" t="n">
+        <v>3.868392483668318</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.445975186873295</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>92</v>
+      </c>
+      <c r="R30" t="n">
+        <v>91.5</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0.00546448087431694</v>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>CATALINA</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CLL. 52A SUR # 77W-05</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="n">
+        <v>4.610163448985827</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-74.16882050372209</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>CLASS ROMA</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>CLASS ROMA</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>0.9408702676285158</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.9408702676285158</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.3544550501783</v>
+      </c>
+      <c r="N31" t="n">
+        <v>4.015663434638409</v>
+      </c>
+      <c r="O31" t="n">
+        <v>3.220499210284587</v>
+      </c>
+      <c r="P31" t="n">
+        <v>4.77708847995658</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>87</v>
+      </c>
+      <c r="R31" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="S31" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="T31" t="n">
+        <v>-0.1076923076923077</v>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Reasignación sugerida por cercanía: CLASS ROMA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>MILENIO PLAZA</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>AV. C. DE CALI # 42B-51 SUR</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="n">
+        <v>4.629983671874888</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-74.16920110619316</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>PATIO BONITO</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>1.02751060711853</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.902248430786002</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.02751060711853</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1.834041948629808</v>
+      </c>
+      <c r="O32" t="n">
+        <v>3.530832368371214</v>
+      </c>
+      <c r="P32" t="n">
+        <v>3.068877958767579</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="R32" t="n">
+        <v>89</v>
+      </c>
+      <c r="S32" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="T32" t="n">
+        <v>-0.1179775280898876</v>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Reasignación sugerida por cercanía: KENNEDY CENTRAL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>COL. DIST. VILLA RICA SEDE A</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CRA. 77K BIS A # 50-26 SUR</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="n">
+        <v>4.605787476319285</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-74.16695696308949</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>CLASS ROMA</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>CLASS ROMA</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>1.398664633453733</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.398664633453733</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.786706668573383</v>
+      </c>
+      <c r="N33" t="n">
+        <v>4.525312411103004</v>
+      </c>
+      <c r="O33" t="n">
+        <v>3.165458776852683</v>
+      </c>
+      <c r="P33" t="n">
+        <v>5.120997128467862</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="R33" t="n">
+        <v>88</v>
+      </c>
+      <c r="S33" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="T33" t="n">
+        <v>-0.1420454545454546</v>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Reasignación sugerida por cercanía: CLASS ROMA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ALMENAR</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>SALON COMUNAL ALMENAR</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="n">
+        <v>4.619939810553133</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-74.17035065790459</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>0.6242832813148107</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.8967336898568259</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.6242832813148107</v>
+      </c>
+      <c r="N34" t="n">
+        <v>2.91657938112859</v>
+      </c>
+      <c r="O34" t="n">
+        <v>3.339927252547326</v>
+      </c>
+      <c r="P34" t="n">
+        <v>3.963321663294743</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>75</v>
+      </c>
+      <c r="R34" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="S34" t="n">
+        <v>-15.5</v>
+      </c>
+      <c r="T34" t="n">
+        <v>-0.1712707182320442</v>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>COL. DIST SALUDCOOP SUR</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CRA. 89 # 26-03 SUR</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="n">
+        <v>4.642868768241949</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-74.16414185446558</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>PATIO BONITO</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>PATIO BONITO</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>PATIO BONITO</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>1.043848903850548</v>
+      </c>
+      <c r="L35" t="n">
+        <v>3.439901084235772</v>
+      </c>
+      <c r="M35" t="n">
+        <v>2.351548658959572</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1.043848903850548</v>
+      </c>
+      <c r="O35" t="n">
+        <v>3.950227267424228</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.864432101236587</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>107</v>
+      </c>
+      <c r="R35" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="S35" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0.2090395480225989</v>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>COLEGIO ALQUERIA</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CLL. 37B SUR # 68D-93</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="n">
+        <v>4.605372323163491</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-74.13606089082896</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>1.312651936000702</v>
+      </c>
+      <c r="L36" t="n">
+        <v>4.558820985030971</v>
+      </c>
+      <c r="M36" t="n">
+        <v>3.689216588478159</v>
+      </c>
+      <c r="N36" t="n">
+        <v>6.100239561431183</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1.312651936000702</v>
+      </c>
+      <c r="P36" t="n">
+        <v>4.903780378574937</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>72</v>
+      </c>
+      <c r="R36" t="n">
+        <v>82</v>
+      </c>
+      <c r="S36" t="n">
+        <v>-10</v>
+      </c>
+      <c r="T36" t="n">
+        <v>-0.1219512195121951</v>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>MANUEL CEPEDA</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CLL. 56 SUR #81-26</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="n">
+        <v>4.616834944420529</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-74.17744634776071</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>CLASS ROMA</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>CLASS ROMA</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>CLASS ROMA</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>0.3083483130646937</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.3083483130646937</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.481786733499345</v>
+      </c>
+      <c r="N37" t="n">
+        <v>3.28395586258303</v>
+      </c>
+      <c r="O37" t="n">
+        <v>4.102716934323538</v>
+      </c>
+      <c r="P37" t="n">
+        <v>4.740281719257915</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="R37" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="S37" t="n">
+        <v>9</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0.1104294478527607</v>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>LA CHUCUA</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CRA. 72I # 42F-54 SUR</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="n">
+        <v>4.604010418208003</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-74.14860444077195</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>1.643454278001587</v>
+      </c>
+      <c r="L38" t="n">
+        <v>3.267060685106916</v>
+      </c>
+      <c r="M38" t="n">
+        <v>2.682210518412818</v>
+      </c>
+      <c r="N38" t="n">
+        <v>5.399263760834875</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1.643454278001587</v>
+      </c>
+      <c r="P38" t="n">
+        <v>4.871527043571213</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="R38" t="n">
+        <v>85</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0.06470588235294118</v>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>LAS AMERICAS SEDE A</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CRA. 73C BIS # 38C-84 SUR</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="n">
+        <v>4.61668376392881</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-74.15003484853374</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>1.064894837308976</v>
+      </c>
+      <c r="L39" t="n">
+        <v>2.910600112549991</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.752869930370583</v>
+      </c>
+      <c r="N39" t="n">
+        <v>4.139448348406922</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1.064894837308976</v>
+      </c>
+      <c r="P39" t="n">
+        <v>3.468803954345051</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="R39" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="S39" t="n">
+        <v>29</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0.3945578231292517</v>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>SANTA MARIA DE KENNEDY</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>CLL. 51C SUR # 82A-09</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="n">
+        <v>4.622665445870914</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-74.17637706882167</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>CLASS ROMA</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>CLASS ROMA</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>CLASS ROMA</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>0.9237762874399515</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.9237762874399515</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1.263505355117962</v>
+      </c>
+      <c r="N40" t="n">
+        <v>2.625273258738235</v>
+      </c>
+      <c r="O40" t="n">
+        <v>4.04537046931733</v>
+      </c>
+      <c r="P40" t="n">
+        <v>4.203058818961592</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>76</v>
+      </c>
+      <c r="R40" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="S40" t="n">
+        <v>-20.5</v>
+      </c>
+      <c r="T40" t="n">
+        <v>-0.2124352331606218</v>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>COLEGIO RODRIGO TRIANA</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>CLL. 38B # 89-81 SUR</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="n">
+        <v>4.640797981546184</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-74.16786927169738</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>PATIO BONITO</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>PATIO BONITO</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>PATIO BONITO</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>0.814576743128466</v>
+      </c>
+      <c r="L41" t="n">
+        <v>3.081112873090184</v>
+      </c>
+      <c r="M41" t="n">
+        <v>2.14277580000271</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0.814576743128466</v>
+      </c>
+      <c r="O41" t="n">
+        <v>4.079315807474546</v>
+      </c>
+      <c r="P41" t="n">
+        <v>2.329168363243517</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>101</v>
+      </c>
+      <c r="R41" t="n">
+        <v>81</v>
+      </c>
+      <c r="S41" t="n">
+        <v>20</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0.2469135802469136</v>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>COLEGIO TOM ADAMS</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CLL. 40J SUR # 78-08</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="n">
+        <v>4.61832449920057</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-74.15566785553233</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>1.103348009423426</v>
+      </c>
+      <c r="L42" t="n">
+        <v>2.317098464004602</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1.103348009423426</v>
+      </c>
+      <c r="N42" t="n">
+        <v>3.63151897943516</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1.702857875586381</v>
+      </c>
+      <c r="P42" t="n">
+        <v>3.385929214057551</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>74</v>
+      </c>
+      <c r="R42" t="n">
+        <v>76</v>
+      </c>
+      <c r="S42" t="n">
+        <v>-2</v>
+      </c>
+      <c r="T42" t="n">
+        <v>-0.02631578947368421</v>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>SAN JOSE DE CASTILLA SEDE A</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>CLL. 7C # 78F-20</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="n">
+        <v>4.638262101667564</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-74.14395295672919</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>VALLADOLID</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>VALLADOLID</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>1.156331805228261</v>
+      </c>
+      <c r="L43" t="n">
+        <v>4.453232377978924</v>
+      </c>
+      <c r="M43" t="n">
+        <v>2.970677765526562</v>
+      </c>
+      <c r="N43" t="n">
+        <v>3.334197782175878</v>
+      </c>
+      <c r="O43" t="n">
+        <v>2.468268067622548</v>
+      </c>
+      <c r="P43" t="n">
+        <v>1.156331805228261</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>74</v>
+      </c>
+      <c r="R43" t="n">
+        <v>77</v>
+      </c>
+      <c r="S43" t="n">
+        <v>-3</v>
+      </c>
+      <c r="T43" t="n">
+        <v>-0.03896103896103896</v>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>SAN FRANCISCO EN EL TINTAL</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>CLL. 6D # 90-51</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="n">
+        <v>4.650375398080754</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-74.15787281968693</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>PATIO BONITO</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>VALLADOLID</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>VALLADOLID</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>1.123163785054512</v>
+      </c>
+      <c r="L44" t="n">
+        <v>4.490027175554745</v>
+      </c>
+      <c r="M44" t="n">
+        <v>3.281169954996872</v>
+      </c>
+      <c r="N44" t="n">
+        <v>1.745511790790106</v>
+      </c>
+      <c r="O44" t="n">
+        <v>4.249243541989141</v>
+      </c>
+      <c r="P44" t="n">
+        <v>1.123163785054512</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="R44" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="S44" t="n">
+        <v>-6</v>
+      </c>
+      <c r="T44" t="n">
+        <v>-0.08391608391608392</v>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>PROSPERO PINZON</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>CLL. 35C SUR # 78F-81</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="n">
+        <v>4.624491888361685</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-74.15109401078229</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>1.489008204672017</v>
+      </c>
+      <c r="L45" t="n">
+        <v>3.001194032449666</v>
+      </c>
+      <c r="M45" t="n">
+        <v>1.57298524512399</v>
+      </c>
+      <c r="N45" t="n">
+        <v>3.41137589553263</v>
+      </c>
+      <c r="O45" t="n">
+        <v>1.489008204672017</v>
+      </c>
+      <c r="P45" t="n">
+        <v>2.615310279048182</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="R45" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="S45" t="n">
+        <v>13</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0.1870503597122302</v>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Reasignación sugerida por cercanía: CARVAJAL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>FRANCISCO JOSE DE CALDAS - INEM SEDE B</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>CLL. 35C SUR # 78N-10</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="n">
+        <v>4.625554824843849</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-74.15577213884154</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>1.108820747082247</v>
+      </c>
+      <c r="L46" t="n">
+        <v>2.582962585783237</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1.108820747082247</v>
+      </c>
+      <c r="N46" t="n">
+        <v>2.97244486217045</v>
+      </c>
+      <c r="O46" t="n">
+        <v>1.984801962126318</v>
+      </c>
+      <c r="P46" t="n">
+        <v>2.618624190762575</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="R46" t="n">
+        <v>65</v>
+      </c>
+      <c r="S46" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="T46" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>EL JAPON</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>CRA. 78G # 38C-11 SUR</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="n">
+        <v>4.622299344856946</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-74.15353563360081</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>1.273822105856583</v>
+      </c>
+      <c r="L47" t="n">
+        <v>2.661761155761838</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1.273822105856583</v>
+      </c>
+      <c r="N47" t="n">
+        <v>3.409355416770265</v>
+      </c>
+      <c r="O47" t="n">
+        <v>1.596102988632322</v>
+      </c>
+      <c r="P47" t="n">
+        <v>2.901495559086646</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>66</v>
+      </c>
+      <c r="R47" t="n">
+        <v>70</v>
+      </c>
+      <c r="S47" t="n">
+        <v>-4</v>
+      </c>
+      <c r="T47" t="n">
+        <v>-0.05714285714285714</v>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>MARSELLA</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>CRA. 69 # 7-90</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="n">
+        <v>4.631839502311857</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-74.12713447920518</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>2.267466170043467</v>
+      </c>
+      <c r="L48" t="n">
+        <v>5.774157095278324</v>
+      </c>
+      <c r="M48" t="n">
+        <v>4.346033229030899</v>
+      </c>
+      <c r="N48" t="n">
+        <v>5.323634881290279</v>
+      </c>
+      <c r="O48" t="n">
+        <v>2.267466170043467</v>
+      </c>
+      <c r="P48" t="n">
+        <v>2.922308373693</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>65</v>
+      </c>
+      <c r="R48" t="n">
+        <v>67</v>
+      </c>
+      <c r="S48" t="n">
+        <v>-2</v>
+      </c>
+      <c r="T48" t="n">
+        <v>-0.02985074626865672</v>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>COL. RODRIGO DE TRIANA SEDE B</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>CRA. 90A # 39-12 SUR</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="n">
+        <v>4.641005331911792</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-74.16956856715331</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>PATIO BONITO</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>PATIO BONITO</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>PATIO BONITO</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>0.6768639394987797</v>
+      </c>
+      <c r="L49" t="n">
+        <v>3.052436287956858</v>
+      </c>
+      <c r="M49" t="n">
+        <v>2.200994027379338</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0.6768639394987797</v>
+      </c>
+      <c r="O49" t="n">
+        <v>4.236461854376202</v>
+      </c>
+      <c r="P49" t="n">
+        <v>2.500322597570558</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>63</v>
+      </c>
+      <c r="R49" t="n">
+        <v>71</v>
+      </c>
+      <c r="S49" t="n">
+        <v>-8</v>
+      </c>
+      <c r="T49" t="n">
+        <v>-0.1126760563380282</v>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>LOS PERIODISTAS</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>CLL. 41C SUR # 78H-85</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="n">
+        <v>4.61764013957111</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-74.15832380161244</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>0.8704497149580287</v>
+      </c>
+      <c r="L50" t="n">
+        <v>2.013715262465246</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0.8704497149580287</v>
+      </c>
+      <c r="N50" t="n">
+        <v>3.552163278646252</v>
+      </c>
+      <c r="O50" t="n">
+        <v>1.988155379920652</v>
+      </c>
+      <c r="P50" t="n">
+        <v>3.542867807231943</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>59</v>
+      </c>
+      <c r="R50" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="S50" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="T50" t="n">
+        <v>-0.1386861313868613</v>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>PIO XII - SEDE COLEGIO ISABEL II</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>CRA. 79F # 6B-30/34</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="n">
+        <v>4.635209261647902</v>
+      </c>
+      <c r="G51" t="n">
+        <v>-74.15164846765055</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>VALLADOLID</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>VALLADOLID</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>1.457063006675804</v>
+      </c>
+      <c r="L51" t="n">
+        <v>3.574130411090262</v>
+      </c>
+      <c r="M51" t="n">
+        <v>2.106716208374196</v>
+      </c>
+      <c r="N51" t="n">
+        <v>2.655813882369778</v>
+      </c>
+      <c r="O51" t="n">
+        <v>2.438412650888681</v>
+      </c>
+      <c r="P51" t="n">
+        <v>1.457063006675804</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="R51" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="S51" t="n">
+        <v>11</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0.1848739495798319</v>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>CODEMA</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>COL. DIST. CODEMA</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="n">
+        <v>4.648603178621415</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-74.16533739303424</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>PATIO BONITO</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>PATIO BONITO</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>PATIO BONITO</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>0.8968489712247996</v>
+      </c>
+      <c r="L52" t="n">
+        <v>3.993220281150375</v>
+      </c>
+      <c r="M52" t="n">
+        <v>2.987407667431121</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0.8968489712247996</v>
+      </c>
+      <c r="O52" t="n">
+        <v>4.526160949964408</v>
+      </c>
+      <c r="P52" t="n">
+        <v>1.915849547945653</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>80</v>
+      </c>
+      <c r="R52" t="n">
+        <v>62</v>
+      </c>
+      <c r="S52" t="n">
+        <v>18</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0.2903225806451613</v>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>BOITA</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>CLL.48B # 72K-13 SUR</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="n">
+        <v>4.602492214734755</v>
+      </c>
+      <c r="G53" t="n">
+        <v>-74.1526821503699</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
+        <v>2.053141417239636</v>
+      </c>
+      <c r="L53" t="n">
+        <v>2.920813801769557</v>
+      </c>
+      <c r="M53" t="n">
+        <v>2.53939301991372</v>
+      </c>
+      <c r="N53" t="n">
+        <v>5.340201001717823</v>
+      </c>
+      <c r="O53" t="n">
+        <v>2.053141417239636</v>
+      </c>
+      <c r="P53" t="n">
+        <v>5.065851344724463</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>59</v>
+      </c>
+      <c r="R53" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="S53" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="T53" t="n">
+        <v>-0.112781954887218</v>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>INEM FRANCISCO DE PAULA SANTANDER SEDE A</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>CLL. 38C SUR # 79-08</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="n">
+        <v>4.625499797629267</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-74.15584906868284</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
+        <v>1.098604485931941</v>
+      </c>
+      <c r="L54" t="n">
+        <v>2.572543218058225</v>
+      </c>
+      <c r="M54" t="n">
+        <v>1.098604485931941</v>
+      </c>
+      <c r="N54" t="n">
+        <v>2.97167155210033</v>
+      </c>
+      <c r="O54" t="n">
+        <v>1.98897117496233</v>
+      </c>
+      <c r="P54" t="n">
+        <v>2.627195451005466</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="R54" t="n">
+        <v>65</v>
+      </c>
+      <c r="S54" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0.2692307692307692</v>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>COLEGIO DARIO ECHANDIA</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>CLL. 5A SUR# 88B-08</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="n">
+        <v>4.64197230074716</v>
+      </c>
+      <c r="G55" t="n">
+        <v>-74.16214952656186</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>PATIO BONITO</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>PATIO BONITO</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>PATIO BONITO</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
+        <v>1.285487540524145</v>
+      </c>
+      <c r="L55" t="n">
+        <v>3.442300378636511</v>
+      </c>
+      <c r="M55" t="n">
+        <v>2.272178066392884</v>
+      </c>
+      <c r="N55" t="n">
+        <v>1.285487540524145</v>
+      </c>
+      <c r="O55" t="n">
+        <v>3.730214956726898</v>
+      </c>
+      <c r="P55" t="n">
+        <v>1.690512916936935</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="R55" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="S55" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>-0.01550387596899225</v>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>FLORALIA</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>TRV. 68C # 31-26 SUR</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="n">
+        <v>4.608715454384933</v>
+      </c>
+      <c r="G56" t="n">
+        <v>-74.13254489269919</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>1.218105534587033</v>
+      </c>
+      <c r="L56" t="n">
+        <v>4.878163498293284</v>
+      </c>
+      <c r="M56" t="n">
+        <v>3.879231249916</v>
+      </c>
+      <c r="N56" t="n">
+        <v>6.110055441036693</v>
+      </c>
+      <c r="O56" t="n">
+        <v>1.218105534587033</v>
+      </c>
+      <c r="P56" t="n">
+        <v>4.676037518031997</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="R56" t="n">
+        <v>60</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0.008333333333333333</v>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>CARLOS ARTURO TORRES</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>TV. 72B # 44C-19 SUR</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="n">
+        <v>4.599621193332875</v>
+      </c>
+      <c r="G57" t="n">
+        <v>-74.1464112673422</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>1.97396692272352</v>
+      </c>
+      <c r="L57" t="n">
+        <v>3.685224736906305</v>
+      </c>
+      <c r="M57" t="n">
+        <v>3.209368159720915</v>
+      </c>
+      <c r="N57" t="n">
+        <v>5.943538874542416</v>
+      </c>
+      <c r="O57" t="n">
+        <v>1.97396692272352</v>
+      </c>
+      <c r="P57" t="n">
+        <v>5.362372890882339</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="R57" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="S57" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>-0.01481481481481482</v>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>EL SAUCEDAL</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>CRA. 83 # 38B-12 SUR</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="n">
+        <v>4.633263094276227</v>
+      </c>
+      <c r="G58" t="n">
+        <v>-74.16291842463268</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
+        <v>1.302351841906548</v>
+      </c>
+      <c r="L58" t="n">
+        <v>2.565633964643553</v>
+      </c>
+      <c r="M58" t="n">
+        <v>1.302351841906548</v>
+      </c>
+      <c r="N58" t="n">
+        <v>1.807615394475423</v>
+      </c>
+      <c r="O58" t="n">
+        <v>3.122548312121617</v>
+      </c>
+      <c r="P58" t="n">
+        <v>2.308219202041787</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="R58" t="n">
+        <v>61</v>
+      </c>
+      <c r="S58" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="T58" t="n">
+        <v>-0.1885245901639344</v>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>COLEGIO C.E.L.C.O. SAN LUCAS</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>CLL. 35A SUR # 78I-21</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="n">
+        <v>4.625249426895294</v>
+      </c>
+      <c r="G59" t="n">
+        <v>-74.15120478836998</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
+        <v>1.551144331493847</v>
+      </c>
+      <c r="L59" t="n">
+        <v>3.022565221745928</v>
+      </c>
+      <c r="M59" t="n">
+        <v>1.579624759647571</v>
+      </c>
+      <c r="N59" t="n">
+        <v>3.34387779569332</v>
+      </c>
+      <c r="O59" t="n">
+        <v>1.551144331493847</v>
+      </c>
+      <c r="P59" t="n">
+        <v>2.533449041480816</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>52</v>
+      </c>
+      <c r="R59" t="n">
+        <v>53</v>
+      </c>
+      <c r="S59" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>-0.01886792452830189</v>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Reasignación sugerida por cercanía: CARVAJAL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>VILLA ADRIANA</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>CLL. 20 SUR # 68D-36</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="n">
+        <v>4.613191433382651</v>
+      </c>
+      <c r="G60" t="n">
+        <v>-74.12907884375181</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="K60" t="n">
+        <v>1.306319385179546</v>
+      </c>
+      <c r="L60" t="n">
+        <v>5.223379293360082</v>
+      </c>
+      <c r="M60" t="n">
+        <v>4.09477255655753</v>
+      </c>
+      <c r="N60" t="n">
+        <v>6.086277353834831</v>
+      </c>
+      <c r="O60" t="n">
+        <v>1.306319385179546</v>
+      </c>
+      <c r="P60" t="n">
+        <v>4.387988699984429</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>40</v>
+      </c>
+      <c r="R60" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="S60" t="n">
+        <v>-16.5</v>
+      </c>
+      <c r="T60" t="n">
+        <v>-0.2920353982300885</v>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>COL. DIST VILLA RICA-SEDE B</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>CLL. 49 SUR # 78-35</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="n">
+        <v>4.611236024664688</v>
+      </c>
+      <c r="G61" t="n">
+        <v>-74.16629103502849</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>CLASS ROMA</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>CLASS ROMA</t>
+        </is>
+      </c>
+      <c r="K61" t="n">
+        <v>1.151026358750785</v>
+      </c>
+      <c r="L61" t="n">
+        <v>1.151026358750785</v>
+      </c>
+      <c r="M61" t="n">
+        <v>1.176376502429712</v>
+      </c>
+      <c r="N61" t="n">
+        <v>3.940454825662657</v>
+      </c>
+      <c r="O61" t="n">
+        <v>2.921702401510622</v>
+      </c>
+      <c r="P61" t="n">
+        <v>4.541486453502494</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>75</v>
+      </c>
+      <c r="R61" t="n">
+        <v>57</v>
+      </c>
+      <c r="S61" t="n">
+        <v>18</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Reasignación sugerida por cercanía: CLASS ROMA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>ESC. TECNOLOGICA INST. TECNICO CENTRAL</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>CLL. 6C # 94A-25</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="n">
+        <v>4.656625444678493</v>
+      </c>
+      <c r="G62" t="n">
+        <v>-74.16171204824929</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>PATIO BONITO</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>PATIO BONITO</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>PATIO BONITO</t>
+        </is>
+      </c>
+      <c r="K62" t="n">
+        <v>1.718757380328138</v>
+      </c>
+      <c r="L62" t="n">
+        <v>4.966176522386207</v>
+      </c>
+      <c r="M62" t="n">
+        <v>3.896463156243561</v>
+      </c>
+      <c r="N62" t="n">
+        <v>1.718757380328138</v>
+      </c>
+      <c r="O62" t="n">
+        <v>5.062093706247037</v>
+      </c>
+      <c r="P62" t="n">
+        <v>1.801514876478667</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="R62" t="n">
+        <v>47</v>
+      </c>
+      <c r="S62" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="T62" t="n">
+        <v>0.4148936170212766</v>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>COLEGIO SAN PEDRO CLAVER SEDE A</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>CRA. 79C # 41B-51 SUR</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="n">
+        <v>4.622110317101393</v>
+      </c>
+      <c r="G63" t="n">
+        <v>-74.16068121747188</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="K63" t="n">
+        <v>0.4821011675777849</v>
+      </c>
+      <c r="L63" t="n">
+        <v>1.923043185329621</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0.4821011675777849</v>
+      </c>
+      <c r="N63" t="n">
+        <v>2.990635574534235</v>
+      </c>
+      <c r="O63" t="n">
+        <v>2.334010877421969</v>
+      </c>
+      <c r="P63" t="n">
+        <v>3.182022652027373</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>56</v>
+      </c>
+      <c r="R63" t="n">
+        <v>51</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0.09803921568627451</v>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>LOS HEROES</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>CLL. 35B SUR # 73A-40 INT.1</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="n">
+        <v>4.620579149364705</v>
+      </c>
+      <c r="G64" t="n">
+        <v>-74.14512737181559</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="K64" t="n">
+        <v>0.7018154551789459</v>
+      </c>
+      <c r="L64" t="n">
+        <v>3.511780082584993</v>
+      </c>
+      <c r="M64" t="n">
+        <v>2.207981778290769</v>
+      </c>
+      <c r="N64" t="n">
+        <v>4.190569067414922</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0.7018154551789459</v>
+      </c>
+      <c r="P64" t="n">
+        <v>3.046301146317357</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="R64" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="S64" t="n">
+        <v>3</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0.06315789473684211</v>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Reasignación sugerida por cercanía: CARVAJAL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>JOHN F. KENNEDY</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>CRA. 74B # 38A-35 SUR</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="n">
+        <v>4.619523053234511</v>
+      </c>
+      <c r="G65" t="n">
+        <v>-74.15045676386379</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="K65" t="n">
+        <v>1.165882852718897</v>
+      </c>
+      <c r="L65" t="n">
+        <v>2.909545337078077</v>
+      </c>
+      <c r="M65" t="n">
+        <v>1.632240612508917</v>
+      </c>
+      <c r="N65" t="n">
+        <v>3.864962000879169</v>
+      </c>
+      <c r="O65" t="n">
+        <v>1.165882852718897</v>
+      </c>
+      <c r="P65" t="n">
+        <v>3.157350588476849</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>46</v>
+      </c>
+      <c r="R65" t="n">
+        <v>46</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Reasignación sugerida por cercanía: CARVAJAL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>CC PLAZA DE LAS AMERICAS</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>CRA. 71D # 6-94 SUR</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="n">
+        <v>4.61910860349318</v>
+      </c>
+      <c r="G66" t="n">
+        <v>-74.13509740518676</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="K66" t="n">
+        <v>0.6665124821171102</v>
+      </c>
+      <c r="L66" t="n">
+        <v>4.585186832171606</v>
+      </c>
+      <c r="M66" t="n">
+        <v>3.328745109170061</v>
+      </c>
+      <c r="N66" t="n">
+        <v>5.159380921360872</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0.6665124821171102</v>
+      </c>
+      <c r="P66" t="n">
+        <v>3.501107805920398</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>56</v>
+      </c>
+      <c r="R66" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="T66" t="n">
+        <v>0.2307692307692308</v>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>SALON COMUNAL MARSELLA</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>CRA. 69 # 8-28</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="n">
+        <v>4.63302435693653</v>
+      </c>
+      <c r="G67" t="n">
+        <v>-74.12688568255854</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="K67" t="n">
+        <v>2.386385131654898</v>
+      </c>
+      <c r="L67" t="n">
+        <v>5.845594228159132</v>
+      </c>
+      <c r="M67" t="n">
+        <v>4.408353964177843</v>
+      </c>
+      <c r="N67" t="n">
+        <v>5.31259092547733</v>
+      </c>
+      <c r="O67" t="n">
+        <v>2.386385131654898</v>
+      </c>
+      <c r="P67" t="n">
+        <v>2.866668117453472</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>23</v>
+      </c>
+      <c r="R67" t="n">
+        <v>39</v>
+      </c>
+      <c r="S67" t="n">
+        <v>-16</v>
+      </c>
+      <c r="T67" t="n">
+        <v>-0.4102564102564102</v>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>MARIA PAZ</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>CLL. 5A SUR # 82-63</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="n">
+        <v>4.636932589051167</v>
+      </c>
+      <c r="G68" t="n">
+        <v>-74.15809960619315</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>VALLADOLID</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>VALLADOLID</t>
+        </is>
+      </c>
+      <c r="K68" t="n">
+        <v>1.643452020399809</v>
+      </c>
+      <c r="L68" t="n">
+        <v>3.212621844420202</v>
+      </c>
+      <c r="M68" t="n">
+        <v>1.855208003957904</v>
+      </c>
+      <c r="N68" t="n">
+        <v>1.937707566185642</v>
+      </c>
+      <c r="O68" t="n">
+        <v>3.012526992055515</v>
+      </c>
+      <c r="P68" t="n">
+        <v>1.643452020399809</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>57</v>
+      </c>
+      <c r="R68" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="S68" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="T68" t="n">
+        <v>0.3103448275862069</v>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>VILLANUEVA</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>CRA. 68I # 39D-04 SUR</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="n">
+        <v>4.603488299523999</v>
+      </c>
+      <c r="G69" t="n">
+        <v>-74.14137828544375</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="K69" t="n">
+        <v>1.433264891640001</v>
+      </c>
+      <c r="L69" t="n">
+        <v>4.043514755829754</v>
+      </c>
+      <c r="M69" t="n">
+        <v>3.31382881740265</v>
+      </c>
+      <c r="N69" t="n">
+        <v>5.888286458614425</v>
+      </c>
+      <c r="O69" t="n">
+        <v>1.433264891640001</v>
+      </c>
+      <c r="P69" t="n">
+        <v>4.984687120027299</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="R69" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>COLEGIO FE Y ALEGRIA</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>TRV. 78C # 6D-49</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="n">
+        <v>4.63434456431422</v>
+      </c>
+      <c r="G70" t="n">
+        <v>-74.1458764061931</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>VALLADOLID</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>VALLADOLID</t>
+        </is>
+      </c>
+      <c r="K70" t="n">
+        <v>1.517739800579325</v>
+      </c>
+      <c r="L70" t="n">
+        <v>4.02834332562864</v>
+      </c>
+      <c r="M70" t="n">
+        <v>2.542473377553732</v>
+      </c>
+      <c r="N70" t="n">
+        <v>3.276002148521732</v>
+      </c>
+      <c r="O70" t="n">
+        <v>2.090577888180277</v>
+      </c>
+      <c r="P70" t="n">
+        <v>1.517739800579325</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>40</v>
+      </c>
+      <c r="R70" t="n">
+        <v>41</v>
+      </c>
+      <c r="S70" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>-0.02439024390243903</v>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>UNVERSIDAD UNIAGUSTINIANA</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>AV. CIUDAD DE CALI # 11B-95</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="n">
+        <v>4.65363293856562</v>
+      </c>
+      <c r="G71" t="n">
+        <v>-74.14524966386375</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>PATIO BONITO</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>VALLADOLID</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>VALLADOLID</t>
+        </is>
+      </c>
+      <c r="K71" t="n">
+        <v>0.7181394803263783</v>
+      </c>
+      <c r="L71" t="n">
+        <v>5.552578162938822</v>
+      </c>
+      <c r="M71" t="n">
+        <v>4.168485445041653</v>
+      </c>
+      <c r="N71" t="n">
+        <v>3.190366909553118</v>
+      </c>
+      <c r="O71" t="n">
+        <v>4.180624681070251</v>
+      </c>
+      <c r="P71" t="n">
+        <v>0.7181394803263783</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>61</v>
+      </c>
+      <c r="R71" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="S71" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="T71" t="n">
+        <v>0.5844155844155844</v>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>CARVAJAL II SEDE ANTONIA SANTOS I</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>CLL. 25 SUR # 69C-34</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="n">
+        <v>4.615312883074003</v>
+      </c>
+      <c r="G72" t="n">
+        <v>-74.13554380630582</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="K72" t="n">
+        <v>0.5538656899691768</v>
+      </c>
+      <c r="L72" t="n">
+        <v>4.506461522833722</v>
+      </c>
+      <c r="M72" t="n">
+        <v>3.343642075321443</v>
+      </c>
+      <c r="N72" t="n">
+        <v>5.376944056511918</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0.5538656899691768</v>
+      </c>
+      <c r="P72" t="n">
+        <v>3.871799598651915</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="R72" t="n">
+        <v>39</v>
+      </c>
+      <c r="S72" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="T72" t="n">
+        <v>-0.141025641025641</v>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>SALON COMUNAL VILLA ALSACIA</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>CLL. 11A # 72D-20</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="n">
+        <v>4.643707823001684</v>
+      </c>
+      <c r="G73" t="n">
+        <v>-74.13613808468941</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>VALLADOLID</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>VALLADOLID</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
+        <v>1.399033225520616</v>
+      </c>
+      <c r="L73" t="n">
+        <v>5.509673828203571</v>
+      </c>
+      <c r="M73" t="n">
+        <v>4.026237004558624</v>
+      </c>
+      <c r="N73" t="n">
+        <v>4.094515114809728</v>
+      </c>
+      <c r="O73" t="n">
+        <v>3.079784739538413</v>
+      </c>
+      <c r="P73" t="n">
+        <v>1.399033225520616</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>29</v>
+      </c>
+      <c r="R73" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="S73" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="T73" t="n">
+        <v>-0.1830985915492958</v>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>LICEO EL CASTILLO</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>CRA. 82 BIS # 7D-12</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="n">
+        <v>4.644239031896902</v>
+      </c>
+      <c r="G74" t="n">
+        <v>-74.14992873803973</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>VALLADOLID</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>VALLADOLID</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
+        <v>0.4481650209217371</v>
+      </c>
+      <c r="L74" t="n">
+        <v>4.41715973928606</v>
+      </c>
+      <c r="M74" t="n">
+        <v>3.00920526154662</v>
+      </c>
+      <c r="N74" t="n">
+        <v>2.565698439618832</v>
+      </c>
+      <c r="O74" t="n">
+        <v>3.275526632185775</v>
+      </c>
+      <c r="P74" t="n">
+        <v>0.4481650209217371</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="R74" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="S74" t="n">
+        <v>2</v>
+      </c>
+      <c r="T74" t="n">
+        <v>0.05797101449275362</v>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>COLEGIO PAULO VI SEDE A</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>CRA. 78N # 41-17.21 SUR</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="n">
+        <v>4.620990660656232</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-74.15789474600763</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="K75" t="n">
+        <v>0.7935329180804782</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.157831278948338</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.7935329180804782</v>
+      </c>
+      <c r="N75" t="n">
+        <v>3.24977986372584</v>
+      </c>
+      <c r="O75" t="n">
+        <v>2.003159897521876</v>
+      </c>
+      <c r="P75" t="n">
+        <v>3.175615971061437</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="R75" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="S75" t="n">
+        <v>-5</v>
+      </c>
+      <c r="T75" t="n">
+        <v>-0.1587301587301587</v>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>CENTRO COMERCIAL CIUDAD TINTAL</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>CRA. 94 # 6C-30</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="n">
+        <v>4.652737774754291</v>
+      </c>
+      <c r="G76" t="n">
+        <v>-74.16011649823781</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>PATIO BONITO</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>VALLADOLID</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>VALLADOLID</t>
+        </is>
+      </c>
+      <c r="K76" t="n">
+        <v>1.442953840799914</v>
+      </c>
+      <c r="L76" t="n">
+        <v>4.624432197673248</v>
+      </c>
+      <c r="M76" t="n">
+        <v>3.489432864168381</v>
+      </c>
+      <c r="N76" t="n">
+        <v>1.611502058728714</v>
+      </c>
+      <c r="O76" t="n">
+        <v>4.597421942520587</v>
+      </c>
+      <c r="P76" t="n">
+        <v>1.442953840799914</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>22</v>
+      </c>
+      <c r="R76" t="n">
+        <v>30</v>
+      </c>
+      <c r="S76" t="n">
+        <v>-8</v>
+      </c>
+      <c r="T76" t="n">
+        <v>-0.2666666666666667</v>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>COLEGIO DEBORA ARANGO</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>CRA. 84A # 57B-04 SUR</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="n">
+        <v>4.618578980247849</v>
+      </c>
+      <c r="G77" t="n">
+        <v>-74.18344534233101</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>CLASS ROMA</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>CLASS ROMA</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>CLASS ROMA</t>
+        </is>
+      </c>
+      <c r="K77" t="n">
+        <v>0.9308049291092665</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0.9308049291092665</v>
+      </c>
+      <c r="M77" t="n">
+        <v>2.072697339134521</v>
+      </c>
+      <c r="N77" t="n">
+        <v>3.264776105376968</v>
+      </c>
+      <c r="O77" t="n">
+        <v>4.773717019378574</v>
+      </c>
+      <c r="P77" t="n">
+        <v>5.093458550866186</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>31</v>
+      </c>
+      <c r="R77" t="n">
+        <v>29</v>
+      </c>
+      <c r="S77" t="n">
+        <v>2</v>
+      </c>
+      <c r="T77" t="n">
+        <v>0.06896551724137931</v>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>COL. TERESA MARTINEZ DE VARELA</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>CLL. 8A BIS # 94-72</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="n">
+        <v>4.657243750413549</v>
+      </c>
+      <c r="G78" t="n">
+        <v>-74.15657946627316</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>PATIO BONITO</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>VALLADOLID</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>VALLADOLID</t>
+        </is>
+      </c>
+      <c r="K78" t="n">
+        <v>1.410034779784213</v>
+      </c>
+      <c r="L78" t="n">
+        <v>5.240540955184621</v>
+      </c>
+      <c r="M78" t="n">
+        <v>4.0571695520885</v>
+      </c>
+      <c r="N78" t="n">
+        <v>2.20650791728598</v>
+      </c>
+      <c r="O78" t="n">
+        <v>4.887317838133634</v>
+      </c>
+      <c r="P78" t="n">
+        <v>1.410034779784213</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="R78" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="S78" t="n">
+        <v>17</v>
+      </c>
+      <c r="T78" t="n">
+        <v>0.6415094339622641</v>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>COLEGIO JEAN PIAGET</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>CLL. 2B # 70-22</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="n">
+        <v>4.624631837137064</v>
+      </c>
+      <c r="G79" t="n">
+        <v>-74.13162168354697</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
+        <v>1.342795740007128</v>
+      </c>
+      <c r="L79" t="n">
+        <v>5.070219587059067</v>
+      </c>
+      <c r="M79" t="n">
+        <v>3.7150404772071</v>
+      </c>
+      <c r="N79" t="n">
+        <v>5.167604943091788</v>
+      </c>
+      <c r="O79" t="n">
+        <v>1.342795740007128</v>
+      </c>
+      <c r="P79" t="n">
+        <v>3.15749308934031</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>26</v>
+      </c>
+      <c r="R79" t="n">
+        <v>27</v>
+      </c>
+      <c r="S79" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>-0.03703703703703703</v>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>SALON COMUNAL BOITA II SECTOR</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>CRA. 72R BIS # 48-11 SUR</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="n">
+        <v>4.604055917012727</v>
+      </c>
+      <c r="G80" t="n">
+        <v>-74.15635301225927</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="K80" t="n">
+        <v>2.188098591657161</v>
+      </c>
+      <c r="L80" t="n">
+        <v>2.479451513765205</v>
+      </c>
+      <c r="M80" t="n">
+        <v>2.188098591657161</v>
+      </c>
+      <c r="N80" t="n">
+        <v>5.019625859359133</v>
+      </c>
+      <c r="O80" t="n">
+        <v>2.231657683093838</v>
+      </c>
+      <c r="P80" t="n">
+        <v>4.951969153592564</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>20</v>
+      </c>
+      <c r="R80" t="n">
+        <v>21</v>
+      </c>
+      <c r="S80" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T80" t="n">
+        <v>-0.04761904761904762</v>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Reasignación sugerida por cercanía: KENNEDY CENTRAL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>FLORESTA SUR SEDE B</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>CLL. 2 # 68B-82 SUR</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="n">
+        <v>4.622477093379867</v>
+      </c>
+      <c r="G81" t="n">
+        <v>-74.1270868401846</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="K81" t="n">
+        <v>1.628858680492363</v>
+      </c>
+      <c r="L81" t="n">
+        <v>5.516848617261154</v>
+      </c>
+      <c r="M81" t="n">
+        <v>4.204504488312343</v>
+      </c>
+      <c r="N81" t="n">
+        <v>5.724115677388468</v>
+      </c>
+      <c r="O81" t="n">
+        <v>1.628858680492363</v>
+      </c>
+      <c r="P81" t="n">
+        <v>3.653433649401631</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="R81" t="n">
+        <v>20</v>
+      </c>
+      <c r="S81" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T81" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>SALON COMUNAL CARVAJAL OSORIO</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>CRA. 68L # 37D-38 SUR</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="n">
+        <v>4.607361322479445</v>
+      </c>
+      <c r="G82" t="n">
+        <v>-74.1381371554869</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="K82" t="n">
+        <v>1.030672085514936</v>
+      </c>
+      <c r="L82" t="n">
+        <v>4.28899451130758</v>
+      </c>
+      <c r="M82" t="n">
+        <v>3.380858453853236</v>
+      </c>
+      <c r="N82" t="n">
+        <v>5.781874795386877</v>
+      </c>
+      <c r="O82" t="n">
+        <v>1.030672085514936</v>
+      </c>
+      <c r="P82" t="n">
+        <v>4.63127617480028</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="R82" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="S82" t="n">
+        <v>-10</v>
+      </c>
+      <c r="T82" t="n">
+        <v>-0.4081632653061225</v>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>COLEGIO INTEGRACION MODERNA</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>CLL. 4 # 71A-41</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="n">
+        <v>4.626767553890399</v>
+      </c>
+      <c r="G83" t="n">
+        <v>-74.13467057759422</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="K83" t="n">
+        <v>1.323408817999874</v>
+      </c>
+      <c r="L83" t="n">
+        <v>4.804328768656527</v>
+      </c>
+      <c r="M83" t="n">
+        <v>3.409331848357156</v>
+      </c>
+      <c r="N83" t="n">
+        <v>4.758604565424535</v>
+      </c>
+      <c r="O83" t="n">
+        <v>1.323408817999874</v>
+      </c>
+      <c r="P83" t="n">
+        <v>2.771980235033889</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>20</v>
+      </c>
+      <c r="R83" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="S83" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="T83" t="n">
+        <v>-0.148936170212766</v>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>POLIDEPORTIVO CASTILLA</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>CLL. 8B BIS # 73B-1</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="n">
+        <v>4.639256654477254</v>
+      </c>
+      <c r="G84" t="n">
+        <v>-74.13928652734809</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>VALLADOLID</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>VALLADOLID</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
+        <v>1.361482033876237</v>
+      </c>
+      <c r="L84" t="n">
+        <v>4.939111548497402</v>
+      </c>
+      <c r="M84" t="n">
+        <v>3.453347658836577</v>
+      </c>
+      <c r="N84" t="n">
+        <v>3.812645765998224</v>
+      </c>
+      <c r="O84" t="n">
+        <v>2.550995993972103</v>
+      </c>
+      <c r="P84" t="n">
+        <v>1.361482033876237</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="R84" t="n">
+        <v>23</v>
+      </c>
+      <c r="S84" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="T84" t="n">
+        <v>0.9782608695652174</v>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>ALOHA</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>CLL. 7A BIS # 71A-20</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="n">
+        <v>4.632978495570468</v>
+      </c>
+      <c r="G85" t="n">
+        <v>-74.13328346850038</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="K85" t="n">
+        <v>2.012309869241056</v>
+      </c>
+      <c r="L85" t="n">
+        <v>5.186777073066827</v>
+      </c>
+      <c r="M85" t="n">
+        <v>3.732357604923441</v>
+      </c>
+      <c r="N85" t="n">
+        <v>4.635938073205935</v>
+      </c>
+      <c r="O85" t="n">
+        <v>2.012309869241056</v>
+      </c>
+      <c r="P85" t="n">
+        <v>2.325499369592395</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="R85" t="n">
+        <v>23</v>
+      </c>
+      <c r="S85" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="T85" t="n">
+        <v>-0.3695652173913043</v>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>SALON COMUNAL ROMA IV</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>CRA. 78J # 54-16 SUR</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="n">
+        <v>4.611684447069997</v>
+      </c>
+      <c r="G86" t="n">
+        <v>-74.17022943558608</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>CLASS ROMA</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>CLASS ROMA</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>CLASS ROMA</t>
+        </is>
+      </c>
+      <c r="K86" t="n">
+        <v>0.7247239154432612</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0.7247239154432612</v>
+      </c>
+      <c r="M86" t="n">
+        <v>1.258529096323564</v>
+      </c>
+      <c r="N86" t="n">
+        <v>3.832018801397006</v>
+      </c>
+      <c r="O86" t="n">
+        <v>3.342871452216639</v>
+      </c>
+      <c r="P86" t="n">
+        <v>4.709095778798457</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>43</v>
+      </c>
+      <c r="R86" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="S86" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="T86" t="n">
+        <v>1</v>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>CARLOS ARANGO VELEZ SEDE A</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>TRV. 68G # 35A-42 SUR</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="n">
+        <v>4.607857204992963</v>
+      </c>
+      <c r="G87" t="n">
+        <v>-74.13533977950259</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="K87" t="n">
+        <v>1.0995880004487</v>
+      </c>
+      <c r="L87" t="n">
+        <v>4.585220840019334</v>
+      </c>
+      <c r="M87" t="n">
+        <v>3.633223058446946</v>
+      </c>
+      <c r="N87" t="n">
+        <v>5.954118334586605</v>
+      </c>
+      <c r="O87" t="n">
+        <v>1.0995880004487</v>
+      </c>
+      <c r="P87" t="n">
+        <v>4.662010377223332</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>38</v>
+      </c>
+      <c r="R87" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="S87" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="T87" t="n">
+        <v>0.7674418604651163</v>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>COLEGIO SAN PEDRO CLAVER SEDE B</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>CLL. 42G SUR #87-06</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="n">
+        <v>4.632041051526458</v>
+      </c>
+      <c r="G88" t="n">
+        <v>-74.1716530307835</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>PATIO BONITO</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="K88" t="n">
+        <v>1.361469549775156</v>
+      </c>
+      <c r="L88" t="n">
+        <v>2.029408063151214</v>
+      </c>
+      <c r="M88" t="n">
+        <v>1.361469549775156</v>
+      </c>
+      <c r="N88" t="n">
+        <v>1.563303733474988</v>
+      </c>
+      <c r="O88" t="n">
+        <v>3.875545310822536</v>
+      </c>
+      <c r="P88" t="n">
+        <v>3.147977901017831</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>19</v>
+      </c>
+      <c r="R88" t="n">
+        <v>17</v>
+      </c>
+      <c r="S88" t="n">
+        <v>2</v>
+      </c>
+      <c r="T88" t="n">
+        <v>0.1176470588235294</v>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Reasignación sugerida por cercanía: KENNEDY CENTRAL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>ISABEL II</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>DIAG. 2D # 79C-83</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="n">
+        <v>4.633474513323257</v>
+      </c>
+      <c r="G89" t="n">
+        <v>-74.15315575166245</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>VALLADOLID</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>VALLADOLID</t>
+        </is>
+      </c>
+      <c r="K89" t="n">
+        <v>1.691620784660405</v>
+      </c>
+      <c r="L89" t="n">
+        <v>3.322089271355936</v>
+      </c>
+      <c r="M89" t="n">
+        <v>1.852173584725342</v>
+      </c>
+      <c r="N89" t="n">
+        <v>2.606135535083581</v>
+      </c>
+      <c r="O89" t="n">
+        <v>2.370019615726993</v>
+      </c>
+      <c r="P89" t="n">
+        <v>1.691620784660405</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="R89" t="n">
+        <v>16</v>
+      </c>
+      <c r="S89" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="T89" t="n">
+        <v>-0.03125</v>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>COLEGIO OEA ANTONIA SANTOS</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>CRA. 69 # 39-27 SUR</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="n">
+        <v>4.609139801962333</v>
+      </c>
+      <c r="G90" t="n">
+        <v>-74.14094003890564</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="K90" t="n">
+        <v>0.8029809233173397</v>
+      </c>
+      <c r="L90" t="n">
+        <v>3.95002230503638</v>
+      </c>
+      <c r="M90" t="n">
+        <v>3.013736858185893</v>
+      </c>
+      <c r="N90" t="n">
+        <v>5.428034341083497</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0.8029809233173397</v>
+      </c>
+      <c r="P90" t="n">
+        <v>4.372776845582433</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="R90" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="S90" t="n">
+        <v>-3</v>
+      </c>
+      <c r="T90" t="n">
+        <v>-0.1818181818181818</v>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>FERNANDO SOTO APARICIO SEDE B</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>CRA. 80A # 51B-29 SUR</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="n">
+        <v>4.617327547056584</v>
+      </c>
+      <c r="G91" t="n">
+        <v>-74.17265186603387</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>CLASS ROMA</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>CLASS ROMA</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>CLASS ROMA</t>
+        </is>
+      </c>
+      <c r="K91" t="n">
+        <v>0.5126888917454049</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0.5126888917454049</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0.9782736664674607</v>
+      </c>
+      <c r="N91" t="n">
+        <v>3.192381391600173</v>
+      </c>
+      <c r="O91" t="n">
+        <v>3.572635457696498</v>
+      </c>
+      <c r="P91" t="n">
+        <v>4.349472514797959</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>16</v>
+      </c>
+      <c r="R91" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="S91" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T91" t="n">
+        <v>0.103448275862069</v>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>COLEGIO EMMA REYES IED</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>CRA. 80B # 6-71</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="n">
+        <v>4.637027054667607</v>
+      </c>
+      <c r="G92" t="n">
+        <v>-74.15097392831733</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>VALLADOLID</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>VALLADOLID</t>
+        </is>
+      </c>
+      <c r="K92" t="n">
+        <v>1.242329832140628</v>
+      </c>
+      <c r="L92" t="n">
+        <v>3.7636131694461</v>
+      </c>
+      <c r="M92" t="n">
+        <v>2.30471740242823</v>
+      </c>
+      <c r="N92" t="n">
+        <v>2.639526333694416</v>
+      </c>
+      <c r="O92" t="n">
+        <v>2.579628032617853</v>
+      </c>
+      <c r="P92" t="n">
+        <v>1.242329832140628</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>28</v>
+      </c>
+      <c r="R92" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="S92" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="T92" t="n">
+        <v>1.074074074074074</v>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>LICEO REYNEL</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>CLL. 39 SUR # 68F-15</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="n">
+        <v>4.602867732665001</v>
+      </c>
+      <c r="G93" t="n">
+        <v>-74.138085550574</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="K93" t="n">
+        <v>1.520852439828315</v>
+      </c>
+      <c r="L93" t="n">
+        <v>4.412618567658773</v>
+      </c>
+      <c r="M93" t="n">
+        <v>3.648513789773589</v>
+      </c>
+      <c r="N93" t="n">
+        <v>6.16615946457692</v>
+      </c>
+      <c r="O93" t="n">
+        <v>1.520852439828315</v>
+      </c>
+      <c r="P93" t="n">
+        <v>5.119234102788465</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>12</v>
+      </c>
+      <c r="R93" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="S93" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="T93" t="n">
+        <v>-0.1724137931034483</v>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>GEMA</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>CLL. 58B SUR # 78K-21</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="n">
+        <v>4.605778077914141</v>
+      </c>
+      <c r="G94" t="n">
+        <v>-74.17565580146317</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>CLASS ROMA</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>CLASS ROMA</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>CLASS ROMA</t>
+        </is>
+      </c>
+      <c r="K94" t="n">
+        <v>0.9560897552833644</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0.9560897552833644</v>
+      </c>
+      <c r="M94" t="n">
+        <v>2.130871819437384</v>
+      </c>
+      <c r="N94" t="n">
+        <v>4.4859852918995</v>
+      </c>
+      <c r="O94" t="n">
+        <v>4.076869368997396</v>
+      </c>
+      <c r="P94" t="n">
+        <v>5.585739590509417</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="R94" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="S94" t="n">
+        <v>0</v>
+      </c>
+      <c r="T94" t="n">
+        <v>0</v>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>SALON COMUNAL VILLA CLAUDIA</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>CLL. 9A SUR # 68F-23</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="n">
+        <v>4.617436400753726</v>
+      </c>
+      <c r="G95" t="n">
+        <v>-74.12898272680069</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="K95" t="n">
+        <v>1.274877204390253</v>
+      </c>
+      <c r="L95" t="n">
+        <v>5.243572744568052</v>
+      </c>
+      <c r="M95" t="n">
+        <v>4.022140960424331</v>
+      </c>
+      <c r="N95" t="n">
+        <v>5.824225575999339</v>
+      </c>
+      <c r="O95" t="n">
+        <v>1.274877204390253</v>
+      </c>
+      <c r="P95" t="n">
+        <v>3.985895516033728</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R95" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="S95" t="n">
+        <v>-8</v>
+      </c>
+      <c r="T95" t="n">
+        <v>-0.5925925925925926</v>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>COLEGIO COOPERATIVO TIMIZA</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>CRA. 72M # 40F-18 SUR</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="n">
+        <v>4.608788142669527</v>
+      </c>
+      <c r="G96" t="n">
+        <v>-74.15070709085178</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="K96" t="n">
+        <v>1.41510125817027</v>
+      </c>
+      <c r="L96" t="n">
+        <v>2.891759055071822</v>
+      </c>
+      <c r="M96" t="n">
+        <v>2.142075969506028</v>
+      </c>
+      <c r="N96" t="n">
+        <v>4.823155486526226</v>
+      </c>
+      <c r="O96" t="n">
+        <v>1.41510125817027</v>
+      </c>
+      <c r="P96" t="n">
+        <v>4.349745804286425</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>26</v>
+      </c>
+      <c r="R96" t="n">
+        <v>13</v>
+      </c>
+      <c r="S96" t="n">
+        <v>13</v>
+      </c>
+      <c r="T96" t="n">
+        <v>1</v>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Reasignación sugerida por cercanía: CARVAJAL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>SALON COMUNAL MONTERREY</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>CLL. 8 BIS # 81-40</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="n">
+        <v>4.643819651459737</v>
+      </c>
+      <c r="G97" t="n">
+        <v>-74.14804991479259</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>VALLADOLID</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>VALLADOLID</t>
+        </is>
+      </c>
+      <c r="K97" t="n">
+        <v>0.4445855561639377</v>
+      </c>
+      <c r="L97" t="n">
+        <v>4.523188338085755</v>
+      </c>
+      <c r="M97" t="n">
+        <v>3.092548309351062</v>
+      </c>
+      <c r="N97" t="n">
+        <v>2.777091920277539</v>
+      </c>
+      <c r="O97" t="n">
+        <v>3.169701393992137</v>
+      </c>
+      <c r="P97" t="n">
+        <v>0.4445855561639377</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="R97" t="n">
+        <v>12</v>
+      </c>
+      <c r="S97" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="T97" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>FERNANDO SOTO APARICIO</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>TRV. 73A BIS B # 36-47 SUR</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="n">
+        <v>4.619408119232562</v>
+      </c>
+      <c r="G98" t="n">
+        <v>-74.1474082558598</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="K98" t="n">
+        <v>0.8448771020376031</v>
+      </c>
+      <c r="L98" t="n">
+        <v>3.239227400813822</v>
+      </c>
+      <c r="M98" t="n">
+        <v>1.968549565752892</v>
+      </c>
+      <c r="N98" t="n">
+        <v>4.100802247078891</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0.8448771020376031</v>
+      </c>
+      <c r="P98" t="n">
+        <v>3.159867460336791</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>15</v>
+      </c>
+      <c r="R98" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="S98" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T98" t="n">
+        <v>0.3043478260869565</v>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Reasignación sugerida por cercanía: CARVAJAL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>LORETO DE CASTILLA</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>CLL. 8A # 78C-60</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="n">
+        <v>4.639221593354907</v>
+      </c>
+      <c r="G99" t="n">
+        <v>-74.14303464526394</v>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>VALLADOLID</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>VALLADOLID</t>
+        </is>
+      </c>
+      <c r="K99" t="n">
+        <v>1.106783309883919</v>
+      </c>
+      <c r="L99" t="n">
+        <v>4.598637800477699</v>
+      </c>
+      <c r="M99" t="n">
+        <v>3.116710096228917</v>
+      </c>
+      <c r="N99" t="n">
+        <v>3.407294799493367</v>
+      </c>
+      <c r="O99" t="n">
+        <v>2.560221752887937</v>
+      </c>
+      <c r="P99" t="n">
+        <v>1.106783309883919</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="R99" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>COLEGIO LUZ Y VIDA</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>CLL. 1 SUR # 86-15</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="n">
+        <v>4.638812463242689</v>
+      </c>
+      <c r="G100" t="n">
+        <v>-74.15917891079442</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>PATIO BONITO</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>VALLADOLID</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>VALLADOLID</t>
+        </is>
+      </c>
+      <c r="K100" t="n">
+        <v>1.587097256356133</v>
+      </c>
+      <c r="L100" t="n">
+        <v>3.308856315160715</v>
+      </c>
+      <c r="M100" t="n">
+        <v>2.005678424842348</v>
+      </c>
+      <c r="N100" t="n">
+        <v>1.73039148670234</v>
+      </c>
+      <c r="O100" t="n">
+        <v>3.249443449335396</v>
+      </c>
+      <c r="P100" t="n">
+        <v>1.587097256356133</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>20</v>
+      </c>
+      <c r="R100" t="n">
+        <v>11</v>
+      </c>
+      <c r="S100" t="n">
+        <v>9</v>
+      </c>
+      <c r="T100" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>COLEGIO ERNESTO GUHL</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>CLL. 42G SUR # 87G-16</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="n">
+        <v>4.633372401498291</v>
+      </c>
+      <c r="G101" t="n">
+        <v>-74.17245459779059</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>PATIO BONITO</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>PATIO BONITO</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>PATIO BONITO</t>
+        </is>
+      </c>
+      <c r="K101" t="n">
+        <v>1.409367612343068</v>
+      </c>
+      <c r="L101" t="n">
+        <v>2.15430533089865</v>
+      </c>
+      <c r="M101" t="n">
+        <v>1.534048754545563</v>
+      </c>
+      <c r="N101" t="n">
+        <v>1.409367612343068</v>
+      </c>
+      <c r="O101" t="n">
+        <v>4.022592554760863</v>
+      </c>
+      <c r="P101" t="n">
+        <v>3.143972945686087</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="R101" t="n">
+        <v>10</v>
+      </c>
+      <c r="S101" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="T101" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>SALON COMUNAL SANTA CATALINA</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>CRA. 72Q BIS # 43-06 SUR</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="n">
+        <v>4.606170504162802</v>
+      </c>
+      <c r="G102" t="n">
+        <v>-74.1538316683192</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="K102" t="n">
+        <v>1.866801776461036</v>
+      </c>
+      <c r="L102" t="n">
+        <v>2.640303670786607</v>
+      </c>
+      <c r="M102" t="n">
+        <v>2.129103109075202</v>
+      </c>
+      <c r="N102" t="n">
+        <v>4.915951827974959</v>
+      </c>
+      <c r="O102" t="n">
+        <v>1.866801776461036</v>
+      </c>
+      <c r="P102" t="n">
+        <v>4.674812749853528</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>12</v>
+      </c>
+      <c r="R102" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="S102" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T102" t="n">
+        <v>0.2631578947368421</v>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>COLEGIO SAN RAFAEL SEDE A</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>TRV. 78I # 42B-81 SUR</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="n">
+        <v>4.617774750445167</v>
+      </c>
+      <c r="G103" t="n">
+        <v>-74.16165677123443</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="K103" t="n">
+        <v>0.5769011495405205</v>
+      </c>
+      <c r="L103" t="n">
+        <v>1.655144382281172</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0.5769011495405205</v>
+      </c>
+      <c r="N103" t="n">
+        <v>3.384909739880926</v>
+      </c>
+      <c r="O103" t="n">
+        <v>2.357704504145225</v>
+      </c>
+      <c r="P103" t="n">
+        <v>3.664400863597925</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="R103" t="n">
+        <v>9</v>
+      </c>
+      <c r="S103" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T103" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>SALON COMUNAL ANDALUCIA II SECTOR</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>CLL. 14A # 81-38</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="n">
+        <v>4.653748067813638</v>
+      </c>
+      <c r="G104" t="n">
+        <v>-74.13690145429857</v>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>VALLADOLID</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>VALLADOLID</t>
+        </is>
+      </c>
+      <c r="K104" t="n">
+        <v>1.402371718387995</v>
+      </c>
+      <c r="L104" t="n">
+        <v>6.176179830168337</v>
+      </c>
+      <c r="M104" t="n">
+        <v>4.730431038783366</v>
+      </c>
+      <c r="N104" t="n">
+        <v>4.092569064878433</v>
+      </c>
+      <c r="O104" t="n">
+        <v>4.177576857953629</v>
+      </c>
+      <c r="P104" t="n">
+        <v>1.402371718387995</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="R104" t="n">
+        <v>8</v>
+      </c>
+      <c r="S104" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T104" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>COLEGIO DISTRITAL JACKELINE</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>CRA. 77Q # 45A-21 SUR</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="n">
+        <v>4.608947951826015</v>
+      </c>
+      <c r="G105" t="n">
+        <v>-74.16283932740487</v>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="K105" t="n">
+        <v>1.442563217224501</v>
+      </c>
+      <c r="L105" t="n">
+        <v>1.59760453023422</v>
+      </c>
+      <c r="M105" t="n">
+        <v>1.442563217224501</v>
+      </c>
+      <c r="N105" t="n">
+        <v>4.275145651635729</v>
+      </c>
+      <c r="O105" t="n">
+        <v>2.616022557133487</v>
+      </c>
+      <c r="P105" t="n">
+        <v>4.621772842767657</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>16</v>
+      </c>
+      <c r="R105" t="n">
+        <v>7</v>
+      </c>
+      <c r="S105" t="n">
+        <v>9</v>
+      </c>
+      <c r="T105" t="n">
+        <v>1.285714285714286</v>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>COLEGIO MILITAR MANUEL MURILLO TORO / SALON COMUNAL CARVAJAL II SECTOR</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>CRA. 70B # 24A-40 SUR</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="n">
+        <v>4.61618790095059</v>
+      </c>
+      <c r="G106" t="n">
+        <v>-74.13594710434316</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="K106" t="n">
+        <v>0.4974822260208032</v>
+      </c>
+      <c r="L106" t="n">
+        <v>4.465142669831348</v>
+      </c>
+      <c r="M106" t="n">
+        <v>3.280296020561783</v>
+      </c>
+      <c r="N106" t="n">
+        <v>5.280814744552626</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0.4974822260208032</v>
+      </c>
+      <c r="P106" t="n">
+        <v>3.764950787046145</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R106" t="n">
+        <v>7</v>
+      </c>
+      <c r="S106" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="T106" t="n">
+        <v>-0.6428571428571429</v>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>COLEGIO CIUDAD DE FOMEQUE</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>CRA. 93B # 42F-16 SUR</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="n">
+        <v>4.640868958822471</v>
+      </c>
+      <c r="G107" t="n">
+        <v>-74.17545372631638</v>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>PATIO BONITO</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>PATIO BONITO</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>PATIO BONITO</t>
+        </is>
+      </c>
+      <c r="K107" t="n">
+        <v>0.6351713696362136</v>
+      </c>
+      <c r="L107" t="n">
+        <v>2.948822049885476</v>
+      </c>
+      <c r="M107" t="n">
+        <v>2.421455813744941</v>
+      </c>
+      <c r="N107" t="n">
+        <v>0.6351713696362136</v>
+      </c>
+      <c r="O107" t="n">
+        <v>4.743698803437025</v>
+      </c>
+      <c r="P107" t="n">
+        <v>3.131873185984605</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R107" t="n">
+        <v>5</v>
+      </c>
+      <c r="S107" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="T107" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>METRO ALQUERIA</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>AV. 68 # 38-87 SUR</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="n">
+        <v>4.602856703130658</v>
+      </c>
+      <c r="G108" t="n">
+        <v>-74.13366682153463</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="K108" t="n">
+        <v>1.676711937825409</v>
+      </c>
+      <c r="L108" t="n">
+        <v>4.883765586727242</v>
+      </c>
+      <c r="M108" t="n">
+        <v>4.059579309967284</v>
+      </c>
+      <c r="N108" t="n">
+        <v>6.48570184001353</v>
+      </c>
+      <c r="O108" t="n">
+        <v>1.676711937825409</v>
+      </c>
+      <c r="P108" t="n">
+        <v>5.24808893617052</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="R108" t="n">
+        <v>4</v>
+      </c>
+      <c r="S108" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="T108" t="n">
+        <v>5.125</v>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>SAGRADO CORAZON</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>CLL. 53B SUR # 84-16</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="n">
+        <v>4.622525095059428</v>
+      </c>
+      <c r="G109" t="n">
+        <v>-74.17824122314002</v>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>CLASS ROMA</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>CLASS ROMA</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>CLASS ROMA</t>
+        </is>
+      </c>
+      <c r="K109" t="n">
+        <v>0.9359198989753403</v>
+      </c>
+      <c r="L109" t="n">
+        <v>0.9359198989753403</v>
+      </c>
+      <c r="M109" t="n">
+        <v>1.468512297945541</v>
+      </c>
+      <c r="N109" t="n">
+        <v>2.677755171623367</v>
+      </c>
+      <c r="O109" t="n">
+        <v>4.246436234092016</v>
+      </c>
+      <c r="P109" t="n">
+        <v>4.369480586825873</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>4</v>
+      </c>
+      <c r="R109" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="S109" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="T109" t="n">
+        <v>-0.1111111111111111</v>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>NICOLAS ESGUERRA</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>CLL. 9C # 68-52</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="n">
+        <v>4.632301702206584</v>
+      </c>
+      <c r="G110" t="n">
+        <v>-74.12227797920511</v>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="K110" t="n">
+        <v>2.682828520472515</v>
+      </c>
+      <c r="L110" t="n">
+        <v>6.299704833232938</v>
+      </c>
+      <c r="M110" t="n">
+        <v>4.880106975938296</v>
+      </c>
+      <c r="N110" t="n">
+        <v>5.826177639823568</v>
+      </c>
+      <c r="O110" t="n">
+        <v>2.682828520472515</v>
+      </c>
+      <c r="P110" t="n">
+        <v>3.338751499422238</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R110" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T110" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>COL. FELIZA BURSZTYN IED</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>CLL. 1 # 69A-07</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="n">
+        <v>4.621678840577117</v>
+      </c>
+      <c r="G111" t="n">
+        <v>-74.12941561968709</v>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="K111" t="n">
+        <v>1.357579545324797</v>
+      </c>
+      <c r="L111" t="n">
+        <v>5.247895405353788</v>
+      </c>
+      <c r="M111" t="n">
+        <v>3.945604234716645</v>
+      </c>
+      <c r="N111" t="n">
+        <v>5.538754714069405</v>
+      </c>
+      <c r="O111" t="n">
+        <v>1.357579545324797</v>
+      </c>
+      <c r="P111" t="n">
+        <v>3.566775135546704</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>38</v>
+      </c>
+      <c r="R111" t="inlineStr"/>
+      <c r="S111" t="inlineStr"/>
+      <c r="T111" t="inlineStr"/>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>CASABLANCA 33</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>CRA 79D # 46-70 SUR</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="n">
+        <v>4.617022546026672</v>
+      </c>
+      <c r="G112" t="n">
+        <v>-74.16773993841484</v>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="K112" t="n">
+        <v>0.6051624367565004</v>
+      </c>
+      <c r="L112" t="n">
+        <v>0.982452158801073</v>
+      </c>
+      <c r="M112" t="n">
+        <v>0.6051624367565004</v>
+      </c>
+      <c r="N112" t="n">
+        <v>3.278469777145413</v>
+      </c>
+      <c r="O112" t="n">
+        <v>3.027492549606762</v>
+      </c>
+      <c r="P112" t="n">
+        <v>4.059420485889888</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="R112" t="inlineStr"/>
+      <c r="S112" t="inlineStr"/>
+      <c r="T112" t="inlineStr"/>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>COL. EL FERROL LA PAZ IED</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>CRA. 69 # 9C-30</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="n">
+        <v>4.634692847061971</v>
+      </c>
+      <c r="G113" t="n">
+        <v>-74.12605665241627</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="K113" t="n">
+        <v>2.588794869770341</v>
+      </c>
+      <c r="L113" t="n">
+        <v>5.999008356958436</v>
+      </c>
+      <c r="M113" t="n">
+        <v>4.551772937786388</v>
+      </c>
+      <c r="N113" t="n">
+        <v>5.35434115847453</v>
+      </c>
+      <c r="O113" t="n">
+        <v>2.588794869770341</v>
+      </c>
+      <c r="P113" t="n">
+        <v>2.842831654822001</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>14</v>
+      </c>
+      <c r="R113" t="inlineStr"/>
+      <c r="S113" t="inlineStr"/>
+      <c r="T113" t="inlineStr"/>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>SALON COMUNAL LAS AMERICAS</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>CLL. 3A # 69B-19</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="n">
+        <v>4.626374899513526</v>
+      </c>
+      <c r="G114" t="n">
+        <v>-74.12821420586424</v>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="K114" t="n">
+        <v>1.754475789893938</v>
+      </c>
+      <c r="L114" t="n">
+        <v>5.482813655235011</v>
+      </c>
+      <c r="M114" t="n">
+        <v>4.111191806150272</v>
+      </c>
+      <c r="N114" t="n">
+        <v>5.424599092471595</v>
+      </c>
+      <c r="O114" t="n">
+        <v>1.754475789893938</v>
+      </c>
+      <c r="P114" t="n">
+        <v>3.244589508623061</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>12</v>
+      </c>
+      <c r="R114" t="inlineStr"/>
+      <c r="S114" t="inlineStr"/>
+      <c r="T114" t="inlineStr"/>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>GIMNASIO MODERNO CASTILLA</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>A. CLL. 8 # 78C-04</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="n">
+        <v>4.639138187200508</v>
+      </c>
+      <c r="G115" t="n">
+        <v>-74.142921168369</v>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>VALLADOLID</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>VALLADOLID</t>
+        </is>
+      </c>
+      <c r="K115" t="n">
+        <v>1.121150095695762</v>
+      </c>
+      <c r="L115" t="n">
+        <v>4.603137588172689</v>
+      </c>
+      <c r="M115" t="n">
+        <v>3.120792462410116</v>
+      </c>
+      <c r="N115" t="n">
+        <v>3.421624697124936</v>
+      </c>
+      <c r="O115" t="n">
+        <v>2.549615616658254</v>
+      </c>
+      <c r="P115" t="n">
+        <v>1.121150095695762</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>10</v>
+      </c>
+      <c r="R115" t="inlineStr"/>
+      <c r="S115" t="inlineStr"/>
+      <c r="T115" t="inlineStr"/>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>IED COL. SAN JOSE SEDE B</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>CRA 78N BIS # 45 SUR-60</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="n">
+        <v>4.616636907423457</v>
+      </c>
+      <c r="G116" t="n">
+        <v>-74.16550436531698</v>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="K116" t="n">
+        <v>0.569880191945387</v>
+      </c>
+      <c r="L116" t="n">
+        <v>1.21131210427916</v>
+      </c>
+      <c r="M116" t="n">
+        <v>0.569880191945387</v>
+      </c>
+      <c r="N116" t="n">
+        <v>3.373073348970834</v>
+      </c>
+      <c r="O116" t="n">
+        <v>2.778965207558426</v>
+      </c>
+      <c r="P116" t="n">
+        <v>3.969310273687554</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="R116" t="inlineStr"/>
+      <c r="S116" t="inlineStr"/>
+      <c r="T116" t="inlineStr"/>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>LICEO SAMARIO</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>CRA. 74 # 42C-80 SUR</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="n">
+        <v>4.610437176050868</v>
+      </c>
+      <c r="G117" t="n">
+        <v>-74.1578251047855</v>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="K117" t="n">
+        <v>1.488036149520507</v>
+      </c>
+      <c r="L117" t="n">
+        <v>2.081890494929874</v>
+      </c>
+      <c r="M117" t="n">
+        <v>1.488036149520507</v>
+      </c>
+      <c r="N117" t="n">
+        <v>4.301168329827358</v>
+      </c>
+      <c r="O117" t="n">
+        <v>2.036463571325267</v>
+      </c>
+      <c r="P117" t="n">
+        <v>4.29488878565044</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="R117" t="inlineStr"/>
+      <c r="S117" t="inlineStr"/>
+      <c r="T117" t="inlineStr"/>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>CASABLANCA 1</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>CRA. 79B # 50-00/31 SUR</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="n">
+        <v>4.635415133352685</v>
+      </c>
+      <c r="G118" t="n">
+        <v>-74.14830004672973</v>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>VALLADOLID</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>VALLADOLID</t>
+        </is>
+      </c>
+      <c r="K118" t="n">
+        <v>1.37935838262393</v>
+      </c>
+      <c r="L118" t="n">
+        <v>3.877864503323467</v>
+      </c>
+      <c r="M118" t="n">
+        <v>2.396798921135465</v>
+      </c>
+      <c r="N118" t="n">
+        <v>2.982204186549824</v>
+      </c>
+      <c r="O118" t="n">
+        <v>2.292928732074488</v>
+      </c>
+      <c r="P118" t="n">
+        <v>1.37935838262393</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R118" t="inlineStr"/>
+      <c r="S118" t="inlineStr"/>
+      <c r="T118" t="inlineStr"/>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>LICEO CARMELITAS</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>CRA. 77K # 57D-23 SUR</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="n">
+        <v>4.606281809458057</v>
+      </c>
+      <c r="G119" t="n">
+        <v>-74.17334159905299</v>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>CLASS ROMA</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>CLASS ROMA</t>
+        </is>
+      </c>
+      <c r="K119" t="n">
+        <v>0.9521661655137271</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.9521661655137271</v>
+      </c>
+      <c r="M119" t="n">
+        <v>1.950826451416816</v>
+      </c>
+      <c r="N119" t="n">
+        <v>4.420521026563097</v>
+      </c>
+      <c r="O119" t="n">
+        <v>3.81516685486168</v>
+      </c>
+      <c r="P119" t="n">
+        <v>5.401600341785629</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R119" t="inlineStr"/>
+      <c r="S119" t="inlineStr"/>
+      <c r="T119" t="inlineStr"/>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Reasignación sugerida por cercanía: CLASS ROMA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>SALON COMUNAL NUEVAS DELICIAS</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>CLL. 44F SUR # 72B-36</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="n">
+        <v>4.599714817247681</v>
+      </c>
+      <c r="G120" t="n">
+        <v>-74.14696684838773</v>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="K120" t="n">
+        <v>1.985783301754357</v>
+      </c>
+      <c r="L120" t="n">
+        <v>3.625485843498656</v>
+      </c>
+      <c r="M120" t="n">
+        <v>3.162087436187425</v>
+      </c>
+      <c r="N120" t="n">
+        <v>5.904156010443669</v>
+      </c>
+      <c r="O120" t="n">
+        <v>1.985783301754357</v>
+      </c>
+      <c r="P120" t="n">
+        <v>5.350208726717519</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>6</v>
+      </c>
+      <c r="R120" t="inlineStr"/>
+      <c r="S120" t="inlineStr"/>
+      <c r="T120" t="inlineStr"/>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>COL. MARIA BETSABE ESPINAL IED</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>CLL. 45 SUR # 72Q-20</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="n">
+        <v>4.605162588716205</v>
+      </c>
+      <c r="G121" t="n">
+        <v>-74.15508986024297</v>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="K121" t="n">
+        <v>2.045654077098847</v>
+      </c>
+      <c r="L121" t="n">
+        <v>2.552669634324206</v>
+      </c>
+      <c r="M121" t="n">
+        <v>2.146489518821277</v>
+      </c>
+      <c r="N121" t="n">
+        <v>4.959780561032128</v>
+      </c>
+      <c r="O121" t="n">
+        <v>2.045654077098847</v>
+      </c>
+      <c r="P121" t="n">
+        <v>4.806459120587329</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R121" t="inlineStr"/>
+      <c r="S121" t="inlineStr"/>
+      <c r="T121" t="inlineStr"/>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Reasignación sugerida por cercanía: CARVAJAL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>SALON INTSMAR-INSTITUTO MARSELLA</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>CRA. 70 # 6C-50</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="n">
+        <v>4.632222056917934</v>
+      </c>
+      <c r="G122" t="n">
+        <v>-74.13065640152013</v>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="K122" t="n">
+        <v>2.071596099838299</v>
+      </c>
+      <c r="L122" t="n">
+        <v>5.423618998953106</v>
+      </c>
+      <c r="M122" t="n">
+        <v>3.98247343323785</v>
+      </c>
+      <c r="N122" t="n">
+        <v>4.938807994541212</v>
+      </c>
+      <c r="O122" t="n">
+        <v>2.071596099838299</v>
+      </c>
+      <c r="P122" t="n">
+        <v>2.594534204095595</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>4</v>
+      </c>
+      <c r="R122" t="inlineStr"/>
+      <c r="S122" t="inlineStr"/>
+      <c r="T122" t="inlineStr"/>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>SALON COMUNAL VALENCIA Y BOMBAY</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>CRA. 72G # 39F-02 SUR</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="n">
+        <v>4.606635896006001</v>
+      </c>
+      <c r="G123" t="n">
+        <v>-74.14433302414838</v>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="K123" t="n">
+        <v>1.162768890098462</v>
+      </c>
+      <c r="L123" t="n">
+        <v>3.634036481487441</v>
+      </c>
+      <c r="M123" t="n">
+        <v>2.841613225142396</v>
+      </c>
+      <c r="N123" t="n">
+        <v>5.412381194638422</v>
+      </c>
+      <c r="O123" t="n">
+        <v>1.162768890098462</v>
+      </c>
+      <c r="P123" t="n">
+        <v>4.597906629392615</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R123" t="inlineStr"/>
+      <c r="S123" t="inlineStr"/>
+      <c r="T123" t="inlineStr"/>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Coincide con iglesia actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>COL. GUSTAVO ROJAS PINILLA SEDE B</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>CRA. 84D # 13-65</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="n">
+        <v>4.652884984468205</v>
+      </c>
+      <c r="G124" t="n">
+        <v>-74.13947856201627</v>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>VALLADOLID</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>VALLADOLID</t>
+        </is>
+      </c>
+      <c r="K124" t="n">
+        <v>1.106285166278131</v>
+      </c>
+      <c r="L124" t="n">
+        <v>5.908280298057636</v>
+      </c>
+      <c r="M124" t="n">
+        <v>4.472660396803884</v>
+      </c>
+      <c r="N124" t="n">
+        <v>3.7933357411618</v>
+      </c>
+      <c r="O124" t="n">
+        <v>4.064607507725719</v>
+      </c>
+      <c r="P124" t="n">
+        <v>1.106285166278131</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>1</v>
+      </c>
+      <c r="R124" t="inlineStr"/>
+      <c r="S124" t="inlineStr"/>
+      <c r="T124" t="inlineStr"/>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>TEMPLO</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>PUESTOS_ASIGNADOS</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>VOTOS_2026_ASIGNADOS</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>VOTOS_2023_ASIGNADOS</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>VARIACION_ABSOLUTA</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>VARIACION_PORCENTUAL</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>DISTANCIA_PROMEDIO_KM</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>DISTANCIA_MAXIMA_KM</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>PUESTOS_PRIORIDAD_ALTA</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>BARRIOS_CUBIERTOS</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>UPZ_CUBIERTAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CLASS ROMA</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C2" t="n">
+        <v>892</v>
+      </c>
+      <c r="D2" t="n">
+        <v>928.5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-36.5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-0.03931071620893915</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.8119912850729776</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.398664633453733</v>
+      </c>
+      <c r="I2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>PATIO BONITO</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1368</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1299.5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.05271258176221624</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.002150741572589</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.718757380328138</v>
+      </c>
+      <c r="I3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>KENNEDY CENTRAL</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>25</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1694.5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1699</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-0.00264861683343143</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.991851716356334</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.188098591657161</v>
+      </c>
+      <c r="I4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CARVAJAL</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>44</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1939.5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1873</v>
+      </c>
+      <c r="E5" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.03550453817405232</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.422424806481158</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.682828520472515</v>
+      </c>
+      <c r="I5" t="n">
+        <v>7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>VALLADOLID</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>26</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1454</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1370.5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.06092666909886903</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.239842801802185</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.104152965784638</v>
+      </c>
+      <c r="I6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:W124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/data/kennedy_mira_consolidado.xlsx
+++ b/data/kennedy_mira_consolidado.xlsx
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>El tablero identifica 30 puestos de prioridad alta y 43 puestos con cambio operativo de templo sugerido, manteniendo separada la iglesia histórica 2026 del templo propuesto para operación territorial.</t>
+          <t>El tablero identifica 30 puestos de prioridad alta y 26 puestos con cambio operativo de templo sugerido, manteniendo separada la iglesia histórica 2026 del templo propuesto para operación territorial.</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; la asignación documental se mantiene como PATIO BONITO.</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; la asignación documental se mantiene como CARVAJAL.</t>
         </is>
       </c>
     </row>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -1725,7 +1725,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; la asignación documental se mantiene como KENNEDY CENTRAL.</t>
         </is>
       </c>
     </row>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -1997,7 +1997,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>PATIO BONITO</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: PATIO BONITO.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; la asignación documental se mantiene como PATIO BONITO.</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>CARVAJAL</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: CARVAJAL.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -2661,7 +2661,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; la asignación documental se mantiene como KENNEDY CENTRAL.</t>
         </is>
       </c>
     </row>
@@ -3011,7 +3011,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>KENNEDY CENTRAL</t>
+          <t>CLASS ROMA</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: KENNEDY CENTRAL.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3285,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; la asignación documental se mantiene como KENNEDY CENTRAL.</t>
         </is>
       </c>
     </row>
@@ -3401,7 +3401,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>CLASS ROMA</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: CLASS ROMA.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>KENNEDY CENTRAL</t>
+          <t>PATIO BONITO</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: KENNEDY CENTRAL.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -3557,7 +3557,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>CLASS ROMA</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -3597,7 +3597,7 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: CLASS ROMA.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -3831,7 +3831,7 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -4065,7 +4065,7 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -4377,7 +4377,7 @@
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; la asignación documental se mantiene como KENNEDY CENTRAL.</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; la asignación documental se mantiene como PATIO BONITO.</t>
         </is>
       </c>
     </row>
@@ -4493,7 +4493,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>CARVAJAL</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -4533,7 +4533,7 @@
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: CARVAJAL.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -4689,7 +4689,7 @@
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -4767,7 +4767,7 @@
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -5001,7 +5001,7 @@
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; la asignación documental se mantiene como KENNEDY CENTRAL.</t>
         </is>
       </c>
     </row>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -5235,7 +5235,7 @@
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -5391,7 +5391,7 @@
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -5469,7 +5469,7 @@
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -5585,7 +5585,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>CARVAJAL</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="K59" t="n">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: CARVAJAL.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -5703,7 +5703,7 @@
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -5741,7 +5741,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>CLASS ROMA</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="K61" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: CLASS ROMA.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5937,7 @@
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -5975,7 +5975,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>CARVAJAL</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="K64" t="n">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: CARVAJAL.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -6053,7 +6053,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>CARVAJAL</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="K65" t="n">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: CARVAJAL.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -6171,7 +6171,7 @@
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -6249,7 +6249,7 @@
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -6327,7 +6327,7 @@
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; la asignación documental se mantiene como KENNEDY CENTRAL.</t>
         </is>
       </c>
     </row>
@@ -6405,7 +6405,7 @@
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -6483,7 +6483,7 @@
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; la asignación documental se mantiene como KENNEDY CENTRAL.</t>
         </is>
       </c>
     </row>
@@ -6561,7 +6561,7 @@
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; la asignación documental se mantiene como PATIO BONITO.</t>
         </is>
       </c>
     </row>
@@ -6639,7 +6639,7 @@
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -6717,7 +6717,7 @@
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; la asignación documental se mantiene como KENNEDY CENTRAL.</t>
         </is>
       </c>
     </row>
@@ -6795,7 +6795,7 @@
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; la asignación documental se mantiene como KENNEDY CENTRAL.</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; la asignación documental se mantiene como PATIO BONITO.</t>
         </is>
       </c>
     </row>
@@ -7029,7 +7029,7 @@
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -7107,7 +7107,7 @@
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; la asignación documental se mantiene como PATIO BONITO.</t>
         </is>
       </c>
     </row>
@@ -7185,7 +7185,7 @@
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -7223,7 +7223,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>KENNEDY CENTRAL</t>
+          <t>CARVAJAL</t>
         </is>
       </c>
       <c r="K80" t="n">
@@ -7263,7 +7263,7 @@
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: KENNEDY CENTRAL.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -7419,7 +7419,7 @@
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -7497,7 +7497,7 @@
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; la asignación documental se mantiene como KENNEDY CENTRAL.</t>
         </is>
       </c>
     </row>
@@ -7653,7 +7653,7 @@
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -7731,7 +7731,7 @@
       </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -7809,7 +7809,7 @@
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -7847,7 +7847,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>KENNEDY CENTRAL</t>
+          <t>PATIO BONITO</t>
         </is>
       </c>
       <c r="K88" t="n">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: KENNEDY CENTRAL.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -7965,7 +7965,7 @@
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; la asignación documental se mantiene como KENNEDY CENTRAL.</t>
         </is>
       </c>
     </row>
@@ -8043,7 +8043,7 @@
       </c>
       <c r="V90" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -8121,7 +8121,7 @@
       </c>
       <c r="V91" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -8199,7 +8199,7 @@
       </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; la asignación documental se mantiene como KENNEDY CENTRAL.</t>
         </is>
       </c>
     </row>
@@ -8277,7 +8277,7 @@
       </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -8355,7 +8355,7 @@
       </c>
       <c r="V94" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -8433,7 +8433,7 @@
       </c>
       <c r="V95" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>CARVAJAL</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="K96" t="n">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="V96" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: CARVAJAL.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -8589,7 +8589,7 @@
       </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; la asignación documental se mantiene como KENNEDY CENTRAL.</t>
         </is>
       </c>
     </row>
@@ -8627,7 +8627,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>CARVAJAL</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="K98" t="n">
@@ -8667,7 +8667,7 @@
       </c>
       <c r="V98" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: CARVAJAL.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -8745,7 +8745,7 @@
       </c>
       <c r="V99" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; la asignación documental se mantiene como KENNEDY CENTRAL.</t>
         </is>
       </c>
     </row>
@@ -8823,7 +8823,7 @@
       </c>
       <c r="V100" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; la asignación documental se mantiene como PATIO BONITO.</t>
         </is>
       </c>
     </row>
@@ -8901,7 +8901,7 @@
       </c>
       <c r="V101" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -8979,7 +8979,7 @@
       </c>
       <c r="V102" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -9057,7 +9057,7 @@
       </c>
       <c r="V103" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -9135,7 +9135,7 @@
       </c>
       <c r="V104" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; la asignación documental se mantiene como KENNEDY CENTRAL.</t>
         </is>
       </c>
     </row>
@@ -9213,7 +9213,7 @@
       </c>
       <c r="V105" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -9291,7 +9291,7 @@
       </c>
       <c r="V106" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -9369,7 +9369,7 @@
       </c>
       <c r="V107" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -9447,7 +9447,7 @@
       </c>
       <c r="V108" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -9525,7 +9525,7 @@
       </c>
       <c r="V109" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -9603,7 +9603,7 @@
       </c>
       <c r="V110" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="V111" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -9747,7 +9747,7 @@
       </c>
       <c r="V112" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -9819,7 +9819,7 @@
       </c>
       <c r="V113" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -9891,7 +9891,7 @@
       </c>
       <c r="V114" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -9963,7 +9963,7 @@
       </c>
       <c r="V115" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; la asignación documental se mantiene como KENNEDY CENTRAL.</t>
         </is>
       </c>
     </row>
@@ -10035,7 +10035,7 @@
       </c>
       <c r="V116" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="V117" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="V118" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; la asignación documental se mantiene como KENNEDY CENTRAL.</t>
         </is>
       </c>
     </row>
@@ -10217,7 +10217,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>CLASS ROMA</t>
+          <t>CARVAJAL</t>
         </is>
       </c>
       <c r="K119" t="n">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="V119" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: CLASS ROMA.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -10323,7 +10323,7 @@
       </c>
       <c r="V120" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -10361,7 +10361,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>CARVAJAL</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="K121" t="n">
@@ -10395,7 +10395,7 @@
       </c>
       <c r="V121" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: CARVAJAL.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -10467,7 +10467,7 @@
       </c>
       <c r="V122" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -10539,7 +10539,7 @@
       </c>
       <c r="V123" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
     </row>
@@ -10611,7 +10611,7 @@
       </c>
       <c r="V124" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; la asignación documental se mantiene como KENNEDY CENTRAL.</t>
         </is>
       </c>
     </row>
@@ -10693,28 +10693,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>892</v>
+        <v>791.5</v>
       </c>
       <c r="D2" t="n">
-        <v>928.5</v>
+        <v>801</v>
       </c>
       <c r="E2" t="n">
-        <v>-36.5</v>
+        <v>-9.5</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.03931071620893915</v>
+        <v>-0.0118601747815231</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8119912850729776</v>
+        <v>0.7434118850066025</v>
       </c>
       <c r="H2" t="n">
-        <v>1.398664633453733</v>
+        <v>1.252380169397706</v>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -10730,22 +10730,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
-        <v>1368</v>
+        <v>1323.5</v>
       </c>
       <c r="D3" t="n">
-        <v>1299.5</v>
+        <v>1278.5</v>
       </c>
       <c r="E3" t="n">
-        <v>68.5</v>
+        <v>45</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05271258176221624</v>
+        <v>0.03519749706687524</v>
       </c>
       <c r="G3" t="n">
-        <v>1.002150741572589</v>
+        <v>1.015003559605596</v>
       </c>
       <c r="H3" t="n">
         <v>1.718757380328138</v>
@@ -10767,25 +10767,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C4" t="n">
-        <v>1694.5</v>
+        <v>2191</v>
       </c>
       <c r="D4" t="n">
-        <v>1699</v>
+        <v>2181</v>
       </c>
       <c r="E4" t="n">
-        <v>-4.5</v>
+        <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.00264861683343143</v>
+        <v>0.004585052728106373</v>
       </c>
       <c r="G4" t="n">
-        <v>0.991851716356334</v>
+        <v>1.031457457846761</v>
       </c>
       <c r="H4" t="n">
-        <v>2.188098591657161</v>
+        <v>2.045654077098847</v>
       </c>
       <c r="I4" t="n">
         <v>6</v>
@@ -10804,28 +10804,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C5" t="n">
-        <v>1939.5</v>
+        <v>1588</v>
       </c>
       <c r="D5" t="n">
-        <v>1873</v>
+        <v>1539.5</v>
       </c>
       <c r="E5" t="n">
-        <v>66.5</v>
+        <v>48.5</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03550453817405232</v>
+        <v>0.03150373497888925</v>
       </c>
       <c r="G5" t="n">
-        <v>1.422424806481158</v>
+        <v>1.456661719659225</v>
       </c>
       <c r="H5" t="n">
         <v>2.682828520472515</v>
       </c>
       <c r="I5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -22618,7 +22618,7 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; la asignación documental se mantiene como PATIO BONITO.</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -22643,7 +22643,7 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>Asignación sugerida por cercanía territorial; conserva iglesia histórica para análisis electoral.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; los demás templos conservan la asignación documental.</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
@@ -22826,7 +22826,7 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -22851,7 +22851,7 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
@@ -23035,7 +23035,7 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -23060,7 +23060,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
@@ -23240,7 +23240,7 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; la asignación documental se mantiene como CARVAJAL.</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -23265,7 +23265,7 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>Asignación sugerida por cercanía territorial; conserva iglesia histórica para análisis electoral.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; los demás templos conservan la asignación documental.</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
@@ -23446,7 +23446,7 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -23471,7 +23471,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -23672,7 +23672,7 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
@@ -23852,7 +23852,7 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -23877,7 +23877,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
@@ -24057,7 +24057,7 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -24082,7 +24082,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
@@ -24263,7 +24263,7 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; la asignación documental se mantiene como KENNEDY CENTRAL.</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -24288,7 +24288,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>Asignación sugerida por cercanía territorial; conserva iglesia histórica para análisis electoral.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; los demás templos conservan la asignación documental.</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
@@ -24462,7 +24462,7 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -24487,7 +24487,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
@@ -24667,7 +24667,7 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -24692,7 +24692,7 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
@@ -24867,7 +24867,7 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>PATIO BONITO</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="AO13" t="n">
@@ -24875,7 +24875,7 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: PATIO BONITO.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
@@ -24890,17 +24890,17 @@
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>PATIO BONITO</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>Asignación sugerida por cercanía territorial; conserva iglesia histórica para análisis electoral.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
@@ -25084,7 +25084,7 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
@@ -25109,7 +25109,7 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
@@ -25283,7 +25283,7 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
@@ -25308,7 +25308,7 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
@@ -25488,7 +25488,7 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
@@ -25513,7 +25513,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
@@ -25691,7 +25691,7 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; la asignación documental se mantiene como PATIO BONITO.</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
@@ -25716,7 +25716,7 @@
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>Asignación sugerida por cercanía territorial; conserva iglesia histórica para análisis electoral.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; los demás templos conservan la asignación documental.</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
@@ -25892,7 +25892,7 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
@@ -25917,7 +25917,7 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
@@ -26097,7 +26097,7 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
@@ -26122,7 +26122,7 @@
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
@@ -26288,7 +26288,7 @@
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>CARVAJAL</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="AO20" t="n">
@@ -26296,7 +26296,7 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: CARVAJAL.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
@@ -26311,17 +26311,17 @@
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>CARVAJAL</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>Asignación sugerida por cercanía territorial; conserva iglesia histórica para análisis electoral.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
@@ -26495,7 +26495,7 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
@@ -26520,7 +26520,7 @@
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
@@ -26700,7 +26700,7 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
@@ -26725,7 +26725,7 @@
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
@@ -26906,7 +26906,7 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
@@ -26931,7 +26931,7 @@
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
@@ -27105,7 +27105,7 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ24" t="inlineStr">
@@ -27130,7 +27130,7 @@
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
@@ -27304,7 +27304,7 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; la asignación documental se mantiene como KENNEDY CENTRAL.</t>
         </is>
       </c>
       <c r="AQ25" t="inlineStr">
@@ -27329,7 +27329,7 @@
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>Asignación sugerida por cercanía territorial; conserva iglesia histórica para análisis electoral.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; los demás templos conservan la asignación documental.</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
@@ -27495,7 +27495,7 @@
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>KENNEDY CENTRAL</t>
+          <t>CLASS ROMA</t>
         </is>
       </c>
       <c r="AO26" t="n">
@@ -27503,7 +27503,7 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: KENNEDY CENTRAL.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
@@ -27518,17 +27518,17 @@
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>KENNEDY CENTRAL</t>
+          <t>CLASS ROMA</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>Asignación sugerida por cercanía territorial; conserva iglesia histórica para análisis electoral.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
@@ -27708,7 +27708,7 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
@@ -27733,7 +27733,7 @@
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
@@ -27907,7 +27907,7 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ28" t="inlineStr">
@@ -27932,7 +27932,7 @@
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
@@ -28113,7 +28113,7 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
@@ -28138,7 +28138,7 @@
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
@@ -28312,7 +28312,7 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; la asignación documental se mantiene como KENNEDY CENTRAL.</t>
         </is>
       </c>
       <c r="AQ30" t="inlineStr">
@@ -28337,7 +28337,7 @@
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>Asignación sugerida por cercanía territorial; conserva iglesia histórica para análisis electoral.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; los demás templos conservan la asignación documental.</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
@@ -28503,7 +28503,7 @@
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>CLASS ROMA</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="AO31" t="n">
@@ -28511,7 +28511,7 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: CLASS ROMA.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ31" t="inlineStr">
@@ -28526,17 +28526,17 @@
       </c>
       <c r="AS31" t="inlineStr">
         <is>
-          <t>CLASS ROMA</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>Asignación sugerida por cercanía territorial; conserva iglesia histórica para análisis electoral.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
@@ -28708,7 +28708,7 @@
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>KENNEDY CENTRAL</t>
+          <t>PATIO BONITO</t>
         </is>
       </c>
       <c r="AO32" t="n">
@@ -28716,7 +28716,7 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: KENNEDY CENTRAL.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
@@ -28731,17 +28731,17 @@
       </c>
       <c r="AS32" t="inlineStr">
         <is>
-          <t>KENNEDY CENTRAL</t>
+          <t>PATIO BONITO</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>Asignación sugerida por cercanía territorial; conserva iglesia histórica para análisis electoral.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
@@ -28907,7 +28907,7 @@
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>CLASS ROMA</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="AO33" t="n">
@@ -28915,7 +28915,7 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: CLASS ROMA.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
@@ -28930,17 +28930,17 @@
       </c>
       <c r="AS33" t="inlineStr">
         <is>
-          <t>CLASS ROMA</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>Asignación sugerida por cercanía territorial; conserva iglesia histórica para análisis electoral.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
@@ -29114,7 +29114,7 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
@@ -29139,7 +29139,7 @@
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
@@ -29320,7 +29320,7 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ35" t="inlineStr">
@@ -29345,7 +29345,7 @@
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
@@ -29519,7 +29519,7 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ36" t="inlineStr">
@@ -29544,7 +29544,7 @@
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
@@ -29718,7 +29718,7 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ37" t="inlineStr">
@@ -29743,7 +29743,7 @@
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
@@ -29917,7 +29917,7 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ38" t="inlineStr">
@@ -29942,7 +29942,7 @@
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
@@ -30116,7 +30116,7 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ39" t="inlineStr">
@@ -30141,7 +30141,7 @@
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
@@ -30315,7 +30315,7 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ40" t="inlineStr">
@@ -30340,7 +30340,7 @@
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV40" t="inlineStr">
@@ -30514,7 +30514,7 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ41" t="inlineStr">
@@ -30539,7 +30539,7 @@
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV41" t="inlineStr">
@@ -30713,7 +30713,7 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ42" t="inlineStr">
@@ -30738,7 +30738,7 @@
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
@@ -30912,7 +30912,7 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; la asignación documental se mantiene como KENNEDY CENTRAL.</t>
         </is>
       </c>
       <c r="AQ43" t="inlineStr">
@@ -30937,7 +30937,7 @@
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>Asignación sugerida por cercanía territorial; conserva iglesia histórica para análisis electoral.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; los demás templos conservan la asignación documental.</t>
         </is>
       </c>
       <c r="AV43" t="inlineStr">
@@ -31118,7 +31118,7 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; la asignación documental se mantiene como PATIO BONITO.</t>
         </is>
       </c>
       <c r="AQ44" t="inlineStr">
@@ -31143,7 +31143,7 @@
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>Asignación sugerida por cercanía territorial; conserva iglesia histórica para análisis electoral.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; los demás templos conservan la asignación documental.</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
@@ -31309,7 +31309,7 @@
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>CARVAJAL</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="AO45" t="n">
@@ -31317,7 +31317,7 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: CARVAJAL.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ45" t="inlineStr">
@@ -31332,17 +31332,17 @@
       </c>
       <c r="AS45" t="inlineStr">
         <is>
-          <t>CARVAJAL</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>Asignación sugerida por cercanía territorial; conserva iglesia histórica para análisis electoral.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
@@ -31516,7 +31516,7 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ46" t="inlineStr">
@@ -31541,7 +31541,7 @@
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
@@ -31715,7 +31715,7 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ47" t="inlineStr">
@@ -31740,7 +31740,7 @@
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
@@ -31920,7 +31920,7 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ48" t="inlineStr">
@@ -31945,7 +31945,7 @@
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV48" t="inlineStr">
@@ -32119,7 +32119,7 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ49" t="inlineStr">
@@ -32144,7 +32144,7 @@
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
@@ -32318,7 +32318,7 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ50" t="inlineStr">
@@ -32343,7 +32343,7 @@
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
@@ -32517,7 +32517,7 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; la asignación documental se mantiene como KENNEDY CENTRAL.</t>
         </is>
       </c>
       <c r="AQ51" t="inlineStr">
@@ -32542,7 +32542,7 @@
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>Asignación sugerida por cercanía territorial; conserva iglesia histórica para análisis electoral.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; los demás templos conservan la asignación documental.</t>
         </is>
       </c>
       <c r="AV51" t="inlineStr">
@@ -32723,7 +32723,7 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ52" t="inlineStr">
@@ -32748,7 +32748,7 @@
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
@@ -32928,7 +32928,7 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ53" t="inlineStr">
@@ -32953,7 +32953,7 @@
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
@@ -33127,7 +33127,7 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ54" t="inlineStr">
@@ -33152,7 +33152,7 @@
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV54" t="inlineStr">
@@ -33326,7 +33326,7 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ55" t="inlineStr">
@@ -33351,7 +33351,7 @@
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
@@ -33525,7 +33525,7 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ56" t="inlineStr">
@@ -33550,7 +33550,7 @@
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
@@ -33724,7 +33724,7 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ57" t="inlineStr">
@@ -33749,7 +33749,7 @@
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
@@ -33929,7 +33929,7 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ58" t="inlineStr">
@@ -33954,7 +33954,7 @@
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV58" t="inlineStr">
@@ -34127,7 +34127,7 @@
       </c>
       <c r="AN59" t="inlineStr">
         <is>
-          <t>CARVAJAL</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="AO59" t="n">
@@ -34135,7 +34135,7 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: CARVAJAL.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ59" t="inlineStr">
@@ -34150,17 +34150,17 @@
       </c>
       <c r="AS59" t="inlineStr">
         <is>
-          <t>CARVAJAL</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>Asignación sugerida por cercanía territorial; conserva iglesia histórica para análisis electoral.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV59" t="inlineStr">
@@ -34338,7 +34338,7 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ60" t="inlineStr">
@@ -34363,7 +34363,7 @@
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV60" t="inlineStr">
@@ -34529,7 +34529,7 @@
       </c>
       <c r="AN61" t="inlineStr">
         <is>
-          <t>CLASS ROMA</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="AO61" t="n">
@@ -34537,7 +34537,7 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: CLASS ROMA.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ61" t="inlineStr">
@@ -34552,17 +34552,17 @@
       </c>
       <c r="AS61" t="inlineStr">
         <is>
-          <t>CLASS ROMA</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>Asignación sugerida por cercanía territorial; conserva iglesia histórica para análisis electoral.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV61" t="inlineStr">
@@ -34740,7 +34740,7 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ62" t="inlineStr">
@@ -34765,7 +34765,7 @@
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
@@ -34939,7 +34939,7 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ63" t="inlineStr">
@@ -34964,7 +34964,7 @@
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV63" t="inlineStr">
@@ -35130,7 +35130,7 @@
       </c>
       <c r="AN64" t="inlineStr">
         <is>
-          <t>CARVAJAL</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="AO64" t="n">
@@ -35138,7 +35138,7 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: CARVAJAL.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ64" t="inlineStr">
@@ -35153,17 +35153,17 @@
       </c>
       <c r="AS64" t="inlineStr">
         <is>
-          <t>CARVAJAL</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>Asignación sugerida por cercanía territorial; conserva iglesia histórica para análisis electoral.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV64" t="inlineStr">
@@ -35329,7 +35329,7 @@
       </c>
       <c r="AN65" t="inlineStr">
         <is>
-          <t>CARVAJAL</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="AO65" t="n">
@@ -35337,7 +35337,7 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: CARVAJAL.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ65" t="inlineStr">
@@ -35352,17 +35352,17 @@
       </c>
       <c r="AS65" t="inlineStr">
         <is>
-          <t>CARVAJAL</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>Asignación sugerida por cercanía territorial; conserva iglesia histórica para análisis electoral.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV65" t="inlineStr">
@@ -35540,7 +35540,7 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ66" t="inlineStr">
@@ -35565,7 +35565,7 @@
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV66" t="inlineStr">
@@ -35739,7 +35739,7 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ67" t="inlineStr">
@@ -35764,7 +35764,7 @@
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV67" t="inlineStr">
@@ -35938,7 +35938,7 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; la asignación documental se mantiene como KENNEDY CENTRAL.</t>
         </is>
       </c>
       <c r="AQ68" t="inlineStr">
@@ -35963,7 +35963,7 @@
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>Asignación sugerida por cercanía territorial; conserva iglesia histórica para análisis electoral.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; los demás templos conservan la asignación documental.</t>
         </is>
       </c>
       <c r="AV68" t="inlineStr">
@@ -36137,7 +36137,7 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ69" t="inlineStr">
@@ -36162,7 +36162,7 @@
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV69" t="inlineStr">
@@ -36336,7 +36336,7 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; la asignación documental se mantiene como KENNEDY CENTRAL.</t>
         </is>
       </c>
       <c r="AQ70" t="inlineStr">
@@ -36361,7 +36361,7 @@
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>Asignación sugerida por cercanía territorial; conserva iglesia histórica para análisis electoral.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; los demás templos conservan la asignación documental.</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
@@ -36535,7 +36535,7 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; la asignación documental se mantiene como PATIO BONITO.</t>
         </is>
       </c>
       <c r="AQ71" t="inlineStr">
@@ -36560,7 +36560,7 @@
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>Asignación sugerida por cercanía territorial; conserva iglesia histórica para análisis electoral.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; los demás templos conservan la asignación documental.</t>
         </is>
       </c>
       <c r="AV71" t="inlineStr">
@@ -36734,7 +36734,7 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ72" t="inlineStr">
@@ -36759,7 +36759,7 @@
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV72" t="inlineStr">
@@ -36941,7 +36941,7 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; la asignación documental se mantiene como KENNEDY CENTRAL.</t>
         </is>
       </c>
       <c r="AQ73" t="inlineStr">
@@ -36966,7 +36966,7 @@
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>Asignación sugerida por cercanía territorial; conserva iglesia histórica para análisis electoral.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; los demás templos conservan la asignación documental.</t>
         </is>
       </c>
       <c r="AV73" t="inlineStr">
@@ -37144,7 +37144,7 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; la asignación documental se mantiene como KENNEDY CENTRAL.</t>
         </is>
       </c>
       <c r="AQ74" t="inlineStr">
@@ -37169,7 +37169,7 @@
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>Asignación sugerida por cercanía territorial; conserva iglesia histórica para análisis electoral.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; los demás templos conservan la asignación documental.</t>
         </is>
       </c>
       <c r="AV74" t="inlineStr">
@@ -37343,7 +37343,7 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ75" t="inlineStr">
@@ -37368,7 +37368,7 @@
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV75" t="inlineStr">
@@ -37542,7 +37542,7 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; la asignación documental se mantiene como PATIO BONITO.</t>
         </is>
       </c>
       <c r="AQ76" t="inlineStr">
@@ -37567,7 +37567,7 @@
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>Asignación sugerida por cercanía territorial; conserva iglesia histórica para análisis electoral.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; los demás templos conservan la asignación documental.</t>
         </is>
       </c>
       <c r="AV76" t="inlineStr">
@@ -37741,7 +37741,7 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ77" t="inlineStr">
@@ -37766,7 +37766,7 @@
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
@@ -37944,7 +37944,7 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; la asignación documental se mantiene como PATIO BONITO.</t>
         </is>
       </c>
       <c r="AQ78" t="inlineStr">
@@ -37969,7 +37969,7 @@
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>Asignación sugerida por cercanía territorial; conserva iglesia histórica para análisis electoral.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; los demás templos conservan la asignación documental.</t>
         </is>
       </c>
       <c r="AV78" t="inlineStr">
@@ -38143,7 +38143,7 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ79" t="inlineStr">
@@ -38168,7 +38168,7 @@
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV79" t="inlineStr">
@@ -38338,7 +38338,7 @@
       </c>
       <c r="AN80" t="inlineStr">
         <is>
-          <t>KENNEDY CENTRAL</t>
+          <t>CARVAJAL</t>
         </is>
       </c>
       <c r="AO80" t="n">
@@ -38346,7 +38346,7 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: KENNEDY CENTRAL.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ80" t="inlineStr">
@@ -38361,17 +38361,17 @@
       </c>
       <c r="AS80" t="inlineStr">
         <is>
-          <t>KENNEDY CENTRAL</t>
+          <t>CARVAJAL</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>Asignación sugerida por cercanía territorial; conserva iglesia histórica para análisis electoral.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV80" t="inlineStr">
@@ -38545,7 +38545,7 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ81" t="inlineStr">
@@ -38570,7 +38570,7 @@
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV81" t="inlineStr">
@@ -38750,7 +38750,7 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ82" t="inlineStr">
@@ -38775,7 +38775,7 @@
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV82" t="inlineStr">
@@ -38949,7 +38949,7 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ83" t="inlineStr">
@@ -38974,7 +38974,7 @@
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV83" t="inlineStr">
@@ -39156,7 +39156,7 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; la asignación documental se mantiene como KENNEDY CENTRAL.</t>
         </is>
       </c>
       <c r="AQ84" t="inlineStr">
@@ -39181,7 +39181,7 @@
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>Asignación sugerida por cercanía territorial; conserva iglesia histórica para análisis electoral.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; los demás templos conservan la asignación documental.</t>
         </is>
       </c>
       <c r="AV84" t="inlineStr">
@@ -39355,7 +39355,7 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ85" t="inlineStr">
@@ -39380,7 +39380,7 @@
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV85" t="inlineStr">
@@ -39554,7 +39554,7 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ86" t="inlineStr">
@@ -39579,7 +39579,7 @@
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV86" t="inlineStr">
@@ -39753,7 +39753,7 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ87" t="inlineStr">
@@ -39778,7 +39778,7 @@
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
@@ -39944,7 +39944,7 @@
       </c>
       <c r="AN88" t="inlineStr">
         <is>
-          <t>KENNEDY CENTRAL</t>
+          <t>PATIO BONITO</t>
         </is>
       </c>
       <c r="AO88" t="n">
@@ -39952,7 +39952,7 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: KENNEDY CENTRAL.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ88" t="inlineStr">
@@ -39967,17 +39967,17 @@
       </c>
       <c r="AS88" t="inlineStr">
         <is>
-          <t>KENNEDY CENTRAL</t>
+          <t>PATIO BONITO</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>Asignación sugerida por cercanía territorial; conserva iglesia histórica para análisis electoral.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
@@ -40151,7 +40151,7 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; la asignación documental se mantiene como KENNEDY CENTRAL.</t>
         </is>
       </c>
       <c r="AQ89" t="inlineStr">
@@ -40176,7 +40176,7 @@
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>Asignación sugerida por cercanía territorial; conserva iglesia histórica para análisis electoral.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; los demás templos conservan la asignación documental.</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
@@ -40350,7 +40350,7 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ90" t="inlineStr">
@@ -40375,7 +40375,7 @@
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV90" t="inlineStr">
@@ -40549,7 +40549,7 @@
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ91" t="inlineStr">
@@ -40574,7 +40574,7 @@
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV91" t="inlineStr">
@@ -40752,7 +40752,7 @@
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; la asignación documental se mantiene como KENNEDY CENTRAL.</t>
         </is>
       </c>
       <c r="AQ92" t="inlineStr">
@@ -40777,7 +40777,7 @@
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>Asignación sugerida por cercanía territorial; conserva iglesia histórica para análisis electoral.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; los demás templos conservan la asignación documental.</t>
         </is>
       </c>
       <c r="AV92" t="inlineStr">
@@ -40951,7 +40951,7 @@
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ93" t="inlineStr">
@@ -40976,7 +40976,7 @@
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV93" t="inlineStr">
@@ -41150,7 +41150,7 @@
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ94" t="inlineStr">
@@ -41175,7 +41175,7 @@
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV94" t="inlineStr">
@@ -41353,7 +41353,7 @@
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ95" t="inlineStr">
@@ -41378,7 +41378,7 @@
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV95" t="inlineStr">
@@ -41544,7 +41544,7 @@
       </c>
       <c r="AN96" t="inlineStr">
         <is>
-          <t>CARVAJAL</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="AO96" t="n">
@@ -41552,7 +41552,7 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: CARVAJAL.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ96" t="inlineStr">
@@ -41567,17 +41567,17 @@
       </c>
       <c r="AS96" t="inlineStr">
         <is>
-          <t>CARVAJAL</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>Asignación sugerida por cercanía territorial; conserva iglesia histórica para análisis electoral.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV96" t="inlineStr">
@@ -41751,7 +41751,7 @@
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; la asignación documental se mantiene como KENNEDY CENTRAL.</t>
         </is>
       </c>
       <c r="AQ97" t="inlineStr">
@@ -41776,7 +41776,7 @@
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>Asignación sugerida por cercanía territorial; conserva iglesia histórica para análisis electoral.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; los demás templos conservan la asignación documental.</t>
         </is>
       </c>
       <c r="AV97" t="inlineStr">
@@ -41942,7 +41942,7 @@
       </c>
       <c r="AN98" t="inlineStr">
         <is>
-          <t>CARVAJAL</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="AO98" t="n">
@@ -41950,7 +41950,7 @@
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: CARVAJAL.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ98" t="inlineStr">
@@ -41965,17 +41965,17 @@
       </c>
       <c r="AS98" t="inlineStr">
         <is>
-          <t>CARVAJAL</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>Asignación sugerida por cercanía territorial; conserva iglesia histórica para análisis electoral.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV98" t="inlineStr">
@@ -42153,7 +42153,7 @@
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; la asignación documental se mantiene como KENNEDY CENTRAL.</t>
         </is>
       </c>
       <c r="AQ99" t="inlineStr">
@@ -42178,7 +42178,7 @@
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>Asignación sugerida por cercanía territorial; conserva iglesia histórica para análisis electoral.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; los demás templos conservan la asignación documental.</t>
         </is>
       </c>
       <c r="AV99" t="inlineStr">
@@ -42352,7 +42352,7 @@
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; la asignación documental se mantiene como PATIO BONITO.</t>
         </is>
       </c>
       <c r="AQ100" t="inlineStr">
@@ -42377,7 +42377,7 @@
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>Asignación sugerida por cercanía territorial; conserva iglesia histórica para análisis electoral.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; los demás templos conservan la asignación documental.</t>
         </is>
       </c>
       <c r="AV100" t="inlineStr">
@@ -42555,7 +42555,7 @@
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ101" t="inlineStr">
@@ -42580,7 +42580,7 @@
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV101" t="inlineStr">
@@ -42754,7 +42754,7 @@
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ102" t="inlineStr">
@@ -42779,7 +42779,7 @@
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV102" t="inlineStr">
@@ -42953,7 +42953,7 @@
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ103" t="inlineStr">
@@ -42978,7 +42978,7 @@
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
@@ -43156,7 +43156,7 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; la asignación documental se mantiene como KENNEDY CENTRAL.</t>
         </is>
       </c>
       <c r="AQ104" t="inlineStr">
@@ -43181,7 +43181,7 @@
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>Asignación sugerida por cercanía territorial; conserva iglesia histórica para análisis electoral.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; los demás templos conservan la asignación documental.</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
@@ -43355,7 +43355,7 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ105" t="inlineStr">
@@ -43380,7 +43380,7 @@
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
@@ -43554,7 +43554,7 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ106" t="inlineStr">
@@ -43579,7 +43579,7 @@
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
@@ -43757,7 +43757,7 @@
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ107" t="inlineStr">
@@ -43782,7 +43782,7 @@
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
@@ -43960,7 +43960,7 @@
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ108" t="inlineStr">
@@ -43985,7 +43985,7 @@
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV108" t="inlineStr">
@@ -44159,7 +44159,7 @@
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ109" t="inlineStr">
@@ -44184,7 +44184,7 @@
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
@@ -44358,7 +44358,7 @@
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ110" t="inlineStr">
@@ -44383,7 +44383,7 @@
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
@@ -44543,7 +44543,7 @@
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ111" t="inlineStr">
@@ -44568,7 +44568,7 @@
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV111" t="inlineStr">
@@ -44728,7 +44728,7 @@
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ112" t="inlineStr">
@@ -44753,7 +44753,7 @@
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV112" t="inlineStr">
@@ -44913,7 +44913,7 @@
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ113" t="inlineStr">
@@ -44938,7 +44938,7 @@
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV113" t="inlineStr">
@@ -45098,7 +45098,7 @@
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ114" t="inlineStr">
@@ -45123,7 +45123,7 @@
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV114" t="inlineStr">
@@ -45283,7 +45283,7 @@
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; la asignación documental se mantiene como KENNEDY CENTRAL.</t>
         </is>
       </c>
       <c r="AQ115" t="inlineStr">
@@ -45308,7 +45308,7 @@
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>Asignación sugerida por cercanía territorial; conserva iglesia histórica para análisis electoral.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; los demás templos conservan la asignación documental.</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
@@ -45468,7 +45468,7 @@
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ116" t="inlineStr">
@@ -45493,7 +45493,7 @@
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
@@ -45653,7 +45653,7 @@
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ117" t="inlineStr">
@@ -45678,7 +45678,7 @@
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
@@ -45838,7 +45838,7 @@
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; la asignación documental se mantiene como KENNEDY CENTRAL.</t>
         </is>
       </c>
       <c r="AQ118" t="inlineStr">
@@ -45863,7 +45863,7 @@
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>Asignación sugerida por cercanía territorial; conserva iglesia histórica para análisis electoral.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; los demás templos conservan la asignación documental.</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
@@ -46015,7 +46015,7 @@
       </c>
       <c r="AN119" t="inlineStr">
         <is>
-          <t>CLASS ROMA</t>
+          <t>CARVAJAL</t>
         </is>
       </c>
       <c r="AO119" t="n">
@@ -46023,7 +46023,7 @@
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: CLASS ROMA.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ119" t="inlineStr">
@@ -46038,17 +46038,17 @@
       </c>
       <c r="AS119" t="inlineStr">
         <is>
-          <t>CLASS ROMA</t>
+          <t>CARVAJAL</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>Asignación sugerida por cercanía territorial; conserva iglesia histórica para análisis electoral.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
@@ -46208,7 +46208,7 @@
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ120" t="inlineStr">
@@ -46233,7 +46233,7 @@
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
@@ -46385,7 +46385,7 @@
       </c>
       <c r="AN121" t="inlineStr">
         <is>
-          <t>CARVAJAL</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="AO121" t="n">
@@ -46393,7 +46393,7 @@
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: CARVAJAL.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ121" t="inlineStr">
@@ -46408,17 +46408,17 @@
       </c>
       <c r="AS121" t="inlineStr">
         <is>
-          <t>CARVAJAL</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>Asignación sugerida por cercanía territorial; conserva iglesia histórica para análisis electoral.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
@@ -46578,7 +46578,7 @@
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ122" t="inlineStr">
@@ -46603,7 +46603,7 @@
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
@@ -46763,7 +46763,7 @@
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>Coincide con iglesia actual.</t>
+          <t>Se conserva el templo asignado en el documento base.</t>
         </is>
       </c>
       <c r="AQ123" t="inlineStr">
@@ -46788,7 +46788,7 @@
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>La asignación propuesta coincide con la iglesia histórica 2026.</t>
+          <t>Se conserva la asignación documental del puesto.</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
@@ -46948,7 +46948,7 @@
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>Reasignación sugerida por cercanía: VALLADOLID.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; la asignación documental se mantiene como KENNEDY CENTRAL.</t>
         </is>
       </c>
       <c r="AQ124" t="inlineStr">
@@ -46973,7 +46973,7 @@
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>Asignación sugerida por cercanía territorial; conserva iglesia histórica para análisis electoral.</t>
+          <t>Propuesta específica para Valladolid por cercanía territorial; los demás templos conservan la asignación documental.</t>
         </is>
       </c>
       <c r="AV124" t="inlineStr">
@@ -65677,12 +65677,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PATIO BONITO</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -66202,12 +66202,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CARVAJAL</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -66652,12 +66652,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>KENNEDY CENTRAL</t>
+          <t>CLASS ROMA</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -67027,12 +67027,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CLASS ROMA</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -67102,12 +67102,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>KENNEDY CENTRAL</t>
+          <t>PATIO BONITO</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -67177,12 +67177,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CLASS ROMA</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -68077,12 +68077,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>CARVAJAL</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -69127,12 +69127,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>CARVAJAL</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -69277,12 +69277,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>CLASS ROMA</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -69502,12 +69502,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>CARVAJAL</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -69577,12 +69577,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>CARVAJAL</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -70702,12 +70702,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>KENNEDY CENTRAL</t>
+          <t>CARVAJAL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -71302,12 +71302,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>KENNEDY CENTRAL</t>
+          <t>PATIO BONITO</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -71902,12 +71902,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>CARVAJAL</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -72052,12 +72052,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>CARVAJAL</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -73579,12 +73579,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>CLASS ROMA</t>
+          <t>CARVAJAL</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -73717,12 +73717,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>CARVAJAL</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -75342,12 +75342,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>PATIO BONITO</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -75391,7 +75391,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>PATIO BONITO</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
     </row>
@@ -75965,12 +75965,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>CARVAJAL</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
@@ -76014,7 +76014,7 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>CARVAJAL</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
     </row>
@@ -76499,12 +76499,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>KENNEDY CENTRAL</t>
+          <t>CLASS ROMA</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
@@ -76548,7 +76548,7 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>KENNEDY CENTRAL</t>
+          <t>CLASS ROMA</t>
         </is>
       </c>
     </row>
@@ -76944,12 +76944,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>CLASS ROMA</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
@@ -76993,7 +76993,7 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>CLASS ROMA</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
     </row>
@@ -77033,12 +77033,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>KENNEDY CENTRAL</t>
+          <t>PATIO BONITO</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
@@ -77082,7 +77082,7 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>KENNEDY CENTRAL</t>
+          <t>PATIO BONITO</t>
         </is>
       </c>
     </row>
@@ -77122,12 +77122,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>CLASS ROMA</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
@@ -77171,7 +77171,7 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>CLASS ROMA</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
     </row>
@@ -78190,12 +78190,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>CARVAJAL</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J45" t="inlineStr"/>
@@ -78239,7 +78239,7 @@
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>CARVAJAL</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
     </row>
@@ -79436,12 +79436,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>CARVAJAL</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J59" t="inlineStr"/>
@@ -79485,7 +79485,7 @@
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>CARVAJAL</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
     </row>
@@ -79614,12 +79614,12 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>CLASS ROMA</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J61" t="inlineStr"/>
@@ -79663,7 +79663,7 @@
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>CLASS ROMA</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
     </row>
@@ -79881,12 +79881,12 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>CARVAJAL</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J64" t="inlineStr"/>
@@ -79930,7 +79930,7 @@
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>CARVAJAL</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
     </row>
@@ -79970,12 +79970,12 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>CARVAJAL</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J65" t="inlineStr"/>
@@ -80019,7 +80019,7 @@
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>CARVAJAL</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
     </row>
@@ -81305,12 +81305,12 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>KENNEDY CENTRAL</t>
+          <t>CARVAJAL</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J80" t="inlineStr"/>
@@ -81354,7 +81354,7 @@
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>KENNEDY CENTRAL</t>
+          <t>CARVAJAL</t>
         </is>
       </c>
     </row>
@@ -82017,12 +82017,12 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>KENNEDY CENTRAL</t>
+          <t>PATIO BONITO</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J88" t="inlineStr"/>
@@ -82066,7 +82066,7 @@
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>KENNEDY CENTRAL</t>
+          <t>PATIO BONITO</t>
         </is>
       </c>
     </row>
@@ -82729,12 +82729,12 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>CARVAJAL</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J96" t="inlineStr"/>
@@ -82778,7 +82778,7 @@
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>CARVAJAL</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
     </row>
@@ -82907,12 +82907,12 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>CARVAJAL</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J98" t="inlineStr"/>
@@ -82956,7 +82956,7 @@
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>CARVAJAL</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
     </row>
@@ -84728,12 +84728,12 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>CLASS ROMA</t>
+          <t>CARVAJAL</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J119" t="inlineStr"/>
@@ -84771,7 +84771,7 @@
       </c>
       <c r="U119" t="inlineStr">
         <is>
-          <t>CLASS ROMA</t>
+          <t>CARVAJAL</t>
         </is>
       </c>
     </row>
@@ -84894,12 +84894,12 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>CARVAJAL</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J121" t="inlineStr"/>
@@ -84937,7 +84937,7 @@
       </c>
       <c r="U121" t="inlineStr">
         <is>
-          <t>CARVAJAL</t>
+          <t>KENNEDY CENTRAL</t>
         </is>
       </c>
     </row>
